--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="R295a71fde0c64aec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="R7ac048be70634af5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="R5c192cadf0f34090"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="Rc0c23b8f58a04469"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="R5c192cadf0f34090"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="Rc0c23b8f58a04469"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="Reba4faccc9874934"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="R24cb07a42f83411e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -440,6 +440,7 @@
     <x:col min="13" max="13" width="13" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="13" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="13" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="13" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -447,46 +448,49 @@
         <x:v>Date</x:v>
       </x:c>
       <x:c r="B1" s="22" t="n">
-        <x:v>46216</x:v>
+        <x:v>46223</x:v>
       </x:c>
       <x:c r="C1" s="22" t="n">
-        <x:v>46217</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="D1" s="22" t="n">
-        <x:v>46218</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="E1" s="22" t="n">
-        <x:v>46219</x:v>
+        <x:v>46226</x:v>
       </x:c>
       <x:c r="F1" s="22" t="n">
-        <x:v>46220</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="G1" s="22" t="n">
-        <x:v>46221</x:v>
+        <x:v>46228</x:v>
       </x:c>
       <x:c r="H1" s="22" t="n">
-        <x:v>46222</x:v>
+        <x:v>46229</x:v>
       </x:c>
       <x:c r="I1" s="22" t="n">
-        <x:v>46223</x:v>
+        <x:v>46230</x:v>
       </x:c>
       <x:c r="J1" s="22" t="n">
-        <x:v>46224</x:v>
+        <x:v>46231</x:v>
       </x:c>
       <x:c r="K1" s="22" t="n">
-        <x:v>46225</x:v>
+        <x:v>46232</x:v>
       </x:c>
       <x:c r="L1" s="22" t="n">
-        <x:v>46226</x:v>
+        <x:v>46233</x:v>
       </x:c>
       <x:c r="M1" s="22" t="n">
-        <x:v>46227</x:v>
+        <x:v>46234</x:v>
       </x:c>
       <x:c r="N1" s="22" t="n">
-        <x:v>46228</x:v>
-      </x:c>
-      <x:c r="O1" s="23" t="n">
-        <x:v>46229</x:v>
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="O1" s="22" t="n">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="P1" s="23" t="n">
+        <x:v>46237</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -494,46 +498,49 @@
         <x:v>网站整体用户数</x:v>
       </x:c>
       <x:c r="B2" s="24" t="n">
-        <x:v>7918</x:v>
+        <x:v>6376</x:v>
       </x:c>
       <x:c r="C2" s="24" t="n">
-        <x:v>7298</x:v>
+        <x:v>6020</x:v>
       </x:c>
       <x:c r="D2" s="24" t="n">
-        <x:v>6646</x:v>
+        <x:v>5642</x:v>
       </x:c>
       <x:c r="E2" s="24" t="n">
-        <x:v>5549</x:v>
+        <x:v>5813</x:v>
       </x:c>
       <x:c r="F2" s="24" t="n">
-        <x:v>5282</x:v>
+        <x:v>5425</x:v>
       </x:c>
       <x:c r="G2" s="24" t="n">
-        <x:v>5656</x:v>
+        <x:v>6001</x:v>
       </x:c>
       <x:c r="H2" s="24" t="n">
-        <x:v>6685</x:v>
+        <x:v>7931</x:v>
       </x:c>
       <x:c r="I2" s="24" t="n">
-        <x:v>6376</x:v>
+        <x:v>6688</x:v>
       </x:c>
       <x:c r="J2" s="24" t="n">
-        <x:v>6020</x:v>
+        <x:v>5981</x:v>
       </x:c>
       <x:c r="K2" s="24" t="n">
-        <x:v>5642</x:v>
+        <x:v>6542</x:v>
       </x:c>
       <x:c r="L2" s="24" t="n">
-        <x:v>5813</x:v>
+        <x:v>5390</x:v>
       </x:c>
       <x:c r="M2" s="24" t="n">
-        <x:v>5425</x:v>
+        <x:v>5797</x:v>
       </x:c>
       <x:c r="N2" s="24" t="n">
-        <x:v>6001</x:v>
-      </x:c>
-      <x:c r="O2" s="25" t="n">
-        <x:v>7931</x:v>
+        <x:v>6231</x:v>
+      </x:c>
+      <x:c r="O2" s="24" t="n">
+        <x:v>6319</x:v>
+      </x:c>
+      <x:c r="P2" s="25" t="n">
+        <x:v>5508</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -541,46 +548,49 @@
         <x:v>使用AI用户数</x:v>
       </x:c>
       <x:c r="B3" s="24" t="n">
-        <x:v>597</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="C3" s="24" t="n">
-        <x:v>597</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="D3" s="24" t="n">
-        <x:v>585</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="E3" s="24" t="n">
-        <x:v>627</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="F3" s="24" t="n">
-        <x:v>571</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="G3" s="24" t="n">
-        <x:v>646</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="H3" s="24" t="n">
-        <x:v>757</x:v>
+        <x:v>879</x:v>
       </x:c>
       <x:c r="I3" s="24" t="n">
-        <x:v>682</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="J3" s="24" t="n">
-        <x:v>614</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="K3" s="24" t="n">
-        <x:v>633</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="L3" s="24" t="n">
-        <x:v>615</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="M3" s="24" t="n">
-        <x:v>618</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="N3" s="24" t="n">
-        <x:v>620</x:v>
-      </x:c>
-      <x:c r="O3" s="25" t="n">
-        <x:v>879</x:v>
+        <x:v>702</x:v>
+      </x:c>
+      <x:c r="O3" s="24" t="n">
+        <x:v>737</x:v>
+      </x:c>
+      <x:c r="P3" s="25" t="n">
+        <x:v>693</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -588,151 +598,199 @@
         <x:v>AI-UV渗透</x:v>
       </x:c>
       <x:c r="B4" s="26" t="n">
-        <x:v>0.07539782773427633</x:v>
+        <x:v>0.10696361355081556</x:v>
       </x:c>
       <x:c r="C4" s="26" t="n">
-        <x:v>0.0818032337626747</x:v>
+        <x:v>0.10199335548172757</x:v>
       </x:c>
       <x:c r="D4" s="26" t="n">
-        <x:v>0.08802287089978934</x:v>
+        <x:v>0.11219425735554768</x:v>
       </x:c>
       <x:c r="E4" s="26" t="n">
-        <x:v>0.11299333213191566</x:v>
+        <x:v>0.10579735076552554</x:v>
       </x:c>
       <x:c r="F4" s="26" t="n">
-        <x:v>0.10810299129117758</x:v>
+        <x:v>0.11391705069124423</x:v>
       </x:c>
       <x:c r="G4" s="26" t="n">
-        <x:v>0.11421499292786422</x:v>
+        <x:v>0.10331611398100317</x:v>
       </x:c>
       <x:c r="H4" s="26" t="n">
-        <x:v>0.11323859386686612</x:v>
+        <x:v>0.11083091665615938</x:v>
       </x:c>
       <x:c r="I4" s="26" t="n">
-        <x:v>0.10696361355081556</x:v>
+        <x:v>0.11124401913875598</x:v>
       </x:c>
       <x:c r="J4" s="26" t="n">
-        <x:v>0.10199335548172757</x:v>
+        <x:v>0.119879618792844</x:v>
       </x:c>
       <x:c r="K4" s="26" t="n">
-        <x:v>0.11219425735554768</x:v>
+        <x:v>0.11403240599205136</x:v>
       </x:c>
       <x:c r="L4" s="26" t="n">
-        <x:v>0.10579735076552554</x:v>
+        <x:v>0.12282003710575139</x:v>
       </x:c>
       <x:c r="M4" s="26" t="n">
-        <x:v>0.11391705069124423</x:v>
+        <x:v>0.12903225806451613</x:v>
       </x:c>
       <x:c r="N4" s="26" t="n">
-        <x:v>0.10331611398100317</x:v>
-      </x:c>
-      <x:c r="O4" s="27" t="n">
-        <x:v>0.11083091665615938</x:v>
+        <x:v>0.11266249398170439</x:v>
+      </x:c>
+      <x:c r="O4" s="26" t="n">
+        <x:v>0.11663237854090837</x:v>
+      </x:c>
+      <x:c r="P4" s="27" t="n">
+        <x:v>0.12581699346405228</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="19" t="str">
         <x:v>平均会话轮次</x:v>
       </x:c>
-      <x:c r="B5" s="28"/>
-      <x:c r="C5" s="28"/>
-      <x:c r="D5" s="28"/>
-      <x:c r="E5" s="28"/>
-      <x:c r="F5" s="28"/>
-      <x:c r="G5" s="28"/>
+      <x:c r="B5" s="28" t="n">
+        <x:v>1.392156862745098</x:v>
+      </x:c>
+      <x:c r="C5" s="28" t="n">
+        <x:v>1.4372294372294372</x:v>
+      </x:c>
+      <x:c r="D5" s="28" t="n">
+        <x:v>1.3585858585858586</x:v>
+      </x:c>
+      <x:c r="E5" s="28" t="n">
+        <x:v>1.390625</x:v>
+      </x:c>
+      <x:c r="F5" s="28" t="n">
+        <x:v>1.2634146341463415</x:v>
+      </x:c>
+      <x:c r="G5" s="28" t="n">
+        <x:v>1.4303977272727273</x:v>
+      </x:c>
       <x:c r="H5" s="28" t="n">
-        <x:v>1.3399122807017543</x:v>
+        <x:v>1.4630541871921183</x:v>
       </x:c>
       <x:c r="I5" s="28" t="n">
-        <x:v>1.392156862745098</x:v>
+        <x:v>1.288056206088993</x:v>
       </x:c>
       <x:c r="J5" s="28" t="n">
-        <x:v>1.4372294372294372</x:v>
+        <x:v>1.4005235602094241</x:v>
       </x:c>
       <x:c r="K5" s="28" t="n">
-        <x:v>1.3585858585858586</x:v>
+        <x:v>1.4366998577524894</x:v>
       </x:c>
       <x:c r="L5" s="28" t="n">
-        <x:v>1.390625</x:v>
+        <x:v>1.4586070959264126</x:v>
       </x:c>
       <x:c r="M5" s="28" t="n">
-        <x:v>1.2634146341463415</x:v>
+        <x:v>1.4132352941176471</x:v>
       </x:c>
       <x:c r="N5" s="28" t="n">
-        <x:v>1.4303977272727273</x:v>
-      </x:c>
-      <x:c r="O5" s="29" t="n">
-        <x:v>1.4630541871921183</x:v>
+        <x:v>1.485054347826087</x:v>
+      </x:c>
+      <x:c r="O5" s="28" t="n">
+        <x:v>1.490566037735849</x:v>
+      </x:c>
+      <x:c r="P5" s="29" t="n">
+        <x:v>1.4643962848297214</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="19" t="str">
         <x:v>2V2会话用户数</x:v>
       </x:c>
-      <x:c r="B6" s="24"/>
-      <x:c r="C6" s="24"/>
-      <x:c r="D6" s="24"/>
-      <x:c r="E6" s="24"/>
-      <x:c r="F6" s="24"/>
-      <x:c r="G6" s="24"/>
+      <x:c r="B6" s="24" t="n">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C6" s="24" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D6" s="24" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E6" s="24" t="n">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="F6" s="24" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G6" s="24" t="n">
+        <x:v>155</x:v>
+      </x:c>
       <x:c r="H6" s="24" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="I6" s="24" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="J6" s="24" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="K6" s="24" t="n">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="L6" s="24" t="n">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="M6" s="24" t="n">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="N6" s="24" t="n">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="O6" s="24" t="n">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="P6" s="25" t="n">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="I6" s="24" t="n">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="J6" s="24" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="K6" s="24" t="n">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="L6" s="24" t="n">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="M6" s="24" t="n">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="N6" s="24" t="n">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="O6" s="25" t="n">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="19" t="str">
         <x:v>2V2会话用户占比</x:v>
       </x:c>
-      <x:c r="B7" s="26"/>
-      <x:c r="C7" s="26"/>
-      <x:c r="D7" s="26"/>
-      <x:c r="E7" s="26"/>
-      <x:c r="F7" s="26"/>
-      <x:c r="G7" s="26"/>
+      <x:c r="B7" s="26" t="n">
+        <x:v>0.1744868035190616</x:v>
+      </x:c>
+      <x:c r="C7" s="26" t="n">
+        <x:v>0.0732899022801303</x:v>
+      </x:c>
+      <x:c r="D7" s="26" t="n">
+        <x:v>0.17535545023696683</x:v>
+      </x:c>
+      <x:c r="E7" s="26" t="n">
+        <x:v>0.21300813008130082</x:v>
+      </x:c>
+      <x:c r="F7" s="26" t="n">
+        <x:v>0.13592233009708737</x:v>
+      </x:c>
+      <x:c r="G7" s="26" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
       <x:c r="H7" s="26" t="n">
-        <x:v>0.10700132100396301</x:v>
+        <x:v>0.055745164960182024</x:v>
       </x:c>
       <x:c r="I7" s="26" t="n">
-        <x:v>0.1744868035190616</x:v>
+        <x:v>0.09543010752688172</x:v>
       </x:c>
       <x:c r="J7" s="26" t="n">
-        <x:v>0.0732899022801303</x:v>
+        <x:v>0.21478382147838215</x:v>
       </x:c>
       <x:c r="K7" s="26" t="n">
-        <x:v>0.17535545023696683</x:v>
+        <x:v>0.21045576407506703</x:v>
       </x:c>
       <x:c r="L7" s="26" t="n">
-        <x:v>0.21300813008130082</x:v>
+        <x:v>0.26132930513595165</x:v>
       </x:c>
       <x:c r="M7" s="26" t="n">
-        <x:v>0.13592233009708737</x:v>
+        <x:v>0.20855614973262032</x:v>
       </x:c>
       <x:c r="N7" s="26" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="O7" s="27" t="n">
-        <x:v>0.055745164960182024</x:v>
+        <x:v>0.25783475783475784</x:v>
+      </x:c>
+      <x:c r="O7" s="26" t="n">
+        <x:v>0.23202170963364993</x:v>
+      </x:c>
+      <x:c r="P7" s="27" t="n">
+        <x:v>0.11688311688311688</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -740,46 +798,49 @@
         <x:v>推荐产品卡片曝光数</x:v>
       </x:c>
       <x:c r="B8" s="24" t="n">
-        <x:v>419</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C8" s="24" t="n">
-        <x:v>384</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="D8" s="24" t="n">
-        <x:v>394</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="E8" s="24" t="n">
-        <x:v>429</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="F8" s="24" t="n">
-        <x:v>382</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="G8" s="24" t="n">
-        <x:v>458</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="H8" s="24" t="n">
-        <x:v>518</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="I8" s="24" t="n">
-        <x:v>196</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="J8" s="24" t="n">
-        <x:v>362</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="K8" s="24" t="n">
-        <x:v>323</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="L8" s="24" t="n">
-        <x:v>341</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="M8" s="24" t="n">
-        <x:v>351</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="N8" s="24" t="n">
-        <x:v>459</x:v>
-      </x:c>
-      <x:c r="O8" s="25" t="n">
-        <x:v>619</x:v>
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="O8" s="24" t="n">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="P8" s="25" t="n">
+        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -787,46 +848,49 @@
         <x:v>推荐产品卡片点击数</x:v>
       </x:c>
       <x:c r="B9" s="24" t="n">
-        <x:v>103</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C9" s="24" t="n">
-        <x:v>95</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D9" s="24" t="n">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E9" s="24" t="n">
-        <x:v>105</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F9" s="24" t="n">
-        <x:v>89</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G9" s="24" t="n">
-        <x:v>120</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H9" s="24" t="n">
-        <x:v>127</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="I9" s="24" t="n">
-        <x:v>59</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J9" s="24" t="n">
-        <x:v>88</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="K9" s="24" t="n">
-        <x:v>74</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="L9" s="24" t="n">
-        <x:v>83</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="M9" s="24" t="n">
-        <x:v>71</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="N9" s="24" t="n">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="O9" s="25" t="n">
-        <x:v>137</x:v>
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="O9" s="24" t="n">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="P9" s="25" t="n">
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -834,46 +898,49 @@
         <x:v>推荐产品CTR</x:v>
       </x:c>
       <x:c r="B10" s="26" t="n">
-        <x:v>0.2458233890214797</x:v>
+        <x:v>0.3010204081632653</x:v>
       </x:c>
       <x:c r="C10" s="26" t="n">
-        <x:v>0.24739583333333334</x:v>
+        <x:v>0.2430939226519337</x:v>
       </x:c>
       <x:c r="D10" s="26" t="n">
-        <x:v>0.20304568527918782</x:v>
+        <x:v>0.22910216718266255</x:v>
       </x:c>
       <x:c r="E10" s="26" t="n">
-        <x:v>0.24475524475524477</x:v>
+        <x:v>0.2434017595307918</x:v>
       </x:c>
       <x:c r="F10" s="26" t="n">
-        <x:v>0.23298429319371727</x:v>
+        <x:v>0.2022792022792023</x:v>
       </x:c>
       <x:c r="G10" s="26" t="n">
-        <x:v>0.26200873362445415</x:v>
+        <x:v>0.2374727668845316</x:v>
       </x:c>
       <x:c r="H10" s="26" t="n">
-        <x:v>0.24517374517374518</x:v>
+        <x:v>0.22132471728594508</x:v>
       </x:c>
       <x:c r="I10" s="26" t="n">
-        <x:v>0.3010204081632653</x:v>
+        <x:v>0.21359223300970873</x:v>
       </x:c>
       <x:c r="J10" s="26" t="n">
-        <x:v>0.2430939226519337</x:v>
+        <x:v>0.22077922077922077</x:v>
       </x:c>
       <x:c r="K10" s="26" t="n">
-        <x:v>0.22910216718266255</x:v>
+        <x:v>0.25824175824175827</x:v>
       </x:c>
       <x:c r="L10" s="26" t="n">
-        <x:v>0.2434017595307918</x:v>
+        <x:v>0.2540650406504065</x:v>
       </x:c>
       <x:c r="M10" s="26" t="n">
-        <x:v>0.2022792022792023</x:v>
+        <x:v>0.2286902286902287</x:v>
       </x:c>
       <x:c r="N10" s="26" t="n">
-        <x:v>0.2374727668845316</x:v>
-      </x:c>
-      <x:c r="O10" s="27" t="n">
-        <x:v>0.22132471728594508</x:v>
+        <x:v>0.2250453720508167</x:v>
+      </x:c>
+      <x:c r="O10" s="26" t="n">
+        <x:v>0.24577861163227016</x:v>
+      </x:c>
+      <x:c r="P10" s="27" t="n">
+        <x:v>0.22108843537414966</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -881,54 +948,55 @@
         <x:v>网站总线索数</x:v>
       </x:c>
       <x:c r="B11" s="24" t="n">
-        <x:v>52</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C11" s="24" t="n">
-        <x:v>53</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D11" s="24" t="n">
-        <x:v>23</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E11" s="24" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F11" s="24" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G11" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H11" s="24" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F11" s="24" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G11" s="24" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H11" s="24" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="I11" s="24" t="n">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J11" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K11" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L11" s="24" t="n">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="M11" s="24" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N11" s="24" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="O11" s="25" t="n">
-        <x:v>7</x:v>
-      </x:c>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="O11" s="24" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="P11" s="25"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="19" t="str">
         <x:v>AI产生线索数</x:v>
       </x:c>
       <x:c r="B12" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
         <x:v>1</x:v>
@@ -937,116 +1005,118 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E12" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F12" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G12" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I12" s="24" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J12" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I12" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J12" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="K12" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L12" s="24" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="M12" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N12" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O12" s="25" t="n">
-        <x:v>3</x:v>
-      </x:c>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="O12" s="24" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="P12" s="25"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="19" t="str">
         <x:v>AI线索贡献占比</x:v>
       </x:c>
       <x:c r="B13" s="26" t="n">
-        <x:v>0.038461538461538464</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C13" s="26" t="n">
-        <x:v>0.018867924528301886</x:v>
+        <x:v>0.14285714285714285</x:v>
       </x:c>
       <x:c r="D13" s="26" t="n">
-        <x:v>0.08695652173913043</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="E13" s="26" t="n">
-        <x:v>0</x:v>
+        <x:v>0.5333333333333333</x:v>
       </x:c>
       <x:c r="F13" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="G13" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H13" s="26" t="n">
+        <x:v>0.42857142857142855</x:v>
+      </x:c>
+      <x:c r="I13" s="26" t="n">
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="I13" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="J13" s="26" t="n">
-        <x:v>0.14285714285714285</x:v>
+        <x:v>0.18181818181818182</x:v>
       </x:c>
       <x:c r="K13" s="26" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
       <x:c r="L13" s="26" t="n">
-        <x:v>0.2</x:v>
+        <x:v>0.3684210526315789</x:v>
       </x:c>
       <x:c r="M13" s="26" t="n">
-        <x:v>0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N13" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O13" s="27" t="n">
-        <x:v>0.42857142857142855</x:v>
-      </x:c>
+        <x:v>0.5714285714285714</x:v>
+      </x:c>
+      <x:c r="O13" s="26" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="P13" s="27"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="19" t="str">
         <x:v>网站总提交预审数</x:v>
       </x:c>
       <x:c r="B14" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D14" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E14" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F14" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G14" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I14" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J14" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K14" s="24" t="n">
         <x:v>0</x:v>
@@ -1060,9 +1130,10 @@
       <x:c r="N14" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O14" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="O14" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P14" s="25"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="19" t="str">
@@ -1107,9 +1178,10 @@
       <x:c r="N15" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O15" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="O15" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P15" s="25"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="19" t="str">
@@ -1121,54 +1193,41 @@
       <x:c r="C16" s="26" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="D16" s="26"/>
+      <x:c r="E16" s="26"/>
+      <x:c r="F16" s="26"/>
+      <x:c r="G16" s="26"/>
+      <x:c r="H16" s="26"/>
+      <x:c r="I16" s="26"/>
+      <x:c r="J16" s="26"/>
       <x:c r="K16" s="26"/>
       <x:c r="L16" s="26"/>
       <x:c r="M16" s="26"/>
       <x:c r="N16" s="26"/>
-      <x:c r="O16" s="27"/>
+      <x:c r="O16" s="26"/>
+      <x:c r="P16" s="27"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="19" t="str">
         <x:v>网站预审通过数</x:v>
       </x:c>
       <x:c r="B17" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C17" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C17" s="24" t="n">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="D17" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E17" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F17" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G17" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H17" s="24" t="n">
         <x:v>0</x:v>
@@ -1177,7 +1236,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J17" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K17" s="24" t="n">
         <x:v>0</x:v>
@@ -1191,9 +1250,10 @@
       <x:c r="N17" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O17" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="O17" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P17" s="25"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="19" t="str">
@@ -1238,40 +1298,32 @@
       <x:c r="N18" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O18" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="O18" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P18" s="25"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="19" t="str">
         <x:v>AI通过预审占比</x:v>
       </x:c>
-      <x:c r="B19" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="B19" s="26"/>
       <x:c r="C19" s="26" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D19" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E19" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="D19" s="26"/>
+      <x:c r="E19" s="26"/>
       <x:c r="F19" s="26"/>
-      <x:c r="G19" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="G19" s="26"/>
       <x:c r="H19" s="26"/>
       <x:c r="I19" s="26"/>
-      <x:c r="J19" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="J19" s="26"/>
       <x:c r="K19" s="26"/>
       <x:c r="L19" s="26"/>
       <x:c r="M19" s="26"/>
       <x:c r="N19" s="26"/>
-      <x:c r="O19" s="27"/>
+      <x:c r="O19" s="26"/>
+      <x:c r="P19" s="27"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1299,7 +1351,7 @@
         <x:v>统计周期</x:v>
       </x:c>
       <x:c r="B2" s="33" t="str">
-        <x:v>2026-07-13 至 2026-07-26</x:v>
+        <x:v>2026-07-20 至 2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="3">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="Reba4faccc9874934"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="R24cb07a42f83411e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="R21679d882d094f49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="R0551e810b5de4474"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -440,7 +440,6 @@
     <x:col min="13" max="13" width="13" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="13" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="13" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="13" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -486,11 +485,8 @@
       <x:c r="N1" s="22" t="n">
         <x:v>46235</x:v>
       </x:c>
-      <x:c r="O1" s="22" t="n">
+      <x:c r="O1" s="23" t="n">
         <x:v>46236</x:v>
-      </x:c>
-      <x:c r="P1" s="23" t="n">
-        <x:v>46237</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -536,11 +532,8 @@
       <x:c r="N2" s="24" t="n">
         <x:v>6231</x:v>
       </x:c>
-      <x:c r="O2" s="24" t="n">
+      <x:c r="O2" s="25" t="n">
         <x:v>6319</x:v>
-      </x:c>
-      <x:c r="P2" s="25" t="n">
-        <x:v>5508</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -586,11 +579,8 @@
       <x:c r="N3" s="24" t="n">
         <x:v>702</x:v>
       </x:c>
-      <x:c r="O3" s="24" t="n">
+      <x:c r="O3" s="25" t="n">
         <x:v>737</x:v>
-      </x:c>
-      <x:c r="P3" s="25" t="n">
-        <x:v>693</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -636,11 +626,8 @@
       <x:c r="N4" s="26" t="n">
         <x:v>0.11266249398170439</x:v>
       </x:c>
-      <x:c r="O4" s="26" t="n">
+      <x:c r="O4" s="27" t="n">
         <x:v>0.11663237854090837</x:v>
-      </x:c>
-      <x:c r="P4" s="27" t="n">
-        <x:v>0.12581699346405228</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -686,11 +673,8 @@
       <x:c r="N5" s="28" t="n">
         <x:v>1.485054347826087</x:v>
       </x:c>
-      <x:c r="O5" s="28" t="n">
+      <x:c r="O5" s="29" t="n">
         <x:v>1.490566037735849</x:v>
-      </x:c>
-      <x:c r="P5" s="29" t="n">
-        <x:v>1.4643962848297214</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -736,11 +720,8 @@
       <x:c r="N6" s="24" t="n">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="O6" s="24" t="n">
+      <x:c r="O6" s="25" t="n">
         <x:v>171</x:v>
-      </x:c>
-      <x:c r="P6" s="25" t="n">
-        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -786,11 +767,8 @@
       <x:c r="N7" s="26" t="n">
         <x:v>0.25783475783475784</x:v>
       </x:c>
-      <x:c r="O7" s="26" t="n">
+      <x:c r="O7" s="27" t="n">
         <x:v>0.23202170963364993</x:v>
-      </x:c>
-      <x:c r="P7" s="27" t="n">
-        <x:v>0.11688311688311688</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -836,11 +814,8 @@
       <x:c r="N8" s="24" t="n">
         <x:v>551</x:v>
       </x:c>
-      <x:c r="O8" s="24" t="n">
+      <x:c r="O8" s="25" t="n">
         <x:v>533</x:v>
-      </x:c>
-      <x:c r="P8" s="25" t="n">
-        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -886,11 +861,8 @@
       <x:c r="N9" s="24" t="n">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="O9" s="24" t="n">
+      <x:c r="O9" s="25" t="n">
         <x:v>131</x:v>
-      </x:c>
-      <x:c r="P9" s="25" t="n">
-        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -936,11 +908,8 @@
       <x:c r="N10" s="26" t="n">
         <x:v>0.2250453720508167</x:v>
       </x:c>
-      <x:c r="O10" s="26" t="n">
+      <x:c r="O10" s="27" t="n">
         <x:v>0.24577861163227016</x:v>
-      </x:c>
-      <x:c r="P10" s="27" t="n">
-        <x:v>0.22108843537414966</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -986,10 +955,9 @@
       <x:c r="N11" s="24" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="O11" s="24" t="n">
+      <x:c r="O11" s="25" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="P11" s="25"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="19" t="str">
@@ -1034,10 +1002,9 @@
       <x:c r="N12" s="24" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="O12" s="24" t="n">
+      <x:c r="O12" s="25" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P12" s="25"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="19" t="str">
@@ -1082,10 +1049,9 @@
       <x:c r="N13" s="26" t="n">
         <x:v>0.5714285714285714</x:v>
       </x:c>
-      <x:c r="O13" s="26" t="n">
+      <x:c r="O13" s="27" t="n">
         <x:v>0.6666666666666666</x:v>
       </x:c>
-      <x:c r="P13" s="27"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="19" t="str">
@@ -1130,10 +1096,9 @@
       <x:c r="N14" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O14" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P14" s="25"/>
+      <x:c r="O14" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="19" t="str">
@@ -1178,10 +1143,9 @@
       <x:c r="N15" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O15" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P15" s="25"/>
+      <x:c r="O15" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="19" t="str">
@@ -1204,8 +1168,7 @@
       <x:c r="L16" s="26"/>
       <x:c r="M16" s="26"/>
       <x:c r="N16" s="26"/>
-      <x:c r="O16" s="26"/>
-      <x:c r="P16" s="27"/>
+      <x:c r="O16" s="27"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="19" t="str">
@@ -1250,10 +1213,9 @@
       <x:c r="N17" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O17" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P17" s="25"/>
+      <x:c r="O17" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="19" t="str">
@@ -1298,10 +1260,9 @@
       <x:c r="N18" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P18" s="25"/>
+      <x:c r="O18" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="19" t="str">
@@ -1322,8 +1283,7 @@
       <x:c r="L19" s="26"/>
       <x:c r="M19" s="26"/>
       <x:c r="N19" s="26"/>
-      <x:c r="O19" s="26"/>
-      <x:c r="P19" s="27"/>
+      <x:c r="O19" s="27"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1351,7 +1311,7 @@
         <x:v>统计周期</x:v>
       </x:c>
       <x:c r="B2" s="33" t="str">
-        <x:v>2026-07-20 至 2026-08-03</x:v>
+        <x:v>2026-07-20 至 2026-08-02</x:v>
       </x:c>
     </x:row>
     <x:row r="3">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="R21679d882d094f49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="R0551e810b5de4474"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="R37a187cc20c248ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="Rf515b67c80a3466c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1058,46 +1058,46 @@
         <x:v>网站总提交预审数</x:v>
       </x:c>
       <x:c r="B14" s="24" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D14" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="n">
+      <x:c r="E14" s="24" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F14" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D14" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E14" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F14" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="G14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K14" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="O14" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1108,13 +1108,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F15" s="24" t="n">
         <x:v>0</x:v>
@@ -1126,7 +1126,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J15" s="24" t="n">
         <x:v>0</x:v>
@@ -1135,7 +1135,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M15" s="24" t="n">
         <x:v>0</x:v>
@@ -1155,20 +1155,42 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D16" s="26"/>
-      <x:c r="E16" s="26"/>
-      <x:c r="F16" s="26"/>
-      <x:c r="G16" s="26"/>
-      <x:c r="H16" s="26"/>
-      <x:c r="I16" s="26"/>
-      <x:c r="J16" s="26"/>
+        <x:v>0.14285714285714285</x:v>
+      </x:c>
+      <x:c r="D16" s="26" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="E16" s="26" t="n">
+        <x:v>0.36363636363636365</x:v>
+      </x:c>
+      <x:c r="F16" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I16" s="26" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="J16" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="K16" s="26"/>
-      <x:c r="L16" s="26"/>
-      <x:c r="M16" s="26"/>
-      <x:c r="N16" s="26"/>
-      <x:c r="O16" s="27"/>
+      <x:c r="L16" s="26" t="n">
+        <x:v>0.45454545454545453</x:v>
+      </x:c>
+      <x:c r="M16" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N16" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O16" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="19" t="str">
@@ -1178,43 +1200,43 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C17" s="24" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D17" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F17" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D17" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E17" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F17" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="H17" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J17" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K17" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L17" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="M17" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N17" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="O17" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1231,7 +1253,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E18" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F18" s="24" t="n">
         <x:v>0</x:v>
@@ -1243,7 +1265,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I18" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J18" s="24" t="n">
         <x:v>0</x:v>
@@ -1252,7 +1274,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L18" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M18" s="24" t="n">
         <x:v>0</x:v>
@@ -1273,17 +1295,31 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="26"/>
-      <x:c r="E19" s="26"/>
+      <x:c r="E19" s="26" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
       <x:c r="F19" s="26"/>
-      <x:c r="G19" s="26"/>
+      <x:c r="G19" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="H19" s="26"/>
-      <x:c r="I19" s="26"/>
-      <x:c r="J19" s="26"/>
+      <x:c r="I19" s="26" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="J19" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="K19" s="26"/>
-      <x:c r="L19" s="26"/>
+      <x:c r="L19" s="26" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
       <x:c r="M19" s="26"/>
-      <x:c r="N19" s="26"/>
-      <x:c r="O19" s="27"/>
+      <x:c r="N19" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O19" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="R37a187cc20c248ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="Rf515b67c80a3466c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="R7bcd1eaeeb604a67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="Re92ba231ff3242c0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -540,18 +540,10 @@
       <x:c r="A3" s="19" t="str">
         <x:v>使用AI用户数</x:v>
       </x:c>
-      <x:c r="B3" s="24" t="n">
-        <x:v>682</x:v>
-      </x:c>
-      <x:c r="C3" s="24" t="n">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="D3" s="24" t="n">
-        <x:v>633</x:v>
-      </x:c>
-      <x:c r="E3" s="24" t="n">
-        <x:v>615</x:v>
-      </x:c>
+      <x:c r="B3" s="24"/>
+      <x:c r="C3" s="24"/>
+      <x:c r="D3" s="24"/>
+      <x:c r="E3" s="24"/>
       <x:c r="F3" s="24" t="n">
         <x:v>618</x:v>
       </x:c>
@@ -587,18 +579,10 @@
       <x:c r="A4" s="19" t="str">
         <x:v>AI-UV渗透</x:v>
       </x:c>
-      <x:c r="B4" s="26" t="n">
-        <x:v>0.10696361355081556</x:v>
-      </x:c>
-      <x:c r="C4" s="26" t="n">
-        <x:v>0.10199335548172757</x:v>
-      </x:c>
-      <x:c r="D4" s="26" t="n">
-        <x:v>0.11219425735554768</x:v>
-      </x:c>
-      <x:c r="E4" s="26" t="n">
-        <x:v>0.10579735076552554</x:v>
-      </x:c>
+      <x:c r="B4" s="26"/>
+      <x:c r="C4" s="26"/>
+      <x:c r="D4" s="26"/>
+      <x:c r="E4" s="26"/>
       <x:c r="F4" s="26" t="n">
         <x:v>0.11391705069124423</x:v>
       </x:c>
@@ -634,27 +618,13 @@
       <x:c r="A5" s="19" t="str">
         <x:v>平均会话轮次</x:v>
       </x:c>
-      <x:c r="B5" s="28" t="n">
-        <x:v>1.392156862745098</x:v>
-      </x:c>
-      <x:c r="C5" s="28" t="n">
-        <x:v>1.4372294372294372</x:v>
-      </x:c>
-      <x:c r="D5" s="28" t="n">
-        <x:v>1.3585858585858586</x:v>
-      </x:c>
-      <x:c r="E5" s="28" t="n">
-        <x:v>1.390625</x:v>
-      </x:c>
-      <x:c r="F5" s="28" t="n">
-        <x:v>1.2634146341463415</x:v>
-      </x:c>
-      <x:c r="G5" s="28" t="n">
-        <x:v>1.4303977272727273</x:v>
-      </x:c>
-      <x:c r="H5" s="28" t="n">
-        <x:v>1.4630541871921183</x:v>
-      </x:c>
+      <x:c r="B5" s="28"/>
+      <x:c r="C5" s="28"/>
+      <x:c r="D5" s="28"/>
+      <x:c r="E5" s="28"/>
+      <x:c r="F5" s="28"/>
+      <x:c r="G5" s="28"/>
+      <x:c r="H5" s="28"/>
       <x:c r="I5" s="28" t="n">
         <x:v>1.288056206088993</x:v>
       </x:c>
@@ -668,7 +638,7 @@
         <x:v>1.4586070959264126</x:v>
       </x:c>
       <x:c r="M5" s="28" t="n">
-        <x:v>1.4132352941176471</x:v>
+        <x:v>1.3658536585365855</x:v>
       </x:c>
       <x:c r="N5" s="28" t="n">
         <x:v>1.485054347826087</x:v>
@@ -681,27 +651,13 @@
       <x:c r="A6" s="19" t="str">
         <x:v>2V2会话用户数</x:v>
       </x:c>
-      <x:c r="B6" s="24" t="n">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="C6" s="24" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D6" s="24" t="n">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="E6" s="24" t="n">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="F6" s="24" t="n">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="G6" s="24" t="n">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="H6" s="24" t="n">
-        <x:v>49</x:v>
-      </x:c>
+      <x:c r="B6" s="24"/>
+      <x:c r="C6" s="24"/>
+      <x:c r="D6" s="24"/>
+      <x:c r="E6" s="24"/>
+      <x:c r="F6" s="24"/>
+      <x:c r="G6" s="24"/>
+      <x:c r="H6" s="24"/>
       <x:c r="I6" s="24" t="n">
         <x:v>71</x:v>
       </x:c>
@@ -715,7 +671,7 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="M6" s="24" t="n">
-        <x:v>156</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N6" s="24" t="n">
         <x:v>181</x:v>
@@ -728,27 +684,13 @@
       <x:c r="A7" s="19" t="str">
         <x:v>2V2会话用户占比</x:v>
       </x:c>
-      <x:c r="B7" s="26" t="n">
-        <x:v>0.1744868035190616</x:v>
-      </x:c>
-      <x:c r="C7" s="26" t="n">
-        <x:v>0.0732899022801303</x:v>
-      </x:c>
-      <x:c r="D7" s="26" t="n">
-        <x:v>0.17535545023696683</x:v>
-      </x:c>
-      <x:c r="E7" s="26" t="n">
-        <x:v>0.21300813008130082</x:v>
-      </x:c>
-      <x:c r="F7" s="26" t="n">
-        <x:v>0.13592233009708737</x:v>
-      </x:c>
-      <x:c r="G7" s="26" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="H7" s="26" t="n">
-        <x:v>0.055745164960182024</x:v>
-      </x:c>
+      <x:c r="B7" s="26"/>
+      <x:c r="C7" s="26"/>
+      <x:c r="D7" s="26"/>
+      <x:c r="E7" s="26"/>
+      <x:c r="F7" s="26"/>
+      <x:c r="G7" s="26"/>
+      <x:c r="H7" s="26"/>
       <x:c r="I7" s="26" t="n">
         <x:v>0.09543010752688172</x:v>
       </x:c>
@@ -762,7 +704,7 @@
         <x:v>0.26132930513595165</x:v>
       </x:c>
       <x:c r="M7" s="26" t="n">
-        <x:v>0.20855614973262032</x:v>
+        <x:v>0.12433155080213903</x:v>
       </x:c>
       <x:c r="N7" s="26" t="n">
         <x:v>0.25783475783475784</x:v>
@@ -776,16 +718,16 @@
         <x:v>推荐产品卡片曝光数</x:v>
       </x:c>
       <x:c r="B8" s="24" t="n">
-        <x:v>196</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C8" s="24" t="n">
-        <x:v>362</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="24" t="n">
-        <x:v>323</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E8" s="24" t="n">
-        <x:v>341</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F8" s="24" t="n">
         <x:v>351</x:v>
@@ -823,16 +765,16 @@
         <x:v>推荐产品卡片点击数</x:v>
       </x:c>
       <x:c r="B9" s="24" t="n">
-        <x:v>59</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C9" s="24" t="n">
-        <x:v>88</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="24" t="n">
-        <x:v>74</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E9" s="24" t="n">
-        <x:v>83</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F9" s="24" t="n">
         <x:v>71</x:v>
@@ -869,18 +811,10 @@
       <x:c r="A10" s="19" t="str">
         <x:v>推荐产品CTR</x:v>
       </x:c>
-      <x:c r="B10" s="26" t="n">
-        <x:v>0.3010204081632653</x:v>
-      </x:c>
-      <x:c r="C10" s="26" t="n">
-        <x:v>0.2430939226519337</x:v>
-      </x:c>
-      <x:c r="D10" s="26" t="n">
-        <x:v>0.22910216718266255</x:v>
-      </x:c>
-      <x:c r="E10" s="26" t="n">
-        <x:v>0.2434017595307918</x:v>
-      </x:c>
+      <x:c r="B10" s="26"/>
+      <x:c r="C10" s="26"/>
+      <x:c r="D10" s="26"/>
+      <x:c r="E10" s="26"/>
       <x:c r="F10" s="26" t="n">
         <x:v>0.2022792022792023</x:v>
       </x:c>

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="R7bcd1eaeeb604a67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="Re92ba231ff3242c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="Rc46739f028e647c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="R79e7aceae125450e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="Rc46739f028e647c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="R79e7aceae125450e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="R2ed26c0cb3b34961"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="R6c97c8f9eb5b49c7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -440,6 +440,12 @@
     <x:col min="13" max="13" width="13" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="13" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="13" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="13" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="13" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="13" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="13" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="13" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="13" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -447,46 +453,64 @@
         <x:v>Date</x:v>
       </x:c>
       <x:c r="B1" s="22" t="n">
+        <x:v>46219</x:v>
+      </x:c>
+      <x:c r="C1" s="22" t="n">
+        <x:v>46221</x:v>
+      </x:c>
+      <x:c r="D1" s="22" t="n">
+        <x:v>46222</x:v>
+      </x:c>
+      <x:c r="E1" s="22" t="n">
         <x:v>46223</x:v>
       </x:c>
-      <x:c r="C1" s="22" t="n">
+      <x:c r="F1" s="22" t="n">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="D1" s="22" t="n">
+      <x:c r="G1" s="22" t="n">
         <x:v>46225</x:v>
       </x:c>
-      <x:c r="E1" s="22" t="n">
+      <x:c r="H1" s="22" t="n">
         <x:v>46226</x:v>
       </x:c>
-      <x:c r="F1" s="22" t="n">
+      <x:c r="I1" s="22" t="n">
         <x:v>46227</x:v>
       </x:c>
-      <x:c r="G1" s="22" t="n">
+      <x:c r="J1" s="22" t="n">
         <x:v>46228</x:v>
       </x:c>
-      <x:c r="H1" s="22" t="n">
+      <x:c r="K1" s="22" t="n">
         <x:v>46229</x:v>
       </x:c>
-      <x:c r="I1" s="22" t="n">
+      <x:c r="L1" s="22" t="n">
         <x:v>46230</x:v>
       </x:c>
-      <x:c r="J1" s="22" t="n">
+      <x:c r="M1" s="22" t="n">
         <x:v>46231</x:v>
       </x:c>
-      <x:c r="K1" s="22" t="n">
+      <x:c r="N1" s="22" t="n">
         <x:v>46232</x:v>
       </x:c>
-      <x:c r="L1" s="22" t="n">
+      <x:c r="O1" s="22" t="n">
         <x:v>46233</x:v>
       </x:c>
-      <x:c r="M1" s="22" t="n">
+      <x:c r="P1" s="22" t="n">
         <x:v>46234</x:v>
       </x:c>
-      <x:c r="N1" s="22" t="n">
+      <x:c r="Q1" s="22" t="n">
         <x:v>46235</x:v>
       </x:c>
-      <x:c r="O1" s="23" t="n">
+      <x:c r="R1" s="22" t="n">
         <x:v>46236</x:v>
+      </x:c>
+      <x:c r="S1" s="22" t="n">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="T1" s="22" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="U1" s="23" t="n">
+        <x:v>46239</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -494,46 +518,64 @@
         <x:v>网站整体用户数</x:v>
       </x:c>
       <x:c r="B2" s="24" t="n">
+        <x:v>5549</x:v>
+      </x:c>
+      <x:c r="C2" s="24" t="n">
+        <x:v>5656</x:v>
+      </x:c>
+      <x:c r="D2" s="24" t="n">
+        <x:v>6685</x:v>
+      </x:c>
+      <x:c r="E2" s="24" t="n">
         <x:v>6376</x:v>
       </x:c>
-      <x:c r="C2" s="24" t="n">
+      <x:c r="F2" s="24" t="n">
         <x:v>6020</x:v>
       </x:c>
-      <x:c r="D2" s="24" t="n">
+      <x:c r="G2" s="24" t="n">
         <x:v>5642</x:v>
       </x:c>
-      <x:c r="E2" s="24" t="n">
+      <x:c r="H2" s="24" t="n">
         <x:v>5813</x:v>
       </x:c>
-      <x:c r="F2" s="24" t="n">
+      <x:c r="I2" s="24" t="n">
         <x:v>5425</x:v>
       </x:c>
-      <x:c r="G2" s="24" t="n">
+      <x:c r="J2" s="24" t="n">
         <x:v>6001</x:v>
       </x:c>
-      <x:c r="H2" s="24" t="n">
+      <x:c r="K2" s="24" t="n">
         <x:v>7931</x:v>
       </x:c>
-      <x:c r="I2" s="24" t="n">
+      <x:c r="L2" s="24" t="n">
         <x:v>6688</x:v>
       </x:c>
-      <x:c r="J2" s="24" t="n">
+      <x:c r="M2" s="24" t="n">
         <x:v>5981</x:v>
       </x:c>
-      <x:c r="K2" s="24" t="n">
+      <x:c r="N2" s="24" t="n">
         <x:v>6542</x:v>
       </x:c>
-      <x:c r="L2" s="24" t="n">
+      <x:c r="O2" s="24" t="n">
         <x:v>5390</x:v>
       </x:c>
-      <x:c r="M2" s="24" t="n">
+      <x:c r="P2" s="24" t="n">
         <x:v>5797</x:v>
       </x:c>
-      <x:c r="N2" s="24" t="n">
+      <x:c r="Q2" s="24" t="n">
         <x:v>6231</x:v>
       </x:c>
-      <x:c r="O2" s="25" t="n">
+      <x:c r="R2" s="24" t="n">
         <x:v>6319</x:v>
+      </x:c>
+      <x:c r="S2" s="24" t="n">
+        <x:v>5955</x:v>
+      </x:c>
+      <x:c r="T2" s="24" t="n">
+        <x:v>6199</x:v>
+      </x:c>
+      <x:c r="U2" s="25" t="n">
+        <x:v>5549</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -544,35 +586,47 @@
       <x:c r="C3" s="24"/>
       <x:c r="D3" s="24"/>
       <x:c r="E3" s="24"/>
-      <x:c r="F3" s="24" t="n">
+      <x:c r="F3" s="24"/>
+      <x:c r="G3" s="24"/>
+      <x:c r="H3" s="24"/>
+      <x:c r="I3" s="24" t="n">
         <x:v>618</x:v>
       </x:c>
-      <x:c r="G3" s="24" t="n">
+      <x:c r="J3" s="24" t="n">
         <x:v>620</x:v>
       </x:c>
-      <x:c r="H3" s="24" t="n">
+      <x:c r="K3" s="24" t="n">
         <x:v>879</x:v>
       </x:c>
-      <x:c r="I3" s="24" t="n">
+      <x:c r="L3" s="24" t="n">
         <x:v>744</x:v>
       </x:c>
-      <x:c r="J3" s="24" t="n">
+      <x:c r="M3" s="24" t="n">
         <x:v>717</x:v>
       </x:c>
-      <x:c r="K3" s="24" t="n">
+      <x:c r="N3" s="24" t="n">
         <x:v>746</x:v>
       </x:c>
-      <x:c r="L3" s="24" t="n">
+      <x:c r="O3" s="24" t="n">
         <x:v>662</x:v>
       </x:c>
-      <x:c r="M3" s="24" t="n">
+      <x:c r="P3" s="24" t="n">
         <x:v>748</x:v>
       </x:c>
-      <x:c r="N3" s="24" t="n">
+      <x:c r="Q3" s="24" t="n">
         <x:v>702</x:v>
       </x:c>
-      <x:c r="O3" s="25" t="n">
+      <x:c r="R3" s="24" t="n">
         <x:v>737</x:v>
+      </x:c>
+      <x:c r="S3" s="24" t="n">
+        <x:v>753</x:v>
+      </x:c>
+      <x:c r="T3" s="24" t="n">
+        <x:v>769</x:v>
+      </x:c>
+      <x:c r="U3" s="25" t="n">
+        <x:v>682</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -583,35 +637,47 @@
       <x:c r="C4" s="26"/>
       <x:c r="D4" s="26"/>
       <x:c r="E4" s="26"/>
-      <x:c r="F4" s="26" t="n">
+      <x:c r="F4" s="26"/>
+      <x:c r="G4" s="26"/>
+      <x:c r="H4" s="26"/>
+      <x:c r="I4" s="26" t="n">
         <x:v>0.11391705069124423</x:v>
       </x:c>
-      <x:c r="G4" s="26" t="n">
+      <x:c r="J4" s="26" t="n">
         <x:v>0.10331611398100317</x:v>
       </x:c>
-      <x:c r="H4" s="26" t="n">
+      <x:c r="K4" s="26" t="n">
         <x:v>0.11083091665615938</x:v>
       </x:c>
-      <x:c r="I4" s="26" t="n">
+      <x:c r="L4" s="26" t="n">
         <x:v>0.11124401913875598</x:v>
       </x:c>
-      <x:c r="J4" s="26" t="n">
+      <x:c r="M4" s="26" t="n">
         <x:v>0.119879618792844</x:v>
       </x:c>
-      <x:c r="K4" s="26" t="n">
+      <x:c r="N4" s="26" t="n">
         <x:v>0.11403240599205136</x:v>
       </x:c>
-      <x:c r="L4" s="26" t="n">
+      <x:c r="O4" s="26" t="n">
         <x:v>0.12282003710575139</x:v>
       </x:c>
-      <x:c r="M4" s="26" t="n">
+      <x:c r="P4" s="26" t="n">
         <x:v>0.12903225806451613</x:v>
       </x:c>
-      <x:c r="N4" s="26" t="n">
+      <x:c r="Q4" s="26" t="n">
         <x:v>0.11266249398170439</x:v>
       </x:c>
-      <x:c r="O4" s="27" t="n">
+      <x:c r="R4" s="26" t="n">
         <x:v>0.11663237854090837</x:v>
+      </x:c>
+      <x:c r="S4" s="26" t="n">
+        <x:v>0.12644836272040302</x:v>
+      </x:c>
+      <x:c r="T4" s="26" t="n">
+        <x:v>0.1240522664945959</x:v>
+      </x:c>
+      <x:c r="U4" s="27" t="n">
+        <x:v>0.12290502793296089</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -625,26 +691,38 @@
       <x:c r="F5" s="28"/>
       <x:c r="G5" s="28"/>
       <x:c r="H5" s="28"/>
-      <x:c r="I5" s="28" t="n">
+      <x:c r="I5" s="28"/>
+      <x:c r="J5" s="28"/>
+      <x:c r="K5" s="28"/>
+      <x:c r="L5" s="28" t="n">
         <x:v>1.288056206088993</x:v>
       </x:c>
-      <x:c r="J5" s="28" t="n">
+      <x:c r="M5" s="28" t="n">
         <x:v>1.4005235602094241</x:v>
       </x:c>
-      <x:c r="K5" s="28" t="n">
+      <x:c r="N5" s="28" t="n">
         <x:v>1.4366998577524894</x:v>
       </x:c>
-      <x:c r="L5" s="28" t="n">
+      <x:c r="O5" s="28" t="n">
         <x:v>1.4586070959264126</x:v>
       </x:c>
-      <x:c r="M5" s="28" t="n">
+      <x:c r="P5" s="28" t="n">
         <x:v>1.3658536585365855</x:v>
       </x:c>
-      <x:c r="N5" s="28" t="n">
+      <x:c r="Q5" s="28" t="n">
         <x:v>1.485054347826087</x:v>
       </x:c>
-      <x:c r="O5" s="29" t="n">
+      <x:c r="R5" s="28" t="n">
         <x:v>1.490566037735849</x:v>
+      </x:c>
+      <x:c r="S5" s="28" t="n">
+        <x:v>1.3568215892053972</x:v>
+      </x:c>
+      <x:c r="T5" s="28" t="n">
+        <x:v>1.326478149100257</x:v>
+      </x:c>
+      <x:c r="U5" s="29" t="n">
+        <x:v>1.2588757396449703</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -658,26 +736,38 @@
       <x:c r="F6" s="24"/>
       <x:c r="G6" s="24"/>
       <x:c r="H6" s="24"/>
-      <x:c r="I6" s="24" t="n">
+      <x:c r="I6" s="24"/>
+      <x:c r="J6" s="24"/>
+      <x:c r="K6" s="24"/>
+      <x:c r="L6" s="24" t="n">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="J6" s="24" t="n">
+      <x:c r="M6" s="24" t="n">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="K6" s="24" t="n">
+      <x:c r="N6" s="24" t="n">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="L6" s="24" t="n">
+      <x:c r="O6" s="24" t="n">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="M6" s="24" t="n">
+      <x:c r="P6" s="24" t="n">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="N6" s="24" t="n">
+      <x:c r="Q6" s="24" t="n">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="O6" s="25" t="n">
+      <x:c r="R6" s="24" t="n">
         <x:v>171</x:v>
+      </x:c>
+      <x:c r="S6" s="24" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="T6" s="24" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="U6" s="25" t="n">
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -691,26 +781,38 @@
       <x:c r="F7" s="26"/>
       <x:c r="G7" s="26"/>
       <x:c r="H7" s="26"/>
-      <x:c r="I7" s="26" t="n">
+      <x:c r="I7" s="26"/>
+      <x:c r="J7" s="26"/>
+      <x:c r="K7" s="26"/>
+      <x:c r="L7" s="26" t="n">
         <x:v>0.09543010752688172</x:v>
       </x:c>
-      <x:c r="J7" s="26" t="n">
+      <x:c r="M7" s="26" t="n">
         <x:v>0.21478382147838215</x:v>
       </x:c>
-      <x:c r="K7" s="26" t="n">
+      <x:c r="N7" s="26" t="n">
         <x:v>0.21045576407506703</x:v>
       </x:c>
-      <x:c r="L7" s="26" t="n">
+      <x:c r="O7" s="26" t="n">
         <x:v>0.26132930513595165</x:v>
       </x:c>
-      <x:c r="M7" s="26" t="n">
+      <x:c r="P7" s="26" t="n">
         <x:v>0.12433155080213903</x:v>
       </x:c>
-      <x:c r="N7" s="26" t="n">
+      <x:c r="Q7" s="26" t="n">
         <x:v>0.25783475783475784</x:v>
       </x:c>
-      <x:c r="O7" s="27" t="n">
+      <x:c r="R7" s="26" t="n">
         <x:v>0.23202170963364993</x:v>
+      </x:c>
+      <x:c r="S7" s="26" t="n">
+        <x:v>0.17264276228419656</x:v>
+      </x:c>
+      <x:c r="T7" s="26" t="n">
+        <x:v>0.1755526657997399</x:v>
+      </x:c>
+      <x:c r="U7" s="27" t="n">
+        <x:v>0.15542521994134897</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -730,34 +832,52 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F8" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I8" s="24" t="n">
         <x:v>351</x:v>
       </x:c>
-      <x:c r="G8" s="24" t="n">
+      <x:c r="J8" s="24" t="n">
         <x:v>459</x:v>
       </x:c>
-      <x:c r="H8" s="24" t="n">
+      <x:c r="K8" s="24" t="n">
         <x:v>619</x:v>
       </x:c>
-      <x:c r="I8" s="24" t="n">
+      <x:c r="L8" s="24" t="n">
         <x:v>515</x:v>
       </x:c>
-      <x:c r="J8" s="24" t="n">
+      <x:c r="M8" s="24" t="n">
         <x:v>539</x:v>
       </x:c>
-      <x:c r="K8" s="24" t="n">
+      <x:c r="N8" s="24" t="n">
         <x:v>546</x:v>
       </x:c>
-      <x:c r="L8" s="24" t="n">
+      <x:c r="O8" s="24" t="n">
         <x:v>492</x:v>
       </x:c>
-      <x:c r="M8" s="24" t="n">
+      <x:c r="P8" s="24" t="n">
         <x:v>481</x:v>
       </x:c>
-      <x:c r="N8" s="24" t="n">
+      <x:c r="Q8" s="24" t="n">
         <x:v>551</x:v>
       </x:c>
-      <x:c r="O8" s="25" t="n">
+      <x:c r="R8" s="24" t="n">
         <x:v>533</x:v>
+      </x:c>
+      <x:c r="S8" s="24" t="n">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="T8" s="24" t="n">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="U8" s="25" t="n">
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -777,34 +897,52 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F9" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I9" s="24" t="n">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G9" s="24" t="n">
+      <x:c r="J9" s="24" t="n">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="H9" s="24" t="n">
+      <x:c r="K9" s="24" t="n">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="I9" s="24" t="n">
+      <x:c r="L9" s="24" t="n">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="J9" s="24" t="n">
+      <x:c r="M9" s="24" t="n">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="K9" s="24" t="n">
+      <x:c r="N9" s="24" t="n">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="L9" s="24" t="n">
+      <x:c r="O9" s="24" t="n">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="M9" s="24" t="n">
+      <x:c r="P9" s="24" t="n">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="N9" s="24" t="n">
+      <x:c r="Q9" s="24" t="n">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="O9" s="25" t="n">
+      <x:c r="R9" s="24" t="n">
         <x:v>131</x:v>
+      </x:c>
+      <x:c r="S9" s="24" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="T9" s="24" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="U9" s="25" t="n">
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -815,35 +953,47 @@
       <x:c r="C10" s="26"/>
       <x:c r="D10" s="26"/>
       <x:c r="E10" s="26"/>
-      <x:c r="F10" s="26" t="n">
+      <x:c r="F10" s="26"/>
+      <x:c r="G10" s="26"/>
+      <x:c r="H10" s="26"/>
+      <x:c r="I10" s="26" t="n">
         <x:v>0.2022792022792023</x:v>
       </x:c>
-      <x:c r="G10" s="26" t="n">
+      <x:c r="J10" s="26" t="n">
         <x:v>0.2374727668845316</x:v>
       </x:c>
-      <x:c r="H10" s="26" t="n">
+      <x:c r="K10" s="26" t="n">
         <x:v>0.22132471728594508</x:v>
       </x:c>
-      <x:c r="I10" s="26" t="n">
+      <x:c r="L10" s="26" t="n">
         <x:v>0.21359223300970873</x:v>
       </x:c>
-      <x:c r="J10" s="26" t="n">
+      <x:c r="M10" s="26" t="n">
         <x:v>0.22077922077922077</x:v>
       </x:c>
-      <x:c r="K10" s="26" t="n">
+      <x:c r="N10" s="26" t="n">
         <x:v>0.25824175824175827</x:v>
       </x:c>
-      <x:c r="L10" s="26" t="n">
+      <x:c r="O10" s="26" t="n">
         <x:v>0.2540650406504065</x:v>
       </x:c>
-      <x:c r="M10" s="26" t="n">
+      <x:c r="P10" s="26" t="n">
         <x:v>0.2286902286902287</x:v>
       </x:c>
-      <x:c r="N10" s="26" t="n">
+      <x:c r="Q10" s="26" t="n">
         <x:v>0.2250453720508167</x:v>
       </x:c>
-      <x:c r="O10" s="27" t="n">
+      <x:c r="R10" s="26" t="n">
         <x:v>0.24577861163227016</x:v>
+      </x:c>
+      <x:c r="S10" s="26" t="n">
+        <x:v>0.237012987012987</x:v>
+      </x:c>
+      <x:c r="T10" s="26" t="n">
+        <x:v>0.25524475524475526</x:v>
+      </x:c>
+      <x:c r="U10" s="27" t="n">
+        <x:v>0.19834710743801653</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -851,46 +1001,64 @@
         <x:v>网站总线索数</x:v>
       </x:c>
       <x:c r="B11" s="24" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C11" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D11" s="24" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E11" s="24" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F11" s="24" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G11" s="24" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H11" s="24" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F11" s="24" t="n">
+      <x:c r="I11" s="24" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G11" s="24" t="n">
+      <x:c r="J11" s="24" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H11" s="24" t="n">
+      <x:c r="K11" s="24" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I11" s="24" t="n">
+      <x:c r="L11" s="24" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="J11" s="24" t="n">
+      <x:c r="M11" s="24" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K11" s="24" t="n">
+      <x:c r="N11" s="24" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L11" s="24" t="n">
+      <x:c r="O11" s="24" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="M11" s="24" t="n">
+      <x:c r="P11" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N11" s="24" t="n">
+      <x:c r="Q11" s="24" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="O11" s="25" t="n">
+      <x:c r="R11" s="24" t="n">
         <x:v>6</x:v>
+      </x:c>
+      <x:c r="S11" s="24" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="T11" s="24" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="U11" s="25" t="n">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -901,43 +1069,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D12" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E12" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G12" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H12" s="24" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F12" s="24" t="n">
+      <x:c r="I12" s="24" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G12" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H12" s="24" t="n">
+      <x:c r="J12" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K12" s="24" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I12" s="24" t="n">
+      <x:c r="L12" s="24" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J12" s="24" t="n">
+      <x:c r="M12" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K12" s="24" t="n">
+      <x:c r="N12" s="24" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L12" s="24" t="n">
+      <x:c r="O12" s="24" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="M12" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N12" s="24" t="n">
+      <x:c r="P12" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q12" s="24" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="O12" s="25" t="n">
+      <x:c r="R12" s="24" t="n">
         <x:v>4</x:v>
+      </x:c>
+      <x:c r="S12" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="T12" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="U12" s="25" t="n">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -948,43 +1134,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C13" s="26" t="n">
-        <x:v>0.14285714285714285</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="D13" s="26" t="n">
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="E13" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="26" t="n">
+        <x:v>0.14285714285714285</x:v>
+      </x:c>
+      <x:c r="G13" s="26" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="H13" s="26" t="n">
         <x:v>0.5333333333333333</x:v>
       </x:c>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="I13" s="26" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="G13" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H13" s="26" t="n">
+      <x:c r="J13" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="26" t="n">
         <x:v>0.42857142857142855</x:v>
       </x:c>
-      <x:c r="I13" s="26" t="n">
+      <x:c r="L13" s="26" t="n">
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="J13" s="26" t="n">
+      <x:c r="M13" s="26" t="n">
         <x:v>0.18181818181818182</x:v>
       </x:c>
-      <x:c r="K13" s="26" t="n">
+      <x:c r="N13" s="26" t="n">
         <x:v>0.6666666666666666</x:v>
       </x:c>
-      <x:c r="L13" s="26" t="n">
+      <x:c r="O13" s="26" t="n">
         <x:v>0.3684210526315789</x:v>
       </x:c>
-      <x:c r="M13" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="26" t="n">
+      <x:c r="P13" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q13" s="26" t="n">
         <x:v>0.5714285714285714</x:v>
       </x:c>
-      <x:c r="O13" s="27" t="n">
+      <x:c r="R13" s="26" t="n">
         <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="S13" s="26" t="n">
+        <x:v>0.23076923076923078</x:v>
+      </x:c>
+      <x:c r="T13" s="26" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
+      <x:c r="U13" s="27" t="n">
+        <x:v>0.3684210526315789</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -995,43 +1199,61 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D14" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E14" s="24" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F14" s="24" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G14" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H14" s="24" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="F14" s="24" t="n">
+      <x:c r="I14" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G14" s="24" t="n">
+      <x:c r="J14" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H14" s="24" t="n">
+      <x:c r="K14" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I14" s="24" t="n">
+      <x:c r="L14" s="24" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J14" s="24" t="n">
+      <x:c r="M14" s="24" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K14" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L14" s="24" t="n">
+      <x:c r="N14" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O14" s="24" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M14" s="24" t="n">
+      <x:c r="P14" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N14" s="24" t="n">
+      <x:c r="Q14" s="24" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="O14" s="25" t="n">
+      <x:c r="R14" s="24" t="n">
         <x:v>2</x:v>
+      </x:c>
+      <x:c r="S14" s="24" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="T14" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U14" s="25" t="n">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1042,43 +1264,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D15" s="24" t="n">
+      <x:c r="G15" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E15" s="24" t="n">
+      <x:c r="H15" s="24" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F15" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H15" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="I15" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J15" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L15" s="24" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J15" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K15" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L15" s="24" t="n">
+      <x:c r="M15" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O15" s="24" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="M15" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O15" s="25" t="n">
-        <x:v>0</x:v>
+      <x:c r="P15" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q15" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R15" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S15" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T15" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="U15" s="25" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1089,41 +1329,59 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C16" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="26" t="n">
         <x:v>0.14285714285714285</x:v>
       </x:c>
-      <x:c r="D16" s="26" t="n">
+      <x:c r="G16" s="26" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="E16" s="26" t="n">
+      <x:c r="H16" s="26" t="n">
         <x:v>0.36363636363636365</x:v>
       </x:c>
-      <x:c r="F16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="I16" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J16" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L16" s="26" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="J16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K16" s="26"/>
-      <x:c r="L16" s="26" t="n">
+      <x:c r="M16" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N16" s="26"/>
+      <x:c r="O16" s="26" t="n">
         <x:v>0.45454545454545453</x:v>
       </x:c>
-      <x:c r="M16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O16" s="27" t="n">
-        <x:v>0</x:v>
+      <x:c r="P16" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q16" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R16" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S16" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T16" s="26" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="U16" s="27" t="n">
+        <x:v>0.2857142857142857</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1131,28 +1389,28 @@
         <x:v>网站预审通过数</x:v>
       </x:c>
       <x:c r="B17" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C17" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D17" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="24" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D17" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E17" s="24" t="n">
+      <x:c r="G17" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="24" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F17" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="I17" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J17" s="24" t="n">
         <x:v>1</x:v>
@@ -1161,16 +1419,34 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L17" s="24" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M17" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N17" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O17" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="M17" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="24" t="n">
+      <x:c r="P17" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q17" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O17" s="25" t="n">
+      <x:c r="R17" s="24" t="n">
         <x:v>2</x:v>
+      </x:c>
+      <x:c r="S17" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T17" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="U17" s="25" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1187,36 +1463,54 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E18" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F18" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G18" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="I18" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K18" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L18" s="24" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L18" s="24" t="n">
+      <x:c r="M18" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N18" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O18" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O18" s="25" t="n">
+      <x:c r="P18" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q18" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R18" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S18" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T18" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="U18" s="25" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1224,36 +1518,50 @@
       <x:c r="A19" s="19" t="str">
         <x:v>AI通过预审占比</x:v>
       </x:c>
-      <x:c r="B19" s="26"/>
+      <x:c r="B19" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="C19" s="26" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="26"/>
-      <x:c r="E19" s="26" t="n">
+      <x:c r="E19" s="26"/>
+      <x:c r="F19" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" s="26"/>
+      <x:c r="H19" s="26" t="n">
         <x:v>0.6666666666666666</x:v>
       </x:c>
-      <x:c r="F19" s="26"/>
-      <x:c r="G19" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H19" s="26"/>
-      <x:c r="I19" s="26" t="n">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="I19" s="26"/>
       <x:c r="J19" s="26" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K19" s="26"/>
       <x:c r="L19" s="26" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="M19" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N19" s="26"/>
+      <x:c r="O19" s="26" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="M19" s="26"/>
-      <x:c r="N19" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O19" s="27" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="P19" s="26"/>
+      <x:c r="Q19" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R19" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S19" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T19" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U19" s="27"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1281,7 +1589,7 @@
         <x:v>统计周期</x:v>
       </x:c>
       <x:c r="B2" s="33" t="str">
-        <x:v>2026-07-20 至 2026-08-02</x:v>
+        <x:v>2026-07-16 至 2026-08-05</x:v>
       </x:c>
     </x:row>
     <x:row r="3">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="R2ed26c0cb3b34961"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="R6c97c8f9eb5b49c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="R0216e98f62094028"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="Reb2aab075b0f4e0b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -440,12 +440,6 @@
     <x:col min="13" max="13" width="13" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="13" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="13" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="13" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="13" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="13" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="13" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="13" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="13" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -453,64 +447,46 @@
         <x:v>Date</x:v>
       </x:c>
       <x:c r="B1" s="22" t="n">
-        <x:v>46219</x:v>
+        <x:v>46230</x:v>
       </x:c>
       <x:c r="C1" s="22" t="n">
-        <x:v>46221</x:v>
+        <x:v>46231</x:v>
       </x:c>
       <x:c r="D1" s="22" t="n">
-        <x:v>46222</x:v>
+        <x:v>46232</x:v>
       </x:c>
       <x:c r="E1" s="22" t="n">
-        <x:v>46223</x:v>
+        <x:v>46233</x:v>
       </x:c>
       <x:c r="F1" s="22" t="n">
-        <x:v>46224</x:v>
+        <x:v>46234</x:v>
       </x:c>
       <x:c r="G1" s="22" t="n">
-        <x:v>46225</x:v>
+        <x:v>46235</x:v>
       </x:c>
       <x:c r="H1" s="22" t="n">
-        <x:v>46226</x:v>
+        <x:v>46236</x:v>
       </x:c>
       <x:c r="I1" s="22" t="n">
-        <x:v>46227</x:v>
+        <x:v>46237</x:v>
       </x:c>
       <x:c r="J1" s="22" t="n">
-        <x:v>46228</x:v>
+        <x:v>46238</x:v>
       </x:c>
       <x:c r="K1" s="22" t="n">
-        <x:v>46229</x:v>
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L1" s="22" t="n">
-        <x:v>46230</x:v>
+        <x:v>46240</x:v>
       </x:c>
       <x:c r="M1" s="22" t="n">
-        <x:v>46231</x:v>
+        <x:v>46241</x:v>
       </x:c>
       <x:c r="N1" s="22" t="n">
-        <x:v>46232</x:v>
-      </x:c>
-      <x:c r="O1" s="22" t="n">
-        <x:v>46233</x:v>
-      </x:c>
-      <x:c r="P1" s="22" t="n">
-        <x:v>46234</x:v>
-      </x:c>
-      <x:c r="Q1" s="22" t="n">
-        <x:v>46235</x:v>
-      </x:c>
-      <x:c r="R1" s="22" t="n">
-        <x:v>46236</x:v>
-      </x:c>
-      <x:c r="S1" s="22" t="n">
-        <x:v>46237</x:v>
-      </x:c>
-      <x:c r="T1" s="22" t="n">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="U1" s="23" t="n">
-        <x:v>46239</x:v>
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="O1" s="23" t="n">
+        <x:v>46243</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -518,301 +494,281 @@
         <x:v>网站整体用户数</x:v>
       </x:c>
       <x:c r="B2" s="24" t="n">
+        <x:v>6688</x:v>
+      </x:c>
+      <x:c r="C2" s="24" t="n">
+        <x:v>5981</x:v>
+      </x:c>
+      <x:c r="D2" s="24" t="n">
+        <x:v>6542</x:v>
+      </x:c>
+      <x:c r="E2" s="24" t="n">
+        <x:v>5390</x:v>
+      </x:c>
+      <x:c r="F2" s="24" t="n">
+        <x:v>5797</x:v>
+      </x:c>
+      <x:c r="G2" s="24" t="n">
+        <x:v>6231</x:v>
+      </x:c>
+      <x:c r="H2" s="24" t="n">
+        <x:v>6319</x:v>
+      </x:c>
+      <x:c r="I2" s="24" t="n">
+        <x:v>5955</x:v>
+      </x:c>
+      <x:c r="J2" s="24" t="n">
+        <x:v>6199</x:v>
+      </x:c>
+      <x:c r="K2" s="24" t="n">
         <x:v>5549</x:v>
       </x:c>
-      <x:c r="C2" s="24" t="n">
-        <x:v>5656</x:v>
-      </x:c>
-      <x:c r="D2" s="24" t="n">
-        <x:v>6685</x:v>
-      </x:c>
-      <x:c r="E2" s="24" t="n">
-        <x:v>6376</x:v>
-      </x:c>
-      <x:c r="F2" s="24" t="n">
-        <x:v>6020</x:v>
-      </x:c>
-      <x:c r="G2" s="24" t="n">
-        <x:v>5642</x:v>
-      </x:c>
-      <x:c r="H2" s="24" t="n">
-        <x:v>5813</x:v>
-      </x:c>
-      <x:c r="I2" s="24" t="n">
-        <x:v>5425</x:v>
-      </x:c>
-      <x:c r="J2" s="24" t="n">
-        <x:v>6001</x:v>
-      </x:c>
-      <x:c r="K2" s="24" t="n">
-        <x:v>7931</x:v>
-      </x:c>
       <x:c r="L2" s="24" t="n">
-        <x:v>6688</x:v>
+        <x:v>4499</x:v>
       </x:c>
       <x:c r="M2" s="24" t="n">
-        <x:v>5981</x:v>
+        <x:v>4467</x:v>
       </x:c>
       <x:c r="N2" s="24" t="n">
-        <x:v>6542</x:v>
-      </x:c>
-      <x:c r="O2" s="24" t="n">
-        <x:v>5390</x:v>
-      </x:c>
-      <x:c r="P2" s="24" t="n">
-        <x:v>5797</x:v>
-      </x:c>
-      <x:c r="Q2" s="24" t="n">
-        <x:v>6231</x:v>
-      </x:c>
-      <x:c r="R2" s="24" t="n">
-        <x:v>6319</x:v>
-      </x:c>
-      <x:c r="S2" s="24" t="n">
-        <x:v>5955</x:v>
-      </x:c>
-      <x:c r="T2" s="24" t="n">
-        <x:v>6199</x:v>
-      </x:c>
-      <x:c r="U2" s="25" t="n">
-        <x:v>5549</x:v>
+        <x:v>4961</x:v>
+      </x:c>
+      <x:c r="O2" s="25" t="n">
+        <x:v>5079</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="19" t="str">
         <x:v>使用AI用户数</x:v>
       </x:c>
-      <x:c r="B3" s="24"/>
-      <x:c r="C3" s="24"/>
-      <x:c r="D3" s="24"/>
-      <x:c r="E3" s="24"/>
-      <x:c r="F3" s="24"/>
-      <x:c r="G3" s="24"/>
-      <x:c r="H3" s="24"/>
+      <x:c r="B3" s="24" t="n">
+        <x:v>744</x:v>
+      </x:c>
+      <x:c r="C3" s="24" t="n">
+        <x:v>717</x:v>
+      </x:c>
+      <x:c r="D3" s="24" t="n">
+        <x:v>746</x:v>
+      </x:c>
+      <x:c r="E3" s="24" t="n">
+        <x:v>662</x:v>
+      </x:c>
+      <x:c r="F3" s="24" t="n">
+        <x:v>748</x:v>
+      </x:c>
+      <x:c r="G3" s="24" t="n">
+        <x:v>702</x:v>
+      </x:c>
+      <x:c r="H3" s="24" t="n">
+        <x:v>737</x:v>
+      </x:c>
       <x:c r="I3" s="24" t="n">
-        <x:v>618</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="J3" s="24" t="n">
-        <x:v>620</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="K3" s="24" t="n">
-        <x:v>879</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="L3" s="24" t="n">
-        <x:v>744</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="M3" s="24" t="n">
-        <x:v>717</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="N3" s="24" t="n">
-        <x:v>746</x:v>
-      </x:c>
-      <x:c r="O3" s="24" t="n">
-        <x:v>662</x:v>
-      </x:c>
-      <x:c r="P3" s="24" t="n">
-        <x:v>748</x:v>
-      </x:c>
-      <x:c r="Q3" s="24" t="n">
-        <x:v>702</x:v>
-      </x:c>
-      <x:c r="R3" s="24" t="n">
-        <x:v>737</x:v>
-      </x:c>
-      <x:c r="S3" s="24" t="n">
-        <x:v>753</x:v>
-      </x:c>
-      <x:c r="T3" s="24" t="n">
-        <x:v>769</x:v>
-      </x:c>
-      <x:c r="U3" s="25" t="n">
-        <x:v>682</x:v>
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="O3" s="25" t="n">
+        <x:v>603</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="19" t="str">
         <x:v>AI-UV渗透</x:v>
       </x:c>
-      <x:c r="B4" s="26"/>
-      <x:c r="C4" s="26"/>
-      <x:c r="D4" s="26"/>
-      <x:c r="E4" s="26"/>
-      <x:c r="F4" s="26"/>
-      <x:c r="G4" s="26"/>
-      <x:c r="H4" s="26"/>
+      <x:c r="B4" s="26" t="n">
+        <x:v>0.11124401913875598</x:v>
+      </x:c>
+      <x:c r="C4" s="26" t="n">
+        <x:v>0.119879618792844</x:v>
+      </x:c>
+      <x:c r="D4" s="26" t="n">
+        <x:v>0.11403240599205136</x:v>
+      </x:c>
+      <x:c r="E4" s="26" t="n">
+        <x:v>0.12282003710575139</x:v>
+      </x:c>
+      <x:c r="F4" s="26" t="n">
+        <x:v>0.12903225806451613</x:v>
+      </x:c>
+      <x:c r="G4" s="26" t="n">
+        <x:v>0.11266249398170439</x:v>
+      </x:c>
+      <x:c r="H4" s="26" t="n">
+        <x:v>0.11663237854090837</x:v>
+      </x:c>
       <x:c r="I4" s="26" t="n">
-        <x:v>0.11391705069124423</x:v>
+        <x:v>0.12644836272040302</x:v>
       </x:c>
       <x:c r="J4" s="26" t="n">
-        <x:v>0.10331611398100317</x:v>
+        <x:v>0.1240522664945959</x:v>
       </x:c>
       <x:c r="K4" s="26" t="n">
-        <x:v>0.11083091665615938</x:v>
+        <x:v>0.12290502793296089</x:v>
       </x:c>
       <x:c r="L4" s="26" t="n">
-        <x:v>0.11124401913875598</x:v>
+        <x:v>0.13380751278061792</x:v>
       </x:c>
       <x:c r="M4" s="26" t="n">
-        <x:v>0.119879618792844</x:v>
+        <x:v>0.12536377882247593</x:v>
       </x:c>
       <x:c r="N4" s="26" t="n">
-        <x:v>0.11403240599205136</x:v>
-      </x:c>
-      <x:c r="O4" s="26" t="n">
-        <x:v>0.12282003710575139</x:v>
-      </x:c>
-      <x:c r="P4" s="26" t="n">
-        <x:v>0.12903225806451613</x:v>
-      </x:c>
-      <x:c r="Q4" s="26" t="n">
-        <x:v>0.11266249398170439</x:v>
-      </x:c>
-      <x:c r="R4" s="26" t="n">
-        <x:v>0.11663237854090837</x:v>
-      </x:c>
-      <x:c r="S4" s="26" t="n">
-        <x:v>0.12644836272040302</x:v>
-      </x:c>
-      <x:c r="T4" s="26" t="n">
-        <x:v>0.1240522664945959</x:v>
-      </x:c>
-      <x:c r="U4" s="27" t="n">
-        <x:v>0.12290502793296089</x:v>
+        <x:v>0.11449304575690385</x:v>
+      </x:c>
+      <x:c r="O4" s="27" t="n">
+        <x:v>0.11872415829887774</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="19" t="str">
         <x:v>平均会话轮次</x:v>
       </x:c>
-      <x:c r="B5" s="28"/>
-      <x:c r="C5" s="28"/>
-      <x:c r="D5" s="28"/>
-      <x:c r="E5" s="28"/>
-      <x:c r="F5" s="28"/>
-      <x:c r="G5" s="28"/>
-      <x:c r="H5" s="28"/>
-      <x:c r="I5" s="28"/>
-      <x:c r="J5" s="28"/>
-      <x:c r="K5" s="28"/>
+      <x:c r="B5" s="28" t="n">
+        <x:v>1.288056206088993</x:v>
+      </x:c>
+      <x:c r="C5" s="28" t="n">
+        <x:v>1.4005235602094241</x:v>
+      </x:c>
+      <x:c r="D5" s="28" t="n">
+        <x:v>1.4366998577524894</x:v>
+      </x:c>
+      <x:c r="E5" s="28" t="n">
+        <x:v>1.4586070959264126</x:v>
+      </x:c>
+      <x:c r="F5" s="28" t="n">
+        <x:v>1.4132352941176471</x:v>
+      </x:c>
+      <x:c r="G5" s="28" t="n">
+        <x:v>1.485054347826087</x:v>
+      </x:c>
+      <x:c r="H5" s="28" t="n">
+        <x:v>1.458937198067633</x:v>
+      </x:c>
+      <x:c r="I5" s="28" t="n">
+        <x:v>1.3568215892053972</x:v>
+      </x:c>
+      <x:c r="J5" s="28" t="n">
+        <x:v>1.326478149100257</x:v>
+      </x:c>
+      <x:c r="K5" s="28" t="n">
+        <x:v>1.2588757396449703</x:v>
+      </x:c>
       <x:c r="L5" s="28" t="n">
-        <x:v>1.288056206088993</x:v>
+        <x:v>1.3190298507462686</x:v>
       </x:c>
       <x:c r="M5" s="28" t="n">
-        <x:v>1.4005235602094241</x:v>
+        <x:v>1.284965034965035</x:v>
       </x:c>
       <x:c r="N5" s="28" t="n">
-        <x:v>1.4366998577524894</x:v>
-      </x:c>
-      <x:c r="O5" s="28" t="n">
-        <x:v>1.4586070959264126</x:v>
-      </x:c>
-      <x:c r="P5" s="28" t="n">
-        <x:v>1.3658536585365855</x:v>
-      </x:c>
-      <x:c r="Q5" s="28" t="n">
-        <x:v>1.485054347826087</x:v>
-      </x:c>
-      <x:c r="R5" s="28" t="n">
-        <x:v>1.490566037735849</x:v>
-      </x:c>
-      <x:c r="S5" s="28" t="n">
-        <x:v>1.3568215892053972</x:v>
-      </x:c>
-      <x:c r="T5" s="28" t="n">
-        <x:v>1.326478149100257</x:v>
-      </x:c>
-      <x:c r="U5" s="29" t="n">
-        <x:v>1.2588757396449703</x:v>
+        <x:v>1.4908759124087592</x:v>
+      </x:c>
+      <x:c r="O5" s="29" t="n">
+        <x:v>1.544502617801047</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="19" t="str">
         <x:v>2V2会话用户数</x:v>
       </x:c>
-      <x:c r="B6" s="24"/>
-      <x:c r="C6" s="24"/>
-      <x:c r="D6" s="24"/>
-      <x:c r="E6" s="24"/>
-      <x:c r="F6" s="24"/>
-      <x:c r="G6" s="24"/>
-      <x:c r="H6" s="24"/>
-      <x:c r="I6" s="24"/>
-      <x:c r="J6" s="24"/>
-      <x:c r="K6" s="24"/>
+      <x:c r="B6" s="24" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C6" s="24" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D6" s="24" t="n">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="E6" s="24" t="n">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="F6" s="24" t="n">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="G6" s="24" t="n">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="H6" s="24" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="I6" s="24" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="J6" s="24" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="K6" s="24" t="n">
+        <x:v>106</x:v>
+      </x:c>
       <x:c r="L6" s="24" t="n">
-        <x:v>71</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="M6" s="24" t="n">
-        <x:v>154</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="N6" s="24" t="n">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="O6" s="24" t="n">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="P6" s="24" t="n">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="Q6" s="24" t="n">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="R6" s="24" t="n">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="S6" s="24" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="T6" s="24" t="n">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="U6" s="25" t="n">
-        <x:v>106</x:v>
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="O6" s="25" t="n">
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="19" t="str">
         <x:v>2V2会话用户占比</x:v>
       </x:c>
-      <x:c r="B7" s="26"/>
-      <x:c r="C7" s="26"/>
-      <x:c r="D7" s="26"/>
-      <x:c r="E7" s="26"/>
-      <x:c r="F7" s="26"/>
-      <x:c r="G7" s="26"/>
-      <x:c r="H7" s="26"/>
-      <x:c r="I7" s="26"/>
-      <x:c r="J7" s="26"/>
-      <x:c r="K7" s="26"/>
+      <x:c r="B7" s="26" t="n">
+        <x:v>0.09543010752688172</x:v>
+      </x:c>
+      <x:c r="C7" s="26" t="n">
+        <x:v>0.21478382147838215</x:v>
+      </x:c>
+      <x:c r="D7" s="26" t="n">
+        <x:v>0.21045576407506703</x:v>
+      </x:c>
+      <x:c r="E7" s="26" t="n">
+        <x:v>0.26132930513595165</x:v>
+      </x:c>
+      <x:c r="F7" s="26" t="n">
+        <x:v>0.20855614973262032</x:v>
+      </x:c>
+      <x:c r="G7" s="26" t="n">
+        <x:v>0.25783475783475784</x:v>
+      </x:c>
+      <x:c r="H7" s="26" t="n">
+        <x:v>0.13432835820895522</x:v>
+      </x:c>
+      <x:c r="I7" s="26" t="n">
+        <x:v>0.17264276228419656</x:v>
+      </x:c>
+      <x:c r="J7" s="26" t="n">
+        <x:v>0.1755526657997399</x:v>
+      </x:c>
+      <x:c r="K7" s="26" t="n">
+        <x:v>0.15542521994134897</x:v>
+      </x:c>
       <x:c r="L7" s="26" t="n">
-        <x:v>0.09543010752688172</x:v>
+        <x:v>0.16777408637873753</x:v>
       </x:c>
       <x:c r="M7" s="26" t="n">
-        <x:v>0.21478382147838215</x:v>
+        <x:v>0.17857142857142858</x:v>
       </x:c>
       <x:c r="N7" s="26" t="n">
-        <x:v>0.21045576407506703</x:v>
-      </x:c>
-      <x:c r="O7" s="26" t="n">
-        <x:v>0.26132930513595165</x:v>
-      </x:c>
-      <x:c r="P7" s="26" t="n">
-        <x:v>0.12433155080213903</x:v>
-      </x:c>
-      <x:c r="Q7" s="26" t="n">
-        <x:v>0.25783475783475784</x:v>
-      </x:c>
-      <x:c r="R7" s="26" t="n">
-        <x:v>0.23202170963364993</x:v>
-      </x:c>
-      <x:c r="S7" s="26" t="n">
-        <x:v>0.17264276228419656</x:v>
-      </x:c>
-      <x:c r="T7" s="26" t="n">
-        <x:v>0.1755526657997399</x:v>
-      </x:c>
-      <x:c r="U7" s="27" t="n">
-        <x:v>0.15542521994134897</x:v>
+        <x:v>0.23591549295774647</x:v>
+      </x:c>
+      <x:c r="O7" s="27" t="n">
+        <x:v>0.07628524046434494</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -820,64 +776,46 @@
         <x:v>推荐产品卡片曝光数</x:v>
       </x:c>
       <x:c r="B8" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="C8" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="D8" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="E8" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="F8" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="G8" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="H8" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="I8" s="24" t="n">
-        <x:v>351</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="J8" s="24" t="n">
-        <x:v>459</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="K8" s="24" t="n">
-        <x:v>619</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="L8" s="24" t="n">
-        <x:v>515</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="M8" s="24" t="n">
-        <x:v>539</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="N8" s="24" t="n">
-        <x:v>546</x:v>
-      </x:c>
-      <x:c r="O8" s="24" t="n">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="P8" s="24" t="n">
-        <x:v>481</x:v>
-      </x:c>
-      <x:c r="Q8" s="24" t="n">
-        <x:v>551</x:v>
-      </x:c>
-      <x:c r="R8" s="24" t="n">
-        <x:v>533</x:v>
-      </x:c>
-      <x:c r="S8" s="24" t="n">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="T8" s="24" t="n">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="U8" s="25" t="n">
-        <x:v>242</x:v>
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="O8" s="25" t="n">
+        <x:v>407</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -885,115 +823,93 @@
         <x:v>推荐产品卡片点击数</x:v>
       </x:c>
       <x:c r="B9" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C9" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D9" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E9" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F9" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G9" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H9" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="I9" s="24" t="n">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="J9" s="24" t="n">
-        <x:v>109</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K9" s="24" t="n">
-        <x:v>137</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L9" s="24" t="n">
-        <x:v>110</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="M9" s="24" t="n">
-        <x:v>119</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="N9" s="24" t="n">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="O9" s="24" t="n">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="P9" s="24" t="n">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="Q9" s="24" t="n">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="R9" s="24" t="n">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="S9" s="24" t="n">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="T9" s="24" t="n">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="U9" s="25" t="n">
-        <x:v>48</x:v>
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="O9" s="25" t="n">
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="19" t="str">
         <x:v>推荐产品CTR</x:v>
       </x:c>
-      <x:c r="B10" s="26"/>
-      <x:c r="C10" s="26"/>
-      <x:c r="D10" s="26"/>
-      <x:c r="E10" s="26"/>
-      <x:c r="F10" s="26"/>
-      <x:c r="G10" s="26"/>
-      <x:c r="H10" s="26"/>
+      <x:c r="B10" s="26" t="n">
+        <x:v>0.21359223300970873</x:v>
+      </x:c>
+      <x:c r="C10" s="26" t="n">
+        <x:v>0.22077922077922077</x:v>
+      </x:c>
+      <x:c r="D10" s="26" t="n">
+        <x:v>0.25824175824175827</x:v>
+      </x:c>
+      <x:c r="E10" s="26" t="n">
+        <x:v>0.2540650406504065</x:v>
+      </x:c>
+      <x:c r="F10" s="26" t="n">
+        <x:v>0.2286902286902287</x:v>
+      </x:c>
+      <x:c r="G10" s="26" t="n">
+        <x:v>0.2250453720508167</x:v>
+      </x:c>
+      <x:c r="H10" s="26" t="n">
+        <x:v>0.24577861163227016</x:v>
+      </x:c>
       <x:c r="I10" s="26" t="n">
-        <x:v>0.2022792022792023</x:v>
+        <x:v>0.237012987012987</x:v>
       </x:c>
       <x:c r="J10" s="26" t="n">
-        <x:v>0.2374727668845316</x:v>
+        <x:v>0.25524475524475526</x:v>
       </x:c>
       <x:c r="K10" s="26" t="n">
-        <x:v>0.22132471728594508</x:v>
+        <x:v>0.19834710743801653</x:v>
       </x:c>
       <x:c r="L10" s="26" t="n">
-        <x:v>0.21359223300970873</x:v>
+        <x:v>0.24187725631768953</x:v>
       </x:c>
       <x:c r="M10" s="26" t="n">
-        <x:v>0.22077922077922077</x:v>
+        <x:v>0.24363636363636362</x:v>
       </x:c>
       <x:c r="N10" s="26" t="n">
-        <x:v>0.25824175824175827</x:v>
-      </x:c>
-      <x:c r="O10" s="26" t="n">
-        <x:v>0.2540650406504065</x:v>
-      </x:c>
-      <x:c r="P10" s="26" t="n">
-        <x:v>0.2286902286902287</x:v>
-      </x:c>
-      <x:c r="Q10" s="26" t="n">
-        <x:v>0.2250453720508167</x:v>
-      </x:c>
-      <x:c r="R10" s="26" t="n">
-        <x:v>0.24577861163227016</x:v>
-      </x:c>
-      <x:c r="S10" s="26" t="n">
-        <x:v>0.237012987012987</x:v>
-      </x:c>
-      <x:c r="T10" s="26" t="n">
-        <x:v>0.25524475524475526</x:v>
-      </x:c>
-      <x:c r="U10" s="27" t="n">
-        <x:v>0.19834710743801653</x:v>
+        <x:v>0.23787528868360278</x:v>
+      </x:c>
+      <x:c r="O10" s="27" t="n">
+        <x:v>0.20147420147420148</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1001,64 +917,46 @@
         <x:v>网站总线索数</x:v>
       </x:c>
       <x:c r="B11" s="24" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C11" s="24" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D11" s="24" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E11" s="24" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F11" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G11" s="24" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H11" s="24" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I11" s="24" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J11" s="24" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K11" s="24" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="L11" s="24" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M11" s="24" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D11" s="24" t="n">
+      <x:c r="N11" s="24" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E11" s="24" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F11" s="24" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G11" s="24" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H11" s="24" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I11" s="24" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J11" s="24" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K11" s="24" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="L11" s="24" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="M11" s="24" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="N11" s="24" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="O11" s="24" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="P11" s="24" t="n">
+      <x:c r="O11" s="25" t="n">
         <x:v>2</x:v>
-      </x:c>
-      <x:c r="Q11" s="24" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="R11" s="24" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="S11" s="24" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="T11" s="24" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="U11" s="25" t="n">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1066,64 +964,46 @@
         <x:v>AI产生线索数</x:v>
       </x:c>
       <x:c r="B12" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D12" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E12" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F12" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G12" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H12" s="24" t="n">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I12" s="24" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J12" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K12" s="24" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L12" s="24" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L12" s="24" t="n">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="M12" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N12" s="24" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="O12" s="24" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="P12" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q12" s="24" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="R12" s="24" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S12" s="24" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="T12" s="24" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="U12" s="25" t="n">
-        <x:v>7</x:v>
+      <x:c r="O12" s="25" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1131,64 +1011,46 @@
         <x:v>AI线索贡献占比</x:v>
       </x:c>
       <x:c r="B13" s="26" t="n">
-        <x:v>0</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="C13" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.18181818181818182</x:v>
       </x:c>
       <x:c r="D13" s="26" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
       <x:c r="E13" s="26" t="n">
-        <x:v>0</x:v>
+        <x:v>0.3684210526315789</x:v>
       </x:c>
       <x:c r="F13" s="26" t="n">
-        <x:v>0.14285714285714285</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G13" s="26" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.5714285714285714</x:v>
       </x:c>
       <x:c r="H13" s="26" t="n">
-        <x:v>0.5333333333333333</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
       <x:c r="I13" s="26" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.23076923076923078</x:v>
       </x:c>
       <x:c r="J13" s="26" t="n">
-        <x:v>0</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
       <x:c r="K13" s="26" t="n">
+        <x:v>0.3684210526315789</x:v>
+      </x:c>
+      <x:c r="L13" s="26" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
+      <x:c r="M13" s="26" t="n">
         <x:v>0.42857142857142855</x:v>
       </x:c>
-      <x:c r="L13" s="26" t="n">
-        <x:v>0.4</x:v>
-      </x:c>
-      <x:c r="M13" s="26" t="n">
-        <x:v>0.18181818181818182</x:v>
-      </x:c>
       <x:c r="N13" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="O13" s="26" t="n">
-        <x:v>0.3684210526315789</x:v>
-      </x:c>
-      <x:c r="P13" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q13" s="26" t="n">
-        <x:v>0.5714285714285714</x:v>
-      </x:c>
-      <x:c r="R13" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="S13" s="26" t="n">
-        <x:v>0.23076923076923078</x:v>
-      </x:c>
-      <x:c r="T13" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
-      <x:c r="U13" s="27" t="n">
-        <x:v>0.3684210526315789</x:v>
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="O13" s="27" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1196,64 +1058,46 @@
         <x:v>网站总提交预审数</x:v>
       </x:c>
       <x:c r="B14" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D14" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" s="24" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F14" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G14" s="24" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H14" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E14" s="24" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F14" s="24" t="n">
+      <x:c r="I14" s="24" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J14" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K14" s="24" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G14" s="24" t="n">
+      <x:c r="L14" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H14" s="24" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="I14" s="24" t="n">
+      <x:c r="M14" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J14" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K14" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L14" s="24" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="M14" s="24" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="N14" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O14" s="24" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="P14" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q14" s="24" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="R14" s="24" t="n">
+      <x:c r="O14" s="25" t="n">
         <x:v>2</x:v>
-      </x:c>
-      <x:c r="S14" s="24" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="T14" s="24" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="U14" s="25" t="n">
-        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1261,7 +1105,7 @@
         <x:v>AI提交预审数</x:v>
       </x:c>
       <x:c r="B15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
         <x:v>0</x:v>
@@ -1270,28 +1114,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F15" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G15" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H15" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I15" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L15" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M15" s="24" t="n">
         <x:v>0</x:v>
@@ -1299,26 +1143,8 @@
       <x:c r="N15" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O15" s="24" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="P15" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q15" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R15" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S15" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T15" s="24" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="U15" s="25" t="n">
-        <x:v>2</x:v>
+      <x:c r="O15" s="25" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1326,62 +1152,42 @@
         <x:v>AI提交预审占比</x:v>
       </x:c>
       <x:c r="B16" s="26" t="n">
-        <x:v>0</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="C16" s="26" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="D16" s="26"/>
       <x:c r="E16" s="26" t="n">
-        <x:v>0</x:v>
+        <x:v>0.45454545454545453</x:v>
       </x:c>
       <x:c r="F16" s="26" t="n">
-        <x:v>0.14285714285714285</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G16" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H16" s="26" t="n">
-        <x:v>0.36363636363636365</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I16" s="26" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J16" s="26" t="n">
-        <x:v>0</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
       <x:c r="K16" s="26" t="n">
-        <x:v>0</x:v>
+        <x:v>0.2857142857142857</x:v>
       </x:c>
       <x:c r="L16" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M16" s="26" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N16" s="26"/>
-      <x:c r="O16" s="26" t="n">
-        <x:v>0.45454545454545453</x:v>
-      </x:c>
-      <x:c r="P16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T16" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="U16" s="27" t="n">
-        <x:v>0.2857142857142857</x:v>
+      <x:c r="O16" s="27" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1392,34 +1198,34 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C17" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E17" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F17" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G17" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H17" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I17" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J17" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K17" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17" s="24" t="n">
         <x:v>1</x:v>
-      </x:c>
-      <x:c r="K17" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L17" s="24" t="n">
-        <x:v>4</x:v>
       </x:c>
       <x:c r="M17" s="24" t="n">
         <x:v>1</x:v>
@@ -1427,25 +1233,7 @@
       <x:c r="N17" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O17" s="24" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="P17" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q17" s="24" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="R17" s="24" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S17" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T17" s="24" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="U17" s="25" t="n">
+      <x:c r="O17" s="25" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1454,7 +1242,7 @@
         <x:v>AI预审通过数</x:v>
       </x:c>
       <x:c r="B18" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C18" s="24" t="n">
         <x:v>0</x:v>
@@ -1463,7 +1251,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E18" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F18" s="24" t="n">
         <x:v>0</x:v>
@@ -1472,19 +1260,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H18" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I18" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="K18" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L18" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M18" s="24" t="n">
         <x:v>0</x:v>
@@ -1492,25 +1280,7 @@
       <x:c r="N18" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O18" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T18" s="24" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="U18" s="25" t="n">
+      <x:c r="O18" s="25" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1519,49 +1289,37 @@
         <x:v>AI通过预审占比</x:v>
       </x:c>
       <x:c r="B19" s="26" t="n">
-        <x:v>0</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="C19" s="26" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="26"/>
-      <x:c r="E19" s="26"/>
-      <x:c r="F19" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="26"/>
+      <x:c r="E19" s="26" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F19" s="26"/>
+      <x:c r="G19" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="H19" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="I19" s="26"/>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I19" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J19" s="26" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K19" s="26"/>
       <x:c r="L19" s="26" t="n">
-        <x:v>0.75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M19" s="26" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N19" s="26"/>
-      <x:c r="O19" s="26" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="P19" s="26"/>
-      <x:c r="Q19" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R19" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S19" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T19" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U19" s="27"/>
+      <x:c r="O19" s="27"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1589,7 +1347,7 @@
         <x:v>统计周期</x:v>
       </x:c>
       <x:c r="B2" s="33" t="str">
-        <x:v>2026-07-16 至 2026-08-05</x:v>
+        <x:v>2026-07-27 至 2026-08-09</x:v>
       </x:c>
     </x:row>
     <x:row r="3">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="R0216e98f62094028"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="Reb2aab075b0f4e0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="Rf0e7a4f7f1fd427f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="Rd8e9f03c23b14955"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="Rf0e7a4f7f1fd427f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="Rd8e9f03c23b14955"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="R4fe7f1e927e74ea3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="R508cb0471def48bd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -273,9 +273,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -447,46 +447,46 @@
         <x:v>Date</x:v>
       </x:c>
       <x:c r="B1" s="22" t="n">
-        <x:v>46230</x:v>
+        <x:v>46237</x:v>
       </x:c>
       <x:c r="C1" s="22" t="n">
-        <x:v>46231</x:v>
+        <x:v>46238</x:v>
       </x:c>
       <x:c r="D1" s="22" t="n">
-        <x:v>46232</x:v>
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="E1" s="22" t="n">
-        <x:v>46233</x:v>
+        <x:v>46240</x:v>
       </x:c>
       <x:c r="F1" s="22" t="n">
-        <x:v>46234</x:v>
+        <x:v>46241</x:v>
       </x:c>
       <x:c r="G1" s="22" t="n">
-        <x:v>46235</x:v>
+        <x:v>46242</x:v>
       </x:c>
       <x:c r="H1" s="22" t="n">
-        <x:v>46236</x:v>
+        <x:v>46243</x:v>
       </x:c>
       <x:c r="I1" s="22" t="n">
-        <x:v>46237</x:v>
+        <x:v>46244</x:v>
       </x:c>
       <x:c r="J1" s="22" t="n">
-        <x:v>46238</x:v>
+        <x:v>46245</x:v>
       </x:c>
       <x:c r="K1" s="22" t="n">
-        <x:v>46239</x:v>
+        <x:v>46246</x:v>
       </x:c>
       <x:c r="L1" s="22" t="n">
-        <x:v>46240</x:v>
+        <x:v>46247</x:v>
       </x:c>
       <x:c r="M1" s="22" t="n">
-        <x:v>46241</x:v>
+        <x:v>46248</x:v>
       </x:c>
       <x:c r="N1" s="22" t="n">
-        <x:v>46242</x:v>
+        <x:v>46249</x:v>
       </x:c>
       <x:c r="O1" s="23" t="n">
-        <x:v>46243</x:v>
+        <x:v>46250</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -494,46 +494,46 @@
         <x:v>网站整体用户数</x:v>
       </x:c>
       <x:c r="B2" s="24" t="n">
-        <x:v>6688</x:v>
+        <x:v>5955</x:v>
       </x:c>
       <x:c r="C2" s="24" t="n">
-        <x:v>5981</x:v>
+        <x:v>6199</x:v>
       </x:c>
       <x:c r="D2" s="24" t="n">
-        <x:v>6542</x:v>
+        <x:v>5549</x:v>
       </x:c>
       <x:c r="E2" s="24" t="n">
-        <x:v>5390</x:v>
+        <x:v>4499</x:v>
       </x:c>
       <x:c r="F2" s="24" t="n">
-        <x:v>5797</x:v>
+        <x:v>4467</x:v>
       </x:c>
       <x:c r="G2" s="24" t="n">
-        <x:v>6231</x:v>
+        <x:v>4961</x:v>
       </x:c>
       <x:c r="H2" s="24" t="n">
-        <x:v>6319</x:v>
+        <x:v>5283</x:v>
       </x:c>
       <x:c r="I2" s="24" t="n">
-        <x:v>5955</x:v>
+        <x:v>5266</x:v>
       </x:c>
       <x:c r="J2" s="24" t="n">
-        <x:v>6199</x:v>
+        <x:v>6161</x:v>
       </x:c>
       <x:c r="K2" s="24" t="n">
-        <x:v>5549</x:v>
+        <x:v>7094</x:v>
       </x:c>
       <x:c r="L2" s="24" t="n">
-        <x:v>4499</x:v>
+        <x:v>7641</x:v>
       </x:c>
       <x:c r="M2" s="24" t="n">
-        <x:v>4467</x:v>
+        <x:v>5908</x:v>
       </x:c>
       <x:c r="N2" s="24" t="n">
-        <x:v>4961</x:v>
+        <x:v>6665</x:v>
       </x:c>
       <x:c r="O2" s="25" t="n">
-        <x:v>5079</x:v>
+        <x:v>7008</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -541,46 +541,46 @@
         <x:v>使用AI用户数</x:v>
       </x:c>
       <x:c r="B3" s="24" t="n">
-        <x:v>744</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="C3" s="24" t="n">
-        <x:v>717</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="D3" s="24" t="n">
-        <x:v>746</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="E3" s="24" t="n">
-        <x:v>662</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="F3" s="24" t="n">
-        <x:v>748</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="G3" s="24" t="n">
-        <x:v>702</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="H3" s="24" t="n">
-        <x:v>737</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="I3" s="24" t="n">
-        <x:v>753</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="J3" s="24" t="n">
-        <x:v>769</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="K3" s="24" t="n">
-        <x:v>682</x:v>
+        <x:v>893</x:v>
       </x:c>
       <x:c r="L3" s="24" t="n">
-        <x:v>602</x:v>
+        <x:v>878</x:v>
       </x:c>
       <x:c r="M3" s="24" t="n">
-        <x:v>560</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="N3" s="24" t="n">
-        <x:v>568</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="O3" s="25" t="n">
-        <x:v>603</x:v>
+        <x:v>797</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -588,46 +588,46 @@
         <x:v>AI-UV渗透</x:v>
       </x:c>
       <x:c r="B4" s="26" t="n">
-        <x:v>0.11124401913875598</x:v>
+        <x:v>0.12644836272040302</x:v>
       </x:c>
       <x:c r="C4" s="26" t="n">
-        <x:v>0.119879618792844</x:v>
+        <x:v>0.1240522664945959</x:v>
       </x:c>
       <x:c r="D4" s="26" t="n">
-        <x:v>0.11403240599205136</x:v>
+        <x:v>0.12290502793296089</x:v>
       </x:c>
       <x:c r="E4" s="26" t="n">
-        <x:v>0.12282003710575139</x:v>
+        <x:v>0.13380751278061792</x:v>
       </x:c>
       <x:c r="F4" s="26" t="n">
-        <x:v>0.12903225806451613</x:v>
+        <x:v>0.12536377882247593</x:v>
       </x:c>
       <x:c r="G4" s="26" t="n">
-        <x:v>0.11266249398170439</x:v>
+        <x:v>0.11449304575690385</x:v>
       </x:c>
       <x:c r="H4" s="26" t="n">
-        <x:v>0.11663237854090837</x:v>
+        <x:v>0.11849328033314405</x:v>
       </x:c>
       <x:c r="I4" s="26" t="n">
-        <x:v>0.12644836272040302</x:v>
+        <x:v>0.11830611469806304</x:v>
       </x:c>
       <x:c r="J4" s="26" t="n">
-        <x:v>0.1240522664945959</x:v>
+        <x:v>0.13001136179191689</x:v>
       </x:c>
       <x:c r="K4" s="26" t="n">
-        <x:v>0.12290502793296089</x:v>
+        <x:v>0.12588102621934028</x:v>
       </x:c>
       <x:c r="L4" s="26" t="n">
-        <x:v>0.13380751278061792</x:v>
+        <x:v>0.11490642586048946</x:v>
       </x:c>
       <x:c r="M4" s="26" t="n">
-        <x:v>0.12536377882247593</x:v>
+        <x:v>0.10781990521327015</x:v>
       </x:c>
       <x:c r="N4" s="26" t="n">
-        <x:v>0.11449304575690385</x:v>
+        <x:v>0.11282820705176294</x:v>
       </x:c>
       <x:c r="O4" s="27" t="n">
-        <x:v>0.11872415829887774</x:v>
+        <x:v>0.1137271689497717</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -635,46 +635,46 @@
         <x:v>平均会话轮次</x:v>
       </x:c>
       <x:c r="B5" s="28" t="n">
-        <x:v>1.288056206088993</x:v>
+        <x:v>1.3568215892053972</x:v>
       </x:c>
       <x:c r="C5" s="28" t="n">
-        <x:v>1.4005235602094241</x:v>
+        <x:v>1.326478149100257</x:v>
       </x:c>
       <x:c r="D5" s="28" t="n">
-        <x:v>1.4366998577524894</x:v>
+        <x:v>1.2588757396449703</x:v>
       </x:c>
       <x:c r="E5" s="28" t="n">
-        <x:v>1.4586070959264126</x:v>
+        <x:v>1.3190298507462686</x:v>
       </x:c>
       <x:c r="F5" s="28" t="n">
-        <x:v>1.4132352941176471</x:v>
+        <x:v>1.284965034965035</x:v>
       </x:c>
       <x:c r="G5" s="28" t="n">
-        <x:v>1.485054347826087</x:v>
+        <x:v>1.4908759124087592</x:v>
       </x:c>
       <x:c r="H5" s="28" t="n">
-        <x:v>1.458937198067633</x:v>
+        <x:v>1.5400516795865633</x:v>
       </x:c>
       <x:c r="I5" s="28" t="n">
-        <x:v>1.3568215892053972</x:v>
+        <x:v>1.3111510791366907</x:v>
       </x:c>
       <x:c r="J5" s="28" t="n">
-        <x:v>1.326478149100257</x:v>
+        <x:v>1.2496025437201908</x:v>
       </x:c>
       <x:c r="K5" s="28" t="n">
-        <x:v>1.2588757396449703</x:v>
+        <x:v>1.3145780051150895</x:v>
       </x:c>
       <x:c r="L5" s="28" t="n">
-        <x:v>1.3190298507462686</x:v>
+        <x:v>1.4320388349514563</x:v>
       </x:c>
       <x:c r="M5" s="28" t="n">
-        <x:v>1.284965034965035</x:v>
+        <x:v>1.5826666666666667</x:v>
       </x:c>
       <x:c r="N5" s="28" t="n">
-        <x:v>1.4908759124087592</x:v>
+        <x:v>1.467359050445104</x:v>
       </x:c>
       <x:c r="O5" s="29" t="n">
-        <x:v>1.544502617801047</x:v>
+        <x:v>1.607717041800643</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -682,46 +682,46 @@
         <x:v>2V2会话用户数</x:v>
       </x:c>
       <x:c r="B6" s="24" t="n">
-        <x:v>71</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C6" s="24" t="n">
-        <x:v>154</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D6" s="24" t="n">
-        <x:v>157</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E6" s="24" t="n">
-        <x:v>173</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F6" s="24" t="n">
-        <x:v>156</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G6" s="24" t="n">
-        <x:v>181</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="H6" s="24" t="n">
-        <x:v>99</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="I6" s="24" t="n">
-        <x:v>130</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="J6" s="24" t="n">
-        <x:v>135</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K6" s="24" t="n">
-        <x:v>106</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="L6" s="24" t="n">
-        <x:v>101</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="M6" s="24" t="n">
-        <x:v>100</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="N6" s="24" t="n">
-        <x:v>134</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="O6" s="25" t="n">
-        <x:v>46</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -729,46 +729,46 @@
         <x:v>2V2会话用户占比</x:v>
       </x:c>
       <x:c r="B7" s="26" t="n">
-        <x:v>0.09543010752688172</x:v>
+        <x:v>0.17264276228419656</x:v>
       </x:c>
       <x:c r="C7" s="26" t="n">
-        <x:v>0.21478382147838215</x:v>
+        <x:v>0.1755526657997399</x:v>
       </x:c>
       <x:c r="D7" s="26" t="n">
-        <x:v>0.21045576407506703</x:v>
+        <x:v>0.15542521994134897</x:v>
       </x:c>
       <x:c r="E7" s="26" t="n">
-        <x:v>0.26132930513595165</x:v>
+        <x:v>0.16777408637873753</x:v>
       </x:c>
       <x:c r="F7" s="26" t="n">
-        <x:v>0.20855614973262032</x:v>
+        <x:v>0.17857142857142858</x:v>
       </x:c>
       <x:c r="G7" s="26" t="n">
-        <x:v>0.25783475783475784</x:v>
+        <x:v>0.23591549295774647</x:v>
       </x:c>
       <x:c r="H7" s="26" t="n">
-        <x:v>0.13432835820895522</x:v>
+        <x:v>0.17252396166134185</x:v>
       </x:c>
       <x:c r="I7" s="26" t="n">
-        <x:v>0.17264276228419656</x:v>
+        <x:v>0.1476725521669342</x:v>
       </x:c>
       <x:c r="J7" s="26" t="n">
-        <x:v>0.1755526657997399</x:v>
+        <x:v>0.11860174781523096</x:v>
       </x:c>
       <x:c r="K7" s="26" t="n">
-        <x:v>0.15542521994134897</x:v>
+        <x:v>0.1623740201567749</x:v>
       </x:c>
       <x:c r="L7" s="26" t="n">
-        <x:v>0.16777408637873753</x:v>
+        <x:v>0.21753986332574032</x:v>
       </x:c>
       <x:c r="M7" s="26" t="n">
-        <x:v>0.17857142857142858</x:v>
+        <x:v>0.29984301412872844</x:v>
       </x:c>
       <x:c r="N7" s="26" t="n">
-        <x:v>0.23591549295774647</x:v>
+        <x:v>0.2127659574468085</x:v>
       </x:c>
       <x:c r="O7" s="27" t="n">
-        <x:v>0.07628524046434494</x:v>
+        <x:v>0.1028858218318695</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -776,46 +776,46 @@
         <x:v>推荐产品卡片曝光数</x:v>
       </x:c>
       <x:c r="B8" s="24" t="n">
-        <x:v>515</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="C8" s="24" t="n">
-        <x:v>539</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="D8" s="24" t="n">
-        <x:v>546</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="E8" s="24" t="n">
-        <x:v>492</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="F8" s="24" t="n">
-        <x:v>481</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="G8" s="24" t="n">
-        <x:v>551</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="H8" s="24" t="n">
-        <x:v>533</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="I8" s="24" t="n">
-        <x:v>308</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="J8" s="24" t="n">
-        <x:v>286</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="K8" s="24" t="n">
-        <x:v>242</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="L8" s="24" t="n">
-        <x:v>277</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="M8" s="24" t="n">
-        <x:v>275</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="N8" s="24" t="n">
-        <x:v>433</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="O8" s="25" t="n">
-        <x:v>407</x:v>
+        <x:v>627</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -823,46 +823,46 @@
         <x:v>推荐产品卡片点击数</x:v>
       </x:c>
       <x:c r="B9" s="24" t="n">
-        <x:v>110</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C9" s="24" t="n">
-        <x:v>119</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D9" s="24" t="n">
-        <x:v>141</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E9" s="24" t="n">
-        <x:v>125</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F9" s="24" t="n">
-        <x:v>110</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G9" s="24" t="n">
-        <x:v>124</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H9" s="24" t="n">
-        <x:v>131</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="I9" s="24" t="n">
-        <x:v>73</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J9" s="24" t="n">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="K9" s="24" t="n">
-        <x:v>48</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="L9" s="24" t="n">
-        <x:v>67</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="M9" s="24" t="n">
-        <x:v>67</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="N9" s="24" t="n">
-        <x:v>103</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="O9" s="25" t="n">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -870,46 +870,46 @@
         <x:v>推荐产品CTR</x:v>
       </x:c>
       <x:c r="B10" s="26" t="n">
-        <x:v>0.21359223300970873</x:v>
+        <x:v>0.237012987012987</x:v>
       </x:c>
       <x:c r="C10" s="26" t="n">
-        <x:v>0.22077922077922077</x:v>
+        <x:v>0.25524475524475526</x:v>
       </x:c>
       <x:c r="D10" s="26" t="n">
-        <x:v>0.25824175824175827</x:v>
+        <x:v>0.19834710743801653</x:v>
       </x:c>
       <x:c r="E10" s="26" t="n">
-        <x:v>0.2540650406504065</x:v>
+        <x:v>0.24187725631768953</x:v>
       </x:c>
       <x:c r="F10" s="26" t="n">
-        <x:v>0.2286902286902287</x:v>
+        <x:v>0.24363636363636362</x:v>
       </x:c>
       <x:c r="G10" s="26" t="n">
-        <x:v>0.2250453720508167</x:v>
+        <x:v>0.23787528868360278</x:v>
       </x:c>
       <x:c r="H10" s="26" t="n">
-        <x:v>0.24577861163227016</x:v>
+        <x:v>0.2037914691943128</x:v>
       </x:c>
       <x:c r="I10" s="26" t="n">
-        <x:v>0.237012987012987</x:v>
+        <x:v>0.23275862068965517</x:v>
       </x:c>
       <x:c r="J10" s="26" t="n">
-        <x:v>0.25524475524475526</x:v>
+        <x:v>0.22044728434504793</x:v>
       </x:c>
       <x:c r="K10" s="26" t="n">
-        <x:v>0.19834710743801653</x:v>
+        <x:v>0.25309734513274335</x:v>
       </x:c>
       <x:c r="L10" s="26" t="n">
-        <x:v>0.24187725631768953</x:v>
+        <x:v>0.13841368584758942</x:v>
       </x:c>
       <x:c r="M10" s="26" t="n">
-        <x:v>0.24363636363636362</x:v>
+        <x:v>0.166</x:v>
       </x:c>
       <x:c r="N10" s="26" t="n">
-        <x:v>0.23787528868360278</x:v>
+        <x:v>0.1223021582733813</x:v>
       </x:c>
       <x:c r="O10" s="27" t="n">
-        <x:v>0.20147420147420148</x:v>
+        <x:v>0.13556618819776714</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -917,46 +917,46 @@
         <x:v>网站总线索数</x:v>
       </x:c>
       <x:c r="B11" s="24" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="24" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D11" s="24" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E11" s="24" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F11" s="24" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G11" s="24" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H11" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I11" s="24" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J11" s="24" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="24" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E11" s="24" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F11" s="24" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G11" s="24" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H11" s="24" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I11" s="24" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="J11" s="24" t="n">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="K11" s="24" t="n">
-        <x:v>19</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L11" s="24" t="n">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="M11" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N11" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="O11" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -964,46 +964,46 @@
         <x:v>AI产生线索数</x:v>
       </x:c>
       <x:c r="B12" s="24" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D12" s="24" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E12" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F12" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G12" s="24" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E12" s="24" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F12" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="24" t="n">
+      <x:c r="H12" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I12" s="24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J12" s="24" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H12" s="24" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I12" s="24" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="J12" s="24" t="n">
+      <x:c r="K12" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K12" s="24" t="n">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="L12" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="M12" s="24" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="N12" s="24" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O12" s="25" t="n">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="O12" s="25" t="n">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1011,46 +1011,46 @@
         <x:v>AI线索贡献占比</x:v>
       </x:c>
       <x:c r="B13" s="26" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.23076923076923078</x:v>
       </x:c>
       <x:c r="C13" s="26" t="n">
-        <x:v>0.18181818181818182</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
       <x:c r="D13" s="26" t="n">
+        <x:v>0.3684210526315789</x:v>
+      </x:c>
+      <x:c r="E13" s="26" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
+      <x:c r="F13" s="26" t="n">
+        <x:v>0.42857142857142855</x:v>
+      </x:c>
+      <x:c r="G13" s="26" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="H13" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I13" s="26" t="n">
+        <x:v>0.16666666666666666</x:v>
+      </x:c>
+      <x:c r="J13" s="26" t="n">
+        <x:v>0.5333333333333333</x:v>
+      </x:c>
+      <x:c r="K13" s="26" t="n">
         <x:v>0.6666666666666666</x:v>
       </x:c>
-      <x:c r="E13" s="26" t="n">
-        <x:v>0.3684210526315789</x:v>
-      </x:c>
-      <x:c r="F13" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="26" t="n">
-        <x:v>0.5714285714285714</x:v>
-      </x:c>
-      <x:c r="H13" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="I13" s="26" t="n">
-        <x:v>0.23076923076923078</x:v>
-      </x:c>
-      <x:c r="J13" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
-      <x:c r="K13" s="26" t="n">
-        <x:v>0.3684210526315789</x:v>
-      </x:c>
       <x:c r="L13" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M13" s="26" t="n">
-        <x:v>0.42857142857142855</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N13" s="26" t="n">
-        <x:v>0.8</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="O13" s="27" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1058,46 +1058,46 @@
         <x:v>网站总提交预审数</x:v>
       </x:c>
       <x:c r="B14" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E14" s="24" t="n">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F14" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G14" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="24" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I14" s="24" t="n">
-        <x:v>9</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J14" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K14" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L14" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M14" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N14" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O14" s="25" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1105,16 +1105,16 @@
         <x:v>AI提交预审数</x:v>
       </x:c>
       <x:c r="B15" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E15" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F15" s="24" t="n">
         <x:v>0</x:v>
@@ -1126,13 +1126,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K15" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L15" s="24" t="n">
         <x:v>0</x:v>
@@ -1152,83 +1152,75 @@
         <x:v>AI提交预审占比</x:v>
       </x:c>
       <x:c r="B16" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D16" s="26"/>
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
+      <x:c r="D16" s="26" t="n">
+        <x:v>0.2857142857142857</x:v>
+      </x:c>
       <x:c r="E16" s="26" t="n">
-        <x:v>0.45454545454545453</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F16" s="26" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="G16" s="26"/>
       <x:c r="H16" s="26" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I16" s="26" t="n">
-        <x:v>0</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
       <x:c r="J16" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
-      <x:c r="K16" s="26" t="n">
-        <x:v>0.2857142857142857</x:v>
-      </x:c>
-      <x:c r="L16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M16" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" s="26"/>
+      <x:c r="L16" s="26"/>
+      <x:c r="M16" s="26"/>
       <x:c r="N16" s="26"/>
-      <x:c r="O16" s="27" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="O16" s="27"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="19" t="str">
         <x:v>网站预审通过数</x:v>
       </x:c>
       <x:c r="B17" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C17" s="24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D17" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D17" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E17" s="24" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="F17" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G17" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H17" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J17" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K17" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L17" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M17" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N17" s="24" t="n">
         <x:v>0</x:v>
@@ -1242,16 +1234,16 @@
         <x:v>AI预审通过数</x:v>
       </x:c>
       <x:c r="B18" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D18" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E18" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F18" s="24" t="n">
         <x:v>0</x:v>
@@ -1266,7 +1258,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J18" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K18" s="24" t="n">
         <x:v>0</x:v>
@@ -1289,35 +1281,25 @@
         <x:v>AI通过预审占比</x:v>
       </x:c>
       <x:c r="B19" s="26" t="n">
-        <x:v>0.75</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C19" s="26" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D19" s="26"/>
       <x:c r="E19" s="26" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="F19" s="26"/>
-      <x:c r="G19" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H19" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I19" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J19" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" s="26"/>
+      <x:c r="H19" s="26"/>
+      <x:c r="I19" s="26"/>
+      <x:c r="J19" s="26"/>
       <x:c r="K19" s="26"/>
-      <x:c r="L19" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M19" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="L19" s="26"/>
+      <x:c r="M19" s="26"/>
       <x:c r="N19" s="26"/>
       <x:c r="O19" s="27"/>
     </x:row>
@@ -1347,7 +1329,7 @@
         <x:v>统计周期</x:v>
       </x:c>
       <x:c r="B2" s="33" t="str">
-        <x:v>2026-07-27 至 2026-08-09</x:v>
+        <x:v>2026-08-03 至 2026-08-16</x:v>
       </x:c>
     </x:row>
     <x:row r="3">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="R4fe7f1e927e74ea3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="R508cb0471def48bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="Refe024b5d52640b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="R8efefe2aabe84a87"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -590,46 +590,46 @@
         </is>
       </c>
       <c r="B2" s="36" t="n">
-        <v>5955</v>
+        <v>9634</v>
       </c>
       <c r="C2" s="36" t="n">
-        <v>6199</v>
+        <v>8811</v>
       </c>
       <c r="D2" s="36" t="n">
-        <v>5549</v>
+        <v>6869</v>
       </c>
       <c r="E2" s="36" t="n">
-        <v>4499</v>
+        <v>7502</v>
       </c>
       <c r="F2" s="36" t="n">
-        <v>4467</v>
+        <v>6818</v>
       </c>
       <c r="G2" s="36" t="n">
-        <v>4961</v>
+        <v>9439</v>
       </c>
       <c r="H2" s="36" t="n">
-        <v>5283</v>
+        <v>8025</v>
       </c>
       <c r="I2" s="36" t="n">
-        <v>5266</v>
+        <v>7240</v>
       </c>
       <c r="J2" s="36" t="n">
-        <v>6161</v>
+        <v>6763</v>
       </c>
       <c r="K2" s="36" t="n">
-        <v>7094</v>
+        <v>5550</v>
       </c>
       <c r="L2" s="36" t="n">
-        <v>7641</v>
+        <v>5282</v>
       </c>
       <c r="M2" s="36" t="n">
-        <v>5908</v>
+        <v>5657</v>
       </c>
       <c r="N2" s="36" t="n">
-        <v>6665</v>
+        <v>6572</v>
       </c>
       <c r="O2" s="37" t="n">
-        <v>7008</v>
+        <v>6092</v>
       </c>
     </row>
     <row r="3">
@@ -639,44 +639,46 @@
         </is>
       </c>
       <c r="B3" s="36" t="n">
-        <v>698</v>
+        <v>667</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>711</v>
+        <v>778</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>625</v>
+        <v>676</v>
       </c>
       <c r="E3" s="36" t="n">
-        <v>555</v>
+        <v>536</v>
       </c>
       <c r="F3" s="36" t="n">
-        <v>526</v>
+        <v>572</v>
       </c>
       <c r="G3" s="36" t="n">
-        <v>540</v>
-      </c>
-      <c r="H3" s="36" t="n"/>
+        <v>548</v>
+      </c>
+      <c r="H3" s="36" t="n">
+        <v>191</v>
+      </c>
       <c r="I3" s="36" t="n">
-        <v>556</v>
+        <v>338</v>
       </c>
       <c r="J3" s="36" t="n">
-        <v>714</v>
+        <v>629</v>
       </c>
       <c r="K3" s="36" t="n">
-        <v>837</v>
+        <v>782</v>
       </c>
       <c r="L3" s="36" t="n">
-        <v>851</v>
+        <v>824</v>
       </c>
       <c r="M3" s="36" t="n">
-        <v>605</v>
+        <v>750</v>
       </c>
       <c r="N3" s="36" t="n">
-        <v>736</v>
+        <v>674</v>
       </c>
       <c r="O3" s="37" t="n">
-        <v>838</v>
+        <v>870</v>
       </c>
     </row>
     <row r="4">
@@ -686,44 +688,46 @@
         </is>
       </c>
       <c r="B4" s="38" t="n">
-        <v>0.117212</v>
+        <v>0.069234</v>
       </c>
       <c r="C4" s="38" t="n">
-        <v>0.114696</v>
+        <v>0.088299</v>
       </c>
       <c r="D4" s="38" t="n">
-        <v>0.112633</v>
+        <v>0.098413</v>
       </c>
       <c r="E4" s="38" t="n">
-        <v>0.123361</v>
+        <v>0.071448</v>
       </c>
       <c r="F4" s="38" t="n">
-        <v>0.117752</v>
+        <v>0.083896</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.108849</v>
-      </c>
-      <c r="H4" s="38" t="n"/>
+        <v>0.058057</v>
+      </c>
+      <c r="H4" s="38" t="n">
+        <v>0.023801</v>
+      </c>
       <c r="I4" s="38" t="n">
-        <v>0.105583</v>
+        <v>0.046685</v>
       </c>
       <c r="J4" s="38" t="n">
-        <v>0.11589</v>
+        <v>0.09300600000000001</v>
       </c>
       <c r="K4" s="38" t="n">
-        <v>0.117987</v>
+        <v>0.140901</v>
       </c>
       <c r="L4" s="38" t="n">
-        <v>0.111373</v>
+        <v>0.156002</v>
       </c>
       <c r="M4" s="38" t="n">
-        <v>0.102404</v>
+        <v>0.132579</v>
       </c>
       <c r="N4" s="38" t="n">
-        <v>0.110428</v>
+        <v>0.102556</v>
       </c>
       <c r="O4" s="39" t="n">
-        <v>0.119578</v>
+        <v>0.14281</v>
       </c>
     </row>
     <row r="5">
@@ -782,44 +786,46 @@
         </is>
       </c>
       <c r="B6" s="36" t="n">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E6" s="36" t="n">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="F6" s="36" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" s="36" t="n">
+        <v>134</v>
+      </c>
+      <c r="H6" s="36" t="n">
+        <v>46</v>
+      </c>
+      <c r="I6" s="36" t="n">
+        <v>57</v>
+      </c>
+      <c r="J6" s="36" t="n">
         <v>95</v>
       </c>
-      <c r="G6" s="36" t="n">
-        <v>131</v>
-      </c>
-      <c r="H6" s="36" t="n"/>
-      <c r="I6" s="36" t="n">
-        <v>93</v>
-      </c>
-      <c r="J6" s="36" t="n">
-        <v>112</v>
-      </c>
       <c r="K6" s="36" t="n">
-        <v>183</v>
+        <v>145</v>
       </c>
       <c r="L6" s="36" t="n">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="M6" s="36" t="n">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="N6" s="36" t="n">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="O6" s="37" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7">
@@ -829,44 +835,46 @@
         </is>
       </c>
       <c r="B7" s="38" t="n">
-        <v>0.160458</v>
+        <v>0.194903</v>
       </c>
       <c r="C7" s="38" t="n">
-        <v>0.178622</v>
+        <v>0.173522</v>
       </c>
       <c r="D7" s="38" t="n">
-        <v>0.1488</v>
+        <v>0.156805</v>
       </c>
       <c r="E7" s="38" t="n">
-        <v>0.2</v>
+        <v>0.188433</v>
       </c>
       <c r="F7" s="38" t="n">
-        <v>0.180608</v>
+        <v>0.174825</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.242593</v>
-      </c>
-      <c r="H7" s="38" t="n"/>
+        <v>0.244526</v>
+      </c>
+      <c r="H7" s="38" t="n">
+        <v>0.240838</v>
+      </c>
       <c r="I7" s="38" t="n">
-        <v>0.167266</v>
+        <v>0.168639</v>
       </c>
       <c r="J7" s="38" t="n">
-        <v>0.156863</v>
+        <v>0.151033</v>
       </c>
       <c r="K7" s="38" t="n">
-        <v>0.218638</v>
+        <v>0.185422</v>
       </c>
       <c r="L7" s="38" t="n">
-        <v>0.239718</v>
+        <v>0.231796</v>
       </c>
       <c r="M7" s="38" t="n">
-        <v>0.257851</v>
+        <v>0.254667</v>
       </c>
       <c r="N7" s="38" t="n">
-        <v>0.235054</v>
+        <v>0.237389</v>
       </c>
       <c r="O7" s="39" t="n">
-        <v>0.263723</v>
+        <v>0.268966</v>
       </c>
     </row>
     <row r="8">
@@ -876,44 +884,46 @@
         </is>
       </c>
       <c r="B8" s="36" t="n">
-        <v>675</v>
+        <v>647</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>682</v>
+        <v>745</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>607</v>
+        <v>652</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>536</v>
+        <v>521</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>506</v>
+        <v>551</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>520</v>
-      </c>
-      <c r="H8" s="36" t="n"/>
+        <v>529</v>
+      </c>
+      <c r="H8" s="36" t="n">
+        <v>183</v>
+      </c>
       <c r="I8" s="36" t="n">
-        <v>545</v>
+        <v>330</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>688</v>
+        <v>605</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>802</v>
+        <v>758</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>836</v>
+        <v>799</v>
       </c>
       <c r="M8" s="36" t="n">
-        <v>589</v>
+        <v>733</v>
       </c>
       <c r="N8" s="36" t="n">
-        <v>717</v>
+        <v>659</v>
       </c>
       <c r="O8" s="37" t="n">
-        <v>815</v>
+        <v>850</v>
       </c>
     </row>
     <row r="9">
@@ -940,7 +950,9 @@
       <c r="G9" s="36" t="n">
         <v>102</v>
       </c>
-      <c r="H9" s="36" t="n"/>
+      <c r="H9" s="36" t="n">
+        <v>86</v>
+      </c>
       <c r="I9" s="36" t="n">
         <v>51</v>
       </c>
@@ -970,44 +982,46 @@
         </is>
       </c>
       <c r="B10" s="38" t="n">
-        <v>0.105185</v>
+        <v>0.109737</v>
       </c>
       <c r="C10" s="38" t="n">
-        <v>0.107038</v>
+        <v>0.097987</v>
       </c>
       <c r="D10" s="38" t="n">
-        <v>0.08072500000000001</v>
+        <v>0.075153</v>
       </c>
       <c r="E10" s="38" t="n">
-        <v>0.123134</v>
+        <v>0.126679</v>
       </c>
       <c r="F10" s="38" t="n">
-        <v>0.128458</v>
+        <v>0.117967</v>
       </c>
       <c r="G10" s="38" t="n">
-        <v>0.196154</v>
-      </c>
-      <c r="H10" s="38" t="n"/>
+        <v>0.192817</v>
+      </c>
+      <c r="H10" s="38" t="n">
+        <v>0.469945</v>
+      </c>
       <c r="I10" s="38" t="n">
-        <v>0.09357799999999999</v>
+        <v>0.154545</v>
       </c>
       <c r="J10" s="38" t="n">
-        <v>0.097384</v>
+        <v>0.110744</v>
       </c>
       <c r="K10" s="38" t="n">
-        <v>0.177057</v>
+        <v>0.187335</v>
       </c>
       <c r="L10" s="38" t="n">
-        <v>0.106459</v>
+        <v>0.111389</v>
       </c>
       <c r="M10" s="38" t="n">
-        <v>0.142615</v>
+        <v>0.114598</v>
       </c>
       <c r="N10" s="38" t="n">
-        <v>0.099024</v>
+        <v>0.107739</v>
       </c>
       <c r="O10" s="39" t="n">
-        <v>0.110429</v>
+        <v>0.105882</v>
       </c>
     </row>
     <row r="11">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -590,46 +590,46 @@
         </is>
       </c>
       <c r="B2" s="36" t="n">
-        <v>9634</v>
+        <v>5955</v>
       </c>
       <c r="C2" s="36" t="n">
-        <v>8811</v>
+        <v>6199</v>
       </c>
       <c r="D2" s="36" t="n">
-        <v>6869</v>
+        <v>5549</v>
       </c>
       <c r="E2" s="36" t="n">
-        <v>7502</v>
+        <v>4499</v>
       </c>
       <c r="F2" s="36" t="n">
-        <v>6818</v>
+        <v>4467</v>
       </c>
       <c r="G2" s="36" t="n">
-        <v>9439</v>
+        <v>4961</v>
       </c>
       <c r="H2" s="36" t="n">
-        <v>8025</v>
+        <v>5283</v>
       </c>
       <c r="I2" s="36" t="n">
-        <v>7240</v>
+        <v>5266</v>
       </c>
       <c r="J2" s="36" t="n">
-        <v>6763</v>
+        <v>6161</v>
       </c>
       <c r="K2" s="36" t="n">
-        <v>5550</v>
+        <v>7094</v>
       </c>
       <c r="L2" s="36" t="n">
-        <v>5282</v>
+        <v>7641</v>
       </c>
       <c r="M2" s="36" t="n">
-        <v>5657</v>
+        <v>5908</v>
       </c>
       <c r="N2" s="36" t="n">
-        <v>6572</v>
+        <v>6665</v>
       </c>
       <c r="O2" s="37" t="n">
-        <v>6092</v>
+        <v>7008</v>
       </c>
     </row>
     <row r="3">
@@ -639,46 +639,44 @@
         </is>
       </c>
       <c r="B3" s="36" t="n">
-        <v>667</v>
+        <v>698</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>778</v>
+        <v>711</v>
       </c>
       <c r="D3" s="36" t="n">
-        <v>676</v>
+        <v>625</v>
       </c>
       <c r="E3" s="36" t="n">
-        <v>536</v>
+        <v>555</v>
       </c>
       <c r="F3" s="36" t="n">
-        <v>572</v>
+        <v>526</v>
       </c>
       <c r="G3" s="36" t="n">
-        <v>548</v>
-      </c>
-      <c r="H3" s="36" t="n">
-        <v>191</v>
-      </c>
+        <v>540</v>
+      </c>
+      <c r="H3" s="36" t="n"/>
       <c r="I3" s="36" t="n">
-        <v>338</v>
+        <v>556</v>
       </c>
       <c r="J3" s="36" t="n">
-        <v>629</v>
+        <v>714</v>
       </c>
       <c r="K3" s="36" t="n">
-        <v>782</v>
+        <v>837</v>
       </c>
       <c r="L3" s="36" t="n">
-        <v>824</v>
+        <v>851</v>
       </c>
       <c r="M3" s="36" t="n">
-        <v>750</v>
+        <v>605</v>
       </c>
       <c r="N3" s="36" t="n">
-        <v>674</v>
+        <v>736</v>
       </c>
       <c r="O3" s="37" t="n">
-        <v>870</v>
+        <v>838</v>
       </c>
     </row>
     <row r="4">
@@ -688,46 +686,44 @@
         </is>
       </c>
       <c r="B4" s="38" t="n">
-        <v>0.069234</v>
+        <v>0.117212</v>
       </c>
       <c r="C4" s="38" t="n">
-        <v>0.088299</v>
+        <v>0.114696</v>
       </c>
       <c r="D4" s="38" t="n">
-        <v>0.098413</v>
+        <v>0.112633</v>
       </c>
       <c r="E4" s="38" t="n">
-        <v>0.071448</v>
+        <v>0.123361</v>
       </c>
       <c r="F4" s="38" t="n">
-        <v>0.083896</v>
+        <v>0.117752</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>0.058057</v>
-      </c>
-      <c r="H4" s="38" t="n">
-        <v>0.023801</v>
-      </c>
+        <v>0.108849</v>
+      </c>
+      <c r="H4" s="38" t="n"/>
       <c r="I4" s="38" t="n">
-        <v>0.046685</v>
+        <v>0.105583</v>
       </c>
       <c r="J4" s="38" t="n">
-        <v>0.09300600000000001</v>
+        <v>0.11589</v>
       </c>
       <c r="K4" s="38" t="n">
-        <v>0.140901</v>
+        <v>0.117987</v>
       </c>
       <c r="L4" s="38" t="n">
-        <v>0.156002</v>
+        <v>0.111373</v>
       </c>
       <c r="M4" s="38" t="n">
-        <v>0.132579</v>
+        <v>0.102404</v>
       </c>
       <c r="N4" s="38" t="n">
-        <v>0.102556</v>
+        <v>0.110428</v>
       </c>
       <c r="O4" s="39" t="n">
-        <v>0.14281</v>
+        <v>0.119578</v>
       </c>
     </row>
     <row r="5">
@@ -786,46 +782,44 @@
         </is>
       </c>
       <c r="B6" s="36" t="n">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="E6" s="36" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="F6" s="36" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G6" s="36" t="n">
-        <v>134</v>
-      </c>
-      <c r="H6" s="36" t="n">
-        <v>46</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="H6" s="36" t="n"/>
       <c r="I6" s="36" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="J6" s="36" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="K6" s="36" t="n">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="L6" s="36" t="n">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="M6" s="36" t="n">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="N6" s="36" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="O6" s="37" t="n">
-        <v>234</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7">
@@ -835,46 +829,44 @@
         </is>
       </c>
       <c r="B7" s="38" t="n">
-        <v>0.194903</v>
+        <v>0.160458</v>
       </c>
       <c r="C7" s="38" t="n">
-        <v>0.173522</v>
+        <v>0.178622</v>
       </c>
       <c r="D7" s="38" t="n">
-        <v>0.156805</v>
+        <v>0.1488</v>
       </c>
       <c r="E7" s="38" t="n">
-        <v>0.188433</v>
+        <v>0.2</v>
       </c>
       <c r="F7" s="38" t="n">
-        <v>0.174825</v>
+        <v>0.180608</v>
       </c>
       <c r="G7" s="38" t="n">
-        <v>0.244526</v>
-      </c>
-      <c r="H7" s="38" t="n">
-        <v>0.240838</v>
-      </c>
+        <v>0.242593</v>
+      </c>
+      <c r="H7" s="38" t="n"/>
       <c r="I7" s="38" t="n">
-        <v>0.168639</v>
+        <v>0.167266</v>
       </c>
       <c r="J7" s="38" t="n">
-        <v>0.151033</v>
+        <v>0.156863</v>
       </c>
       <c r="K7" s="38" t="n">
-        <v>0.185422</v>
+        <v>0.218638</v>
       </c>
       <c r="L7" s="38" t="n">
-        <v>0.231796</v>
+        <v>0.239718</v>
       </c>
       <c r="M7" s="38" t="n">
-        <v>0.254667</v>
+        <v>0.257851</v>
       </c>
       <c r="N7" s="38" t="n">
-        <v>0.237389</v>
+        <v>0.235054</v>
       </c>
       <c r="O7" s="39" t="n">
-        <v>0.268966</v>
+        <v>0.263723</v>
       </c>
     </row>
     <row r="8">
@@ -884,46 +876,44 @@
         </is>
       </c>
       <c r="B8" s="36" t="n">
-        <v>647</v>
+        <v>675</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>745</v>
+        <v>682</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>652</v>
+        <v>607</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>521</v>
+        <v>536</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>551</v>
+        <v>506</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>529</v>
-      </c>
-      <c r="H8" s="36" t="n">
-        <v>183</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="H8" s="36" t="n"/>
       <c r="I8" s="36" t="n">
-        <v>330</v>
+        <v>545</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>605</v>
+        <v>688</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>758</v>
+        <v>802</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>799</v>
+        <v>836</v>
       </c>
       <c r="M8" s="36" t="n">
-        <v>733</v>
+        <v>589</v>
       </c>
       <c r="N8" s="36" t="n">
-        <v>659</v>
+        <v>717</v>
       </c>
       <c r="O8" s="37" t="n">
-        <v>850</v>
+        <v>815</v>
       </c>
     </row>
     <row r="9">
@@ -950,9 +940,7 @@
       <c r="G9" s="36" t="n">
         <v>102</v>
       </c>
-      <c r="H9" s="36" t="n">
-        <v>86</v>
-      </c>
+      <c r="H9" s="36" t="n"/>
       <c r="I9" s="36" t="n">
         <v>51</v>
       </c>
@@ -982,46 +970,44 @@
         </is>
       </c>
       <c r="B10" s="38" t="n">
-        <v>0.109737</v>
+        <v>0.105185</v>
       </c>
       <c r="C10" s="38" t="n">
-        <v>0.097987</v>
+        <v>0.107038</v>
       </c>
       <c r="D10" s="38" t="n">
-        <v>0.075153</v>
+        <v>0.08072500000000001</v>
       </c>
       <c r="E10" s="38" t="n">
-        <v>0.126679</v>
+        <v>0.123134</v>
       </c>
       <c r="F10" s="38" t="n">
-        <v>0.117967</v>
+        <v>0.128458</v>
       </c>
       <c r="G10" s="38" t="n">
-        <v>0.192817</v>
-      </c>
-      <c r="H10" s="38" t="n">
-        <v>0.469945</v>
-      </c>
+        <v>0.196154</v>
+      </c>
+      <c r="H10" s="38" t="n"/>
       <c r="I10" s="38" t="n">
-        <v>0.154545</v>
+        <v>0.09357799999999999</v>
       </c>
       <c r="J10" s="38" t="n">
-        <v>0.110744</v>
+        <v>0.097384</v>
       </c>
       <c r="K10" s="38" t="n">
-        <v>0.187335</v>
+        <v>0.177057</v>
       </c>
       <c r="L10" s="38" t="n">
-        <v>0.111389</v>
+        <v>0.106459</v>
       </c>
       <c r="M10" s="38" t="n">
-        <v>0.114598</v>
+        <v>0.142615</v>
       </c>
       <c r="N10" s="38" t="n">
-        <v>0.107739</v>
+        <v>0.099024</v>
       </c>
       <c r="O10" s="39" t="n">
-        <v>0.105882</v>
+        <v>0.110429</v>
       </c>
     </row>
     <row r="11">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="R36de8ed5c9144aa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="R3fc45d5f1a8c458c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="Rf24398fbb2c64251"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="R2adc7b91a6384635"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -635,46 +635,46 @@
         <x:v>平均会话轮次</x:v>
       </x:c>
       <x:c r="B5" s="28" t="n">
-        <x:v>1.3047337278106508</x:v>
+        <x:v>1.2931654676258992</x:v>
       </x:c>
       <x:c r="C5" s="28" t="n">
-        <x:v>1.2496025437201908</x:v>
+        <x:v>1.2661064425770308</x:v>
       </x:c>
       <x:c r="D5" s="28" t="n">
-        <x:v>1.3162612035851473</x:v>
+        <x:v>1.3882915173237753</x:v>
       </x:c>
       <x:c r="E5" s="28" t="n">
-        <x:v>1.4320388349514563</x:v>
+        <x:v>1.4923619271445359</x:v>
       </x:c>
       <x:c r="F5" s="28" t="n">
-        <x:v>1.5826666666666667</x:v>
+        <x:v>1.5742574257425743</x:v>
       </x:c>
       <x:c r="G5" s="28" t="n">
-        <x:v>1.467359050445104</x:v>
+        <x:v>1.497282608695652</x:v>
       </x:c>
       <x:c r="H5" s="28" t="n">
-        <x:v>1.607717041800643</x:v>
+        <x:v>1.5763723150357996</x:v>
       </x:c>
       <x:c r="I5" s="28" t="n">
-        <x:v>1.4288747346072186</x:v>
+        <x:v>1.4634146341463414</x:v>
       </x:c>
       <x:c r="J5" s="28" t="n">
-        <x:v>1.527214514407684</x:v>
+        <x:v>1.5452436194895591</x:v>
       </x:c>
       <x:c r="K5" s="28" t="n">
-        <x:v>1.4892086330935252</x:v>
+        <x:v>1.4705882352941178</x:v>
       </x:c>
       <x:c r="L5" s="28" t="n">
-        <x:v>1.5254237288135593</x:v>
+        <x:v>1.5816326530612246</x:v>
       </x:c>
       <x:c r="M5" s="28" t="n">
-        <x:v>1.633969118982743</x:v>
+        <x:v>1.624</x:v>
       </x:c>
       <x:c r="N5" s="28" t="n">
-        <x:v>1.5922421948912016</x:v>
+        <x:v>1.5313152400835073</x:v>
       </x:c>
       <x:c r="O5" s="29" t="n">
-        <x:v>1.456973293768546</x:v>
+        <x:v>1.5749525616698292</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -682,46 +682,46 @@
         <x:v>2V2会话用户数</x:v>
       </x:c>
       <x:c r="B6" s="24" t="n">
-        <x:v>57</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C6" s="24" t="n">
-        <x:v>95</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D6" s="24" t="n">
-        <x:v>145</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="E6" s="24" t="n">
-        <x:v>191</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="F6" s="24" t="n">
-        <x:v>191</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G6" s="24" t="n">
-        <x:v>160</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="H6" s="24" t="n">
-        <x:v>82</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="I6" s="24" t="n">
-        <x:v>105</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="J6" s="24" t="n">
-        <x:v>235</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="K6" s="24" t="n">
-        <x:v>226</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="L6" s="24" t="n">
-        <x:v>219</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="M6" s="24" t="n">
-        <x:v>293</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="N6" s="24" t="n">
-        <x:v>277</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="O6" s="25" t="n">
-        <x:v>75</x:v>
+        <x:v>391</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -729,46 +729,46 @@
         <x:v>2V2会话用户占比</x:v>
       </x:c>
       <x:c r="B7" s="26" t="n">
-        <x:v>0.09149277688603531</x:v>
+        <x:v>0.1492776886035313</x:v>
       </x:c>
       <x:c r="C7" s="26" t="n">
-        <x:v>0.11860174781523096</x:v>
+        <x:v>0.13982521847690388</x:v>
       </x:c>
       <x:c r="D7" s="26" t="n">
-        <x:v>0.1623740201567749</x:v>
+        <x:v>0.20492721164613661</x:v>
       </x:c>
       <x:c r="E7" s="26" t="n">
-        <x:v>0.21753986332574032</x:v>
+        <x:v>0.23234624145785876</x:v>
       </x:c>
       <x:c r="F7" s="26" t="n">
-        <x:v>0.29984301412872844</x:v>
+        <x:v>0.24489795918367346</x:v>
       </x:c>
       <x:c r="G7" s="26" t="n">
-        <x:v>0.2127659574468085</x:v>
+        <x:v>0.2300531914893617</x:v>
       </x:c>
       <x:c r="H7" s="26" t="n">
-        <x:v>0.09738717339667459</x:v>
+        <x:v>0.26247030878859856</x:v>
       </x:c>
       <x:c r="I7" s="26" t="n">
-        <x:v>0.11525795828759605</x:v>
+        <x:v>0.22502744237102085</x:v>
       </x:c>
       <x:c r="J7" s="26" t="n">
-        <x:v>0.269804822043628</x:v>
+        <x:v>0.2675086107921929</x:v>
       </x:c>
       <x:c r="K7" s="26" t="n">
-        <x:v>0.2857142857142857</x:v>
+        <x:v>0.2579013906447535</x:v>
       </x:c>
       <x:c r="L7" s="26" t="n">
-        <x:v>0.25435540069686413</x:v>
+        <x:v>0.2659698025551684</x:v>
       </x:c>
       <x:c r="M7" s="26" t="n">
-        <x:v>0.24016393442622952</x:v>
+        <x:v>0.2639344262295082</x:v>
       </x:c>
       <x:c r="N7" s="26" t="n">
-        <x:v>0.29499467518636846</x:v>
+        <x:v>0.25133120340788073</x:v>
       </x:c>
       <x:c r="O7" s="27" t="n">
-        <x:v>0.048046124279308135</x:v>
+        <x:v>0.2504804612427931</x:v>
       </x:c>
     </x:row>
     <x:row r="8">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="Rf24398fbb2c64251"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="R2adc7b91a6384635"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="Rac2dbdbe00f1475c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="Rbb401b44fc2346ba"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="Rac2dbdbe00f1475c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="Rbb401b44fc2346ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="Refbb3f3ffd574b84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="R81bbc3cfc07d4c0f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -540,123 +540,57 @@
       <x:c r="A3" s="19" t="str">
         <x:v>使用AI用户数</x:v>
       </x:c>
-      <x:c r="B3" s="24" t="n">
-        <x:v>623</x:v>
-      </x:c>
-      <x:c r="C3" s="24" t="n">
-        <x:v>801</x:v>
-      </x:c>
-      <x:c r="D3" s="24" t="n">
-        <x:v>893</x:v>
-      </x:c>
-      <x:c r="E3" s="24" t="n">
-        <x:v>878</x:v>
-      </x:c>
-      <x:c r="F3" s="24" t="n">
-        <x:v>637</x:v>
-      </x:c>
-      <x:c r="G3" s="24" t="n">
-        <x:v>752</x:v>
-      </x:c>
-      <x:c r="H3" s="24" t="n">
-        <x:v>842</x:v>
-      </x:c>
-      <x:c r="I3" s="24" t="n">
-        <x:v>911</x:v>
-      </x:c>
+      <x:c r="B3" s="24"/>
+      <x:c r="C3" s="24"/>
+      <x:c r="D3" s="24"/>
+      <x:c r="E3" s="24"/>
+      <x:c r="F3" s="24"/>
+      <x:c r="G3" s="24"/>
+      <x:c r="H3" s="24"/>
+      <x:c r="I3" s="24"/>
       <x:c r="J3" s="24" t="n">
         <x:v>871</x:v>
       </x:c>
-      <x:c r="K3" s="24" t="n">
-        <x:v>791</x:v>
-      </x:c>
-      <x:c r="L3" s="24" t="n">
-        <x:v>861</x:v>
-      </x:c>
-      <x:c r="M3" s="24" t="n">
-        <x:v>1220</x:v>
-      </x:c>
-      <x:c r="N3" s="24" t="n">
-        <x:v>939</x:v>
-      </x:c>
-      <x:c r="O3" s="25" t="n">
-        <x:v>1561</x:v>
-      </x:c>
+      <x:c r="K3" s="24"/>
+      <x:c r="L3" s="24"/>
+      <x:c r="M3" s="24"/>
+      <x:c r="N3" s="24"/>
+      <x:c r="O3" s="25"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="19" t="str">
         <x:v>AI-UV渗透</x:v>
       </x:c>
-      <x:c r="B4" s="26" t="n">
-        <x:v>0.11830611469806304</x:v>
-      </x:c>
-      <x:c r="C4" s="26" t="n">
-        <x:v>0.13001136179191689</x:v>
-      </x:c>
-      <x:c r="D4" s="26" t="n">
-        <x:v>0.12588102621934028</x:v>
-      </x:c>
-      <x:c r="E4" s="26" t="n">
-        <x:v>0.11490642586048946</x:v>
-      </x:c>
-      <x:c r="F4" s="26" t="n">
-        <x:v>0.10781990521327015</x:v>
-      </x:c>
-      <x:c r="G4" s="26" t="n">
-        <x:v>0.11282820705176294</x:v>
-      </x:c>
-      <x:c r="H4" s="26" t="n">
-        <x:v>0.11457341134848278</x:v>
-      </x:c>
-      <x:c r="I4" s="26" t="n">
-        <x:v>0.11047780742178026</x:v>
-      </x:c>
+      <x:c r="B4" s="26"/>
+      <x:c r="C4" s="26"/>
+      <x:c r="D4" s="26"/>
+      <x:c r="E4" s="26"/>
+      <x:c r="F4" s="26"/>
+      <x:c r="G4" s="26"/>
+      <x:c r="H4" s="26"/>
+      <x:c r="I4" s="26"/>
       <x:c r="J4" s="26" t="n">
         <x:v>0.13023325358851676</x:v>
       </x:c>
-      <x:c r="K4" s="26" t="n">
-        <x:v>0.12269272529858849</x:v>
-      </x:c>
-      <x:c r="L4" s="26" t="n">
-        <x:v>0.1174144279285422</x:v>
-      </x:c>
-      <x:c r="M4" s="26" t="n">
-        <x:v>0.1388098759813403</x:v>
-      </x:c>
-      <x:c r="N4" s="26" t="n">
-        <x:v>0.13154945362846734</x:v>
-      </x:c>
-      <x:c r="O4" s="27" t="n">
-        <x:v>0.13148584905660377</x:v>
-      </x:c>
+      <x:c r="K4" s="26"/>
+      <x:c r="L4" s="26"/>
+      <x:c r="M4" s="26"/>
+      <x:c r="N4" s="26"/>
+      <x:c r="O4" s="27"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="19" t="str">
         <x:v>平均会话轮次</x:v>
       </x:c>
-      <x:c r="B5" s="28" t="n">
-        <x:v>1.2931654676258992</x:v>
-      </x:c>
-      <x:c r="C5" s="28" t="n">
-        <x:v>1.2661064425770308</x:v>
-      </x:c>
-      <x:c r="D5" s="28" t="n">
-        <x:v>1.3882915173237753</x:v>
-      </x:c>
-      <x:c r="E5" s="28" t="n">
-        <x:v>1.4923619271445359</x:v>
-      </x:c>
-      <x:c r="F5" s="28" t="n">
-        <x:v>1.5742574257425743</x:v>
-      </x:c>
-      <x:c r="G5" s="28" t="n">
-        <x:v>1.497282608695652</x:v>
-      </x:c>
-      <x:c r="H5" s="28" t="n">
-        <x:v>1.5763723150357996</x:v>
-      </x:c>
+      <x:c r="B5" s="28"/>
+      <x:c r="C5" s="28"/>
+      <x:c r="D5" s="28"/>
+      <x:c r="E5" s="28"/>
+      <x:c r="F5" s="28"/>
+      <x:c r="G5" s="28"/>
+      <x:c r="H5" s="28"/>
       <x:c r="I5" s="28" t="n">
-        <x:v>1.4634146341463414</x:v>
+        <x:v>1.460088691796009</x:v>
       </x:c>
       <x:c r="J5" s="28" t="n">
         <x:v>1.5452436194895591</x:v>
@@ -674,34 +608,20 @@
         <x:v>1.5313152400835073</x:v>
       </x:c>
       <x:c r="O5" s="29" t="n">
-        <x:v>1.5749525616698292</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="19" t="str">
         <x:v>2V2会话用户数</x:v>
       </x:c>
-      <x:c r="B6" s="24" t="n">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="C6" s="24" t="n">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D6" s="24" t="n">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="E6" s="24" t="n">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="F6" s="24" t="n">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="G6" s="24" t="n">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="H6" s="24" t="n">
-        <x:v>221</x:v>
-      </x:c>
+      <x:c r="B6" s="24"/>
+      <x:c r="C6" s="24"/>
+      <x:c r="D6" s="24"/>
+      <x:c r="E6" s="24"/>
+      <x:c r="F6" s="24"/>
+      <x:c r="G6" s="24"/>
+      <x:c r="H6" s="24"/>
       <x:c r="I6" s="24" t="n">
         <x:v>205</x:v>
       </x:c>
@@ -721,101 +641,75 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="O6" s="25" t="n">
-        <x:v>391</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="19" t="str">
         <x:v>2V2会话用户占比</x:v>
       </x:c>
-      <x:c r="B7" s="26" t="n">
-        <x:v>0.1492776886035313</x:v>
-      </x:c>
-      <x:c r="C7" s="26" t="n">
-        <x:v>0.13982521847690388</x:v>
-      </x:c>
-      <x:c r="D7" s="26" t="n">
-        <x:v>0.20492721164613661</x:v>
-      </x:c>
-      <x:c r="E7" s="26" t="n">
-        <x:v>0.23234624145785876</x:v>
-      </x:c>
-      <x:c r="F7" s="26" t="n">
-        <x:v>0.24489795918367346</x:v>
-      </x:c>
-      <x:c r="G7" s="26" t="n">
-        <x:v>0.2300531914893617</x:v>
-      </x:c>
-      <x:c r="H7" s="26" t="n">
-        <x:v>0.26247030878859856</x:v>
-      </x:c>
-      <x:c r="I7" s="26" t="n">
-        <x:v>0.22502744237102085</x:v>
-      </x:c>
+      <x:c r="B7" s="26"/>
+      <x:c r="C7" s="26"/>
+      <x:c r="D7" s="26"/>
+      <x:c r="E7" s="26"/>
+      <x:c r="F7" s="26"/>
+      <x:c r="G7" s="26"/>
+      <x:c r="H7" s="26"/>
+      <x:c r="I7" s="26"/>
       <x:c r="J7" s="26" t="n">
         <x:v>0.2675086107921929</x:v>
       </x:c>
-      <x:c r="K7" s="26" t="n">
-        <x:v>0.2579013906447535</x:v>
-      </x:c>
-      <x:c r="L7" s="26" t="n">
-        <x:v>0.2659698025551684</x:v>
-      </x:c>
-      <x:c r="M7" s="26" t="n">
-        <x:v>0.2639344262295082</x:v>
-      </x:c>
-      <x:c r="N7" s="26" t="n">
-        <x:v>0.25133120340788073</x:v>
-      </x:c>
-      <x:c r="O7" s="27" t="n">
-        <x:v>0.2504804612427931</x:v>
-      </x:c>
+      <x:c r="K7" s="26"/>
+      <x:c r="L7" s="26"/>
+      <x:c r="M7" s="26"/>
+      <x:c r="N7" s="26"/>
+      <x:c r="O7" s="27"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="19" t="str">
         <x:v>推荐产品卡片曝光数</x:v>
       </x:c>
       <x:c r="B8" s="24" t="n">
-        <x:v>232</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C8" s="24" t="n">
-        <x:v>313</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="24" t="n">
-        <x:v>565</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E8" s="24" t="n">
-        <x:v>643</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F8" s="24" t="n">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G8" s="24" t="n">
-        <x:v>556</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="24" t="n">
-        <x:v>641</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I8" s="24" t="n">
-        <x:v>691</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J8" s="24" t="n">
-        <x:v>677</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K8" s="24" t="n">
-        <x:v>603</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L8" s="24" t="n">
-        <x:v>588</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="M8" s="24" t="n">
-        <x:v>797</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="N8" s="24" t="n">
-        <x:v>604</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="O8" s="25" t="n">
-        <x:v>1034</x:v>
+        <x:v>987</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -823,94 +717,68 @@
         <x:v>推荐产品卡片点击数</x:v>
       </x:c>
       <x:c r="B9" s="24" t="n">
-        <x:v>54</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C9" s="24" t="n">
-        <x:v>69</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="24" t="n">
-        <x:v>143</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E9" s="24" t="n">
-        <x:v>89</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F9" s="24" t="n">
-        <x:v>83</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G9" s="24" t="n">
-        <x:v>68</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="24" t="n">
-        <x:v>89</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I9" s="24" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J9" s="24" t="n">
-        <x:v>111</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K9" s="24" t="n">
-        <x:v>105</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L9" s="24" t="n">
-        <x:v>109</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="M9" s="24" t="n">
-        <x:v>167</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="N9" s="24" t="n">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="O9" s="25" t="n">
-        <x:v>209</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="19" t="str">
         <x:v>推荐产品CTR</x:v>
       </x:c>
-      <x:c r="B10" s="26" t="n">
-        <x:v>0.3723916532905297</x:v>
-      </x:c>
-      <x:c r="C10" s="26" t="n">
-        <x:v>0.39076154806491886</x:v>
-      </x:c>
-      <x:c r="D10" s="26" t="n">
-        <x:v>0.6326987681970885</x:v>
-      </x:c>
-      <x:c r="E10" s="26" t="n">
-        <x:v>0.7323462414578588</x:v>
-      </x:c>
-      <x:c r="F10" s="26" t="n">
-        <x:v>0.7849293563579278</x:v>
-      </x:c>
-      <x:c r="G10" s="26" t="n">
-        <x:v>0.7393617021276596</x:v>
-      </x:c>
-      <x:c r="H10" s="26" t="n">
-        <x:v>0.7612826603325415</x:v>
-      </x:c>
-      <x:c r="I10" s="26" t="n">
-        <x:v>0.7585071350164654</x:v>
-      </x:c>
+      <x:c r="B10" s="26"/>
+      <x:c r="C10" s="26"/>
+      <x:c r="D10" s="26"/>
+      <x:c r="E10" s="26"/>
+      <x:c r="F10" s="26"/>
+      <x:c r="G10" s="26"/>
+      <x:c r="H10" s="26"/>
+      <x:c r="I10" s="26"/>
       <x:c r="J10" s="26" t="n">
-        <x:v>0.7772675086107922</x:v>
-      </x:c>
-      <x:c r="K10" s="26" t="n">
-        <x:v>0.7623261694058154</x:v>
-      </x:c>
-      <x:c r="L10" s="26" t="n">
-        <x:v>0.6829268292682927</x:v>
-      </x:c>
-      <x:c r="M10" s="26" t="n">
-        <x:v>0.6532786885245901</x:v>
-      </x:c>
-      <x:c r="N10" s="26" t="n">
-        <x:v>0.6432374866879659</x:v>
-      </x:c>
-      <x:c r="O10" s="27" t="n">
-        <x:v>0.6623959000640615</x:v>
-      </x:c>
+        <x:v>0.03444316877152698</x:v>
+      </x:c>
+      <x:c r="K10" s="26"/>
+      <x:c r="L10" s="26"/>
+      <x:c r="M10" s="26"/>
+      <x:c r="N10" s="26"/>
+      <x:c r="O10" s="27"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="19" t="str">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="Refbb3f3ffd574b84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="R81bbc3cfc07d4c0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="R9d298649f2604055"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="R75254dc49712416d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -547,15 +547,27 @@
       <x:c r="F3" s="24"/>
       <x:c r="G3" s="24"/>
       <x:c r="H3" s="24"/>
-      <x:c r="I3" s="24"/>
+      <x:c r="I3" s="24" t="n">
+        <x:v>911</x:v>
+      </x:c>
       <x:c r="J3" s="24" t="n">
         <x:v>871</x:v>
       </x:c>
-      <x:c r="K3" s="24"/>
-      <x:c r="L3" s="24"/>
-      <x:c r="M3" s="24"/>
-      <x:c r="N3" s="24"/>
-      <x:c r="O3" s="25"/>
+      <x:c r="K3" s="24" t="n">
+        <x:v>791</x:v>
+      </x:c>
+      <x:c r="L3" s="24" t="n">
+        <x:v>861</x:v>
+      </x:c>
+      <x:c r="M3" s="24" t="n">
+        <x:v>1220</x:v>
+      </x:c>
+      <x:c r="N3" s="24" t="n">
+        <x:v>939</x:v>
+      </x:c>
+      <x:c r="O3" s="25" t="n">
+        <x:v>1561</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="19" t="str">
@@ -568,15 +580,27 @@
       <x:c r="F4" s="26"/>
       <x:c r="G4" s="26"/>
       <x:c r="H4" s="26"/>
-      <x:c r="I4" s="26"/>
+      <x:c r="I4" s="26" t="n">
+        <x:v>0.11047780742178026</x:v>
+      </x:c>
       <x:c r="J4" s="26" t="n">
         <x:v>0.13023325358851676</x:v>
       </x:c>
-      <x:c r="K4" s="26"/>
-      <x:c r="L4" s="26"/>
-      <x:c r="M4" s="26"/>
-      <x:c r="N4" s="26"/>
-      <x:c r="O4" s="27"/>
+      <x:c r="K4" s="26" t="n">
+        <x:v>0.12269272529858849</x:v>
+      </x:c>
+      <x:c r="L4" s="26" t="n">
+        <x:v>0.1174144279285422</x:v>
+      </x:c>
+      <x:c r="M4" s="26" t="n">
+        <x:v>0.1388098759813403</x:v>
+      </x:c>
+      <x:c r="N4" s="26" t="n">
+        <x:v>0.13154945362846734</x:v>
+      </x:c>
+      <x:c r="O4" s="27" t="n">
+        <x:v>0.13148584905660377</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="19" t="str">
@@ -655,15 +679,27 @@
       <x:c r="F7" s="26"/>
       <x:c r="G7" s="26"/>
       <x:c r="H7" s="26"/>
-      <x:c r="I7" s="26"/>
+      <x:c r="I7" s="26" t="n">
+        <x:v>0.22502744237102085</x:v>
+      </x:c>
       <x:c r="J7" s="26" t="n">
         <x:v>0.2675086107921929</x:v>
       </x:c>
-      <x:c r="K7" s="26"/>
-      <x:c r="L7" s="26"/>
-      <x:c r="M7" s="26"/>
-      <x:c r="N7" s="26"/>
-      <x:c r="O7" s="27"/>
+      <x:c r="K7" s="26" t="n">
+        <x:v>0.2579013906447535</x:v>
+      </x:c>
+      <x:c r="L7" s="26" t="n">
+        <x:v>0.2659698025551684</x:v>
+      </x:c>
+      <x:c r="M7" s="26" t="n">
+        <x:v>0.2639344262295082</x:v>
+      </x:c>
+      <x:c r="N7" s="26" t="n">
+        <x:v>0.25133120340788073</x:v>
+      </x:c>
+      <x:c r="O7" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="19" t="str">
@@ -770,15 +806,27 @@
       <x:c r="F10" s="26"/>
       <x:c r="G10" s="26"/>
       <x:c r="H10" s="26"/>
-      <x:c r="I10" s="26"/>
+      <x:c r="I10" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J10" s="26" t="n">
         <x:v>0.03444316877152698</x:v>
       </x:c>
-      <x:c r="K10" s="26"/>
-      <x:c r="L10" s="26"/>
-      <x:c r="M10" s="26"/>
-      <x:c r="N10" s="26"/>
-      <x:c r="O10" s="27"/>
+      <x:c r="K10" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L10" s="26" t="n">
+        <x:v>0.6399535423925667</x:v>
+      </x:c>
+      <x:c r="M10" s="26" t="n">
+        <x:v>0.6245901639344262</x:v>
+      </x:c>
+      <x:c r="N10" s="26" t="n">
+        <x:v>0.6198083067092651</x:v>
+      </x:c>
+      <x:c r="O10" s="27" t="n">
+        <x:v>0.6322869955156951</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="19" t="str">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="R9d298649f2604055"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="R75254dc49712416d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并数据表" sheetId="1" r:id="Rc6a6b00055b94734"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="2" r:id="Racaa6d1b86dd4dd1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -811,7 +811,7 @@
         <v>277</v>
       </c>
       <c r="H6" s="4">
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="I6" s="4">
         <v>319</v>
@@ -858,7 +858,7 @@
         <v>0.29499467518636846</v>
       </c>
       <c r="H7" s="5">
-        <v>0</v>
+        <v>0.24731</v>
       </c>
       <c r="I7" s="5">
         <v>0.2396694214876033</v>

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -749,7 +749,7 @@
         <v>1.4288747346072186</v>
       </c>
       <c r="C5" s="6">
-        <v>1.527214514407684</v>
+        <v>1.525641</v>
       </c>
       <c r="D5" s="6">
         <v>1.4892086330935252</v>
@@ -764,7 +764,7 @@
         <v>1.5922421948912016</v>
       </c>
       <c r="H5" s="6">
-        <v>1</v>
+        <v>1.58227</v>
       </c>
       <c r="I5" s="6">
         <v>1.4867060561299852</v>
@@ -796,7 +796,7 @@
         <v>105</v>
       </c>
       <c r="C6" s="4">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D6" s="4">
         <v>226</v>
@@ -811,7 +811,7 @@
         <v>277</v>
       </c>
       <c r="H6" s="4">
-        <v>391</v>
+        <v>342</v>
       </c>
       <c r="I6" s="4">
         <v>319</v>
@@ -843,7 +843,7 @@
         <v>0.11525795828759605</v>
       </c>
       <c r="C7" s="5">
-        <v>0.269804822043628</v>
+        <v>0.26866</v>
       </c>
       <c r="D7" s="5">
         <v>0.2857142857142857</v>
@@ -858,7 +858,7 @@
         <v>0.29499467518636846</v>
       </c>
       <c r="H7" s="5">
-        <v>0.24731</v>
+        <v>0.21909</v>
       </c>
       <c r="I7" s="5">
         <v>0.2396694214876033</v>

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -746,7 +746,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>1.4288747346072186</v>
+        <v>1.460089</v>
       </c>
       <c r="C5" s="6">
         <v>1.525641</v>
@@ -793,7 +793,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>105</v>
+        <v>205</v>
       </c>
       <c r="C6" s="4">
         <v>234</v>
@@ -840,7 +840,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="5">
-        <v>0.11525795828759605</v>
+        <v>0.22503</v>
       </c>
       <c r="C7" s="5">
         <v>0.26866</v>

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -749,22 +749,22 @@
         <v>1.460089</v>
       </c>
       <c r="C5" s="6">
-        <v>1.525641</v>
+        <v>1.5452436194895591</v>
       </c>
       <c r="D5" s="6">
-        <v>1.4892086330935252</v>
+        <v>1.4705882352941178</v>
       </c>
       <c r="E5" s="6">
-        <v>1.5254237288135593</v>
+        <v>1.5816326530612246</v>
       </c>
       <c r="F5" s="6">
-        <v>1.633969118982743</v>
+        <v>1.624</v>
       </c>
       <c r="G5" s="6">
-        <v>1.5922421948912016</v>
+        <v>1.5313152400835073</v>
       </c>
       <c r="H5" s="6">
-        <v>1.58227</v>
+        <v>1.5749525616698292</v>
       </c>
       <c r="I5" s="6">
         <v>1.4867060561299852</v>
@@ -796,22 +796,22 @@
         <v>205</v>
       </c>
       <c r="C6" s="4">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D6" s="4">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="E6" s="4">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="F6" s="4">
-        <v>293</v>
+        <v>322</v>
       </c>
       <c r="G6" s="4">
-        <v>277</v>
+        <v>236</v>
       </c>
       <c r="H6" s="4">
-        <v>342</v>
+        <v>391</v>
       </c>
       <c r="I6" s="4">
         <v>319</v>
@@ -843,22 +843,22 @@
         <v>0.22503</v>
       </c>
       <c r="C7" s="5">
-        <v>0.26866</v>
+        <v>0.2675086107921929</v>
       </c>
       <c r="D7" s="5">
-        <v>0.2857142857142857</v>
+        <v>0.2579013906447535</v>
       </c>
       <c r="E7" s="5">
-        <v>0.25435540069686413</v>
+        <v>0.2659698025551684</v>
       </c>
       <c r="F7" s="5">
-        <v>0.24016393442622952</v>
+        <v>0.2639344262295082</v>
       </c>
       <c r="G7" s="5">
-        <v>0.29499467518636846</v>
+        <v>0.25133120340788073</v>
       </c>
       <c r="H7" s="5">
-        <v>0.21909</v>
+        <v>0.2504804612427931</v>
       </c>
       <c r="I7" s="5">
         <v>0.2396694214876033</v>

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -652,46 +652,46 @@
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>911</v>
+        <v>1317</v>
       </c>
       <c r="C3" s="4">
-        <v>871</v>
+        <v>1332</v>
       </c>
       <c r="D3" s="4">
-        <v>791</v>
+        <v>1125</v>
       </c>
       <c r="E3" s="4">
-        <v>861</v>
+        <v>1395</v>
       </c>
       <c r="F3" s="4">
-        <v>1220</v>
+        <v>2030</v>
       </c>
       <c r="G3" s="4">
-        <v>939</v>
+        <v>1467</v>
       </c>
       <c r="H3" s="4">
-        <v>1561</v>
+        <v>2490</v>
       </c>
       <c r="I3" s="4">
-        <v>1331</v>
+        <v>2013</v>
       </c>
       <c r="J3" s="4">
-        <v>1341</v>
+        <v>2002</v>
       </c>
       <c r="K3" s="4">
-        <v>1355</v>
+        <v>2083</v>
       </c>
       <c r="L3" s="4">
-        <v>1495</v>
+        <v>2217</v>
       </c>
       <c r="M3" s="4">
-        <v>1443</v>
+        <v>2125</v>
       </c>
       <c r="N3" s="4">
-        <v>1658</v>
+        <v>2453</v>
       </c>
       <c r="O3" s="4">
-        <v>1418</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -699,46 +699,46 @@
         <v>3</v>
       </c>
       <c r="B4" s="5">
-        <v>0.11047780742178026</v>
+        <v>0.159714</v>
       </c>
       <c r="C4" s="5">
-        <v>0.13023325358851676</v>
+        <v>0.199163</v>
       </c>
       <c r="D4" s="5">
-        <v>0.12269272529858849</v>
+        <v>0.1745</v>
       </c>
       <c r="E4" s="5">
-        <v>0.1174144279285422</v>
+        <v>0.190236</v>
       </c>
       <c r="F4" s="5">
-        <v>0.1388098759813403</v>
+        <v>0.230971</v>
       </c>
       <c r="G4" s="5">
-        <v>0.13154945362846734</v>
+        <v>0.20552</v>
       </c>
       <c r="H4" s="5">
-        <v>0.13148584905660377</v>
+        <v>0.209737</v>
       </c>
       <c r="I4" s="5">
-        <v>0.11678511889093621</v>
+        <v>0.176625</v>
       </c>
       <c r="J4" s="5">
-        <v>0.08350457687278162</v>
+        <v>0.124665</v>
       </c>
       <c r="K4" s="5">
-        <v>0.11649901126300403</v>
+        <v>0.17909</v>
       </c>
       <c r="L4" s="5">
-        <v>0.130169786678276</v>
+        <v>0.193034</v>
       </c>
       <c r="M4" s="5">
-        <v>0.1596768839216554</v>
+        <v>0.235144</v>
       </c>
       <c r="N4" s="5">
-        <v>0.1527547447945458</v>
+        <v>0.226</v>
       </c>
       <c r="O4" s="5">
-        <v>0.15760809158608424</v>
+        <v>0.253307</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -840,46 +840,46 @@
         <v>6</v>
       </c>
       <c r="B7" s="5">
-        <v>0.22503</v>
+        <v>0.155657</v>
       </c>
       <c r="C7" s="5">
-        <v>0.2675086107921929</v>
+        <v>0.174925</v>
       </c>
       <c r="D7" s="5">
-        <v>0.2579013906447535</v>
+        <v>0.181333</v>
       </c>
       <c r="E7" s="5">
-        <v>0.2659698025551684</v>
+        <v>0.164158</v>
       </c>
       <c r="F7" s="5">
-        <v>0.2639344262295082</v>
+        <v>0.158621</v>
       </c>
       <c r="G7" s="5">
-        <v>0.25133120340788073</v>
+        <v>0.160873</v>
       </c>
       <c r="H7" s="5">
-        <v>0.2504804612427931</v>
+        <v>0.157028</v>
       </c>
       <c r="I7" s="5">
-        <v>0.2396694214876033</v>
+        <v>0.15847</v>
       </c>
       <c r="J7" s="5">
-        <v>0.23042505592841164</v>
+        <v>0.154346</v>
       </c>
       <c r="K7" s="5">
-        <v>0.24059040590405903</v>
+        <v>0.156505</v>
       </c>
       <c r="L7" s="5">
-        <v>0.22608695652173913</v>
+        <v>0.152458</v>
       </c>
       <c r="M7" s="5">
-        <v>0.2176022176022176</v>
+        <v>0.147765</v>
       </c>
       <c r="N7" s="5">
-        <v>0.22617611580217128</v>
+        <v>0.152874</v>
       </c>
       <c r="O7" s="5">
-        <v>0.2552891396332863</v>
+        <v>0.158842</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -652,46 +652,46 @@
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>1317</v>
+        <v>902</v>
       </c>
       <c r="C3" s="4">
-        <v>1332</v>
+        <v>862</v>
       </c>
       <c r="D3" s="4">
-        <v>1125</v>
+        <v>765</v>
       </c>
       <c r="E3" s="4">
-        <v>1395</v>
+        <v>882</v>
       </c>
       <c r="F3" s="4">
-        <v>2030</v>
+        <v>1250</v>
       </c>
       <c r="G3" s="4">
-        <v>1467</v>
+        <v>958</v>
       </c>
       <c r="H3" s="4">
-        <v>2490</v>
+        <v>1581</v>
       </c>
       <c r="I3" s="4">
-        <v>2013</v>
+        <v>1354</v>
       </c>
       <c r="J3" s="4">
-        <v>2002</v>
+        <v>1375</v>
       </c>
       <c r="K3" s="4">
-        <v>2083</v>
+        <v>1383</v>
       </c>
       <c r="L3" s="4">
-        <v>2217</v>
+        <v>1532</v>
       </c>
       <c r="M3" s="4">
-        <v>2125</v>
+        <v>1474</v>
       </c>
       <c r="N3" s="4">
-        <v>2453</v>
+        <v>1692</v>
       </c>
       <c r="O3" s="4">
-        <v>2279</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -699,46 +699,46 @@
         <v>3</v>
       </c>
       <c r="B4" s="5">
-        <v>0.159714</v>
+        <v>0.10938636914867815</v>
       </c>
       <c r="C4" s="5">
-        <v>0.199163</v>
+        <v>0.12888755980861244</v>
       </c>
       <c r="D4" s="5">
-        <v>0.1745</v>
+        <v>0.11865984178687762</v>
       </c>
       <c r="E4" s="5">
-        <v>0.190236</v>
+        <v>0.1202781944633847</v>
       </c>
       <c r="F4" s="5">
-        <v>0.230971</v>
+        <v>0.14222323358743885</v>
       </c>
       <c r="G4" s="5">
-        <v>0.20552</v>
+        <v>0.13421126365928832</v>
       </c>
       <c r="H4" s="5">
-        <v>0.209737</v>
+        <v>0.13317048517520216</v>
       </c>
       <c r="I4" s="5">
-        <v>0.176625</v>
+        <v>0.11880319382293586</v>
       </c>
       <c r="J4" s="5">
-        <v>0.124665</v>
+        <v>0.08562176972414222</v>
       </c>
       <c r="K4" s="5">
-        <v>0.17909</v>
+        <v>0.11890637090533918</v>
       </c>
       <c r="L4" s="5">
-        <v>0.193034</v>
+        <v>0.13339138006094906</v>
       </c>
       <c r="M4" s="5">
-        <v>0.235144</v>
+        <v>0.16310722584928627</v>
       </c>
       <c r="N4" s="5">
-        <v>0.226</v>
+        <v>0.1558872305140962</v>
       </c>
       <c r="O4" s="5">
-        <v>0.253307</v>
+        <v>0.17061242636434368</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -746,7 +746,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>1.460089</v>
+        <v>1.460088691796009</v>
       </c>
       <c r="C5" s="6">
         <v>1.5452436194895591</v>
@@ -840,46 +840,46 @@
         <v>6</v>
       </c>
       <c r="B7" s="5">
-        <v>0.155657</v>
+        <v>0.22727272727272727</v>
       </c>
       <c r="C7" s="5">
-        <v>0.174925</v>
+        <v>0.2703016241299304</v>
       </c>
       <c r="D7" s="5">
-        <v>0.181333</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="E7" s="5">
-        <v>0.164158</v>
+        <v>0.25963718820861675</v>
       </c>
       <c r="F7" s="5">
-        <v>0.158621</v>
+        <v>0.2576</v>
       </c>
       <c r="G7" s="5">
-        <v>0.160873</v>
+        <v>0.24634655532359082</v>
       </c>
       <c r="H7" s="5">
-        <v>0.157028</v>
+        <v>0.24731182795698925</v>
       </c>
       <c r="I7" s="5">
-        <v>0.15847</v>
+        <v>0.23559822747415066</v>
       </c>
       <c r="J7" s="5">
-        <v>0.154346</v>
+        <v>0.22472727272727272</v>
       </c>
       <c r="K7" s="5">
-        <v>0.156505</v>
+        <v>0.23571945046999276</v>
       </c>
       <c r="L7" s="5">
-        <v>0.152458</v>
+        <v>0.2206266318537859</v>
       </c>
       <c r="M7" s="5">
-        <v>0.147765</v>
+        <v>0.2130257801899593</v>
       </c>
       <c r="N7" s="5">
-        <v>0.152874</v>
+        <v>0.22163120567375885</v>
       </c>
       <c r="O7" s="5">
-        <v>0.158842</v>
+        <v>0.23583061889250814</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -80,7 +80,7 @@
     <t>统计周期</t>
   </si>
   <si>
-    <t>2026-08-17 至 2026-08-30</t>
+    <t>2026-08-24 至 2026-09-06</t>
   </si>
   <si>
     <t>使用AI用户数 ÷ 网站整体用户数</t>
@@ -558,46 +558,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="2">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="C1" s="2">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="D1" s="2">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="E1" s="2">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="F1" s="2">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="G1" s="2">
-        <v>46256</v>
+        <v>46263</v>
       </c>
       <c r="H1" s="2">
-        <v>46257</v>
+        <v>46264</v>
       </c>
       <c r="I1" s="2">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J1" s="2">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="K1" s="2">
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="L1" s="2">
-        <v>46261</v>
+        <v>46268</v>
       </c>
       <c r="M1" s="2">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="N1" s="2">
-        <v>46263</v>
+        <v>46270</v>
       </c>
       <c r="O1" s="2">
-        <v>46264</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -605,46 +605,46 @@
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>8246</v>
+        <v>11397</v>
       </c>
       <c r="C2" s="4">
-        <v>6688</v>
+        <v>16641</v>
       </c>
       <c r="D2" s="4">
-        <v>6447</v>
+        <v>11635</v>
       </c>
       <c r="E2" s="4">
-        <v>7333</v>
+        <v>11495</v>
       </c>
       <c r="F2" s="4">
-        <v>8789</v>
+        <v>9037</v>
       </c>
       <c r="G2" s="4">
-        <v>7138</v>
+        <v>10856</v>
       </c>
       <c r="H2" s="4">
-        <v>11872</v>
+        <v>9427</v>
       </c>
       <c r="I2" s="4">
-        <v>11397</v>
+        <v>9333</v>
       </c>
       <c r="J2" s="4">
-        <v>16059</v>
+        <v>9414</v>
       </c>
       <c r="K2" s="4">
-        <v>11631</v>
+        <v>10534</v>
       </c>
       <c r="L2" s="4">
-        <v>11485</v>
+        <v>6476</v>
       </c>
       <c r="M2" s="4">
-        <v>9037</v>
+        <v>9101</v>
       </c>
       <c r="N2" s="4">
-        <v>10854</v>
+        <v>8226</v>
       </c>
       <c r="O2" s="4">
-        <v>8997</v>
+        <v>11395</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -652,46 +652,46 @@
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>902</v>
+        <v>1354</v>
       </c>
       <c r="C3" s="4">
-        <v>862</v>
+        <v>1375</v>
       </c>
       <c r="D3" s="4">
-        <v>765</v>
+        <v>1383</v>
       </c>
       <c r="E3" s="4">
-        <v>882</v>
+        <v>1532</v>
       </c>
       <c r="F3" s="4">
-        <v>1250</v>
+        <v>1473</v>
       </c>
       <c r="G3" s="4">
-        <v>958</v>
+        <v>1692</v>
       </c>
       <c r="H3" s="4">
-        <v>1581</v>
+        <v>1534</v>
       </c>
       <c r="I3" s="4">
-        <v>1354</v>
+        <v>1391</v>
       </c>
       <c r="J3" s="4">
-        <v>1375</v>
+        <v>1409</v>
       </c>
       <c r="K3" s="4">
-        <v>1383</v>
+        <v>1584</v>
       </c>
       <c r="L3" s="4">
-        <v>1532</v>
+        <v>1003</v>
       </c>
       <c r="M3" s="4">
-        <v>1474</v>
+        <v>1505</v>
       </c>
       <c r="N3" s="4">
-        <v>1692</v>
+        <v>1284</v>
       </c>
       <c r="O3" s="4">
-        <v>1535</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -699,46 +699,46 @@
         <v>3</v>
       </c>
       <c r="B4" s="5">
-        <v>0.10938636914867815</v>
+        <v>0.11880319382293586</v>
       </c>
       <c r="C4" s="5">
-        <v>0.12888755980861244</v>
+        <v>0.08262724595877652</v>
       </c>
       <c r="D4" s="5">
-        <v>0.11865984178687762</v>
+        <v>0.11886549204984959</v>
       </c>
       <c r="E4" s="5">
-        <v>0.1202781944633847</v>
+        <v>0.1332753371030883</v>
       </c>
       <c r="F4" s="5">
-        <v>0.14222323358743885</v>
+        <v>0.16299656965807238</v>
       </c>
       <c r="G4" s="5">
-        <v>0.13421126365928832</v>
+        <v>0.15585851142225499</v>
       </c>
       <c r="H4" s="5">
-        <v>0.13317048517520216</v>
+        <v>0.16272409037869948</v>
       </c>
       <c r="I4" s="5">
-        <v>0.11880319382293586</v>
+        <v>0.14904103717989928</v>
       </c>
       <c r="J4" s="5">
-        <v>0.08562176972414222</v>
+        <v>0.14967070320798812</v>
       </c>
       <c r="K4" s="5">
-        <v>0.11890637090533918</v>
+        <v>0.1503702297322954</v>
       </c>
       <c r="L4" s="5">
-        <v>0.13339138006094906</v>
+        <v>0.15487955528103767</v>
       </c>
       <c r="M4" s="5">
-        <v>0.16310722584928627</v>
+        <v>0.16536644324799474</v>
       </c>
       <c r="N4" s="5">
-        <v>0.1558872305140962</v>
+        <v>0.1560904449307075</v>
       </c>
       <c r="O4" s="5">
-        <v>0.17061242636434368</v>
+        <v>0.16322948661693726</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -746,46 +746,46 @@
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <v>1.460088691796009</v>
+        <v>1.4867060561299852</v>
       </c>
       <c r="C5" s="6">
-        <v>1.5452436194895591</v>
+        <v>1.456</v>
       </c>
       <c r="D5" s="6">
-        <v>1.4705882352941178</v>
+        <v>1.5061460592913956</v>
       </c>
       <c r="E5" s="6">
-        <v>1.5816326530612246</v>
+        <v>1.4471279373368147</v>
       </c>
       <c r="F5" s="6">
-        <v>1.624</v>
+        <v>1.442634080108622</v>
       </c>
       <c r="G5" s="6">
-        <v>1.5313152400835073</v>
+        <v>1.4497635933806146</v>
       </c>
       <c r="H5" s="6">
-        <v>1.5749525616698292</v>
+        <v>1.485006518904824</v>
       </c>
       <c r="I5" s="6">
-        <v>1.4867060561299852</v>
+        <v>1.3975557153127247</v>
       </c>
       <c r="J5" s="6">
-        <v>1.456</v>
+        <v>1.4300922640170333</v>
       </c>
       <c r="K5" s="6">
-        <v>1.5061460592913956</v>
+        <v>1.4659090909090908</v>
       </c>
       <c r="L5" s="6">
-        <v>1.4471279373368147</v>
+        <v>1.5692921236291126</v>
       </c>
       <c r="M5" s="6">
-        <v>1.4416553595658073</v>
+        <v>1.521594684385382</v>
       </c>
       <c r="N5" s="6">
-        <v>1.4497635933806146</v>
+        <v>1.4742990654205608</v>
       </c>
       <c r="O5" s="6">
-        <v>1.4846905537459283</v>
+        <v>1.4919354838709677</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -793,46 +793,46 @@
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>205</v>
+        <v>319</v>
       </c>
       <c r="C6" s="4">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="D6" s="4">
-        <v>204</v>
+        <v>326</v>
       </c>
       <c r="E6" s="4">
-        <v>229</v>
+        <v>338</v>
       </c>
       <c r="F6" s="4">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="G6" s="4">
-        <v>236</v>
+        <v>375</v>
       </c>
       <c r="H6" s="4">
-        <v>391</v>
+        <v>362</v>
       </c>
       <c r="I6" s="4">
-        <v>319</v>
+        <v>290</v>
       </c>
       <c r="J6" s="4">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="K6" s="4">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="L6" s="4">
-        <v>338</v>
+        <v>240</v>
       </c>
       <c r="M6" s="4">
-        <v>314</v>
+        <v>372</v>
       </c>
       <c r="N6" s="4">
-        <v>375</v>
+        <v>313</v>
       </c>
       <c r="O6" s="4">
-        <v>362</v>
+        <v>410</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -840,46 +840,46 @@
         <v>6</v>
       </c>
       <c r="B7" s="5">
-        <v>0.22727272727272727</v>
+        <v>0.23559822747415066</v>
       </c>
       <c r="C7" s="5">
-        <v>0.2703016241299304</v>
+        <v>0.22472727272727272</v>
       </c>
       <c r="D7" s="5">
-        <v>0.26666666666666666</v>
+        <v>0.23571945046999276</v>
       </c>
       <c r="E7" s="5">
-        <v>0.25963718820861675</v>
+        <v>0.2206266318537859</v>
       </c>
       <c r="F7" s="5">
-        <v>0.2576</v>
+        <v>0.21249151391717583</v>
       </c>
       <c r="G7" s="5">
-        <v>0.24634655532359082</v>
+        <v>0.22163120567375885</v>
       </c>
       <c r="H7" s="5">
-        <v>0.24731182795698925</v>
+        <v>0.23598435462842243</v>
       </c>
       <c r="I7" s="5">
-        <v>0.23559822747415066</v>
+        <v>0.20848310567936737</v>
       </c>
       <c r="J7" s="5">
-        <v>0.22472727272727272</v>
+        <v>0.21220723917672107</v>
       </c>
       <c r="K7" s="5">
-        <v>0.23571945046999276</v>
+        <v>0.22537878787878787</v>
       </c>
       <c r="L7" s="5">
-        <v>0.2206266318537859</v>
+        <v>0.23928215353938184</v>
       </c>
       <c r="M7" s="5">
-        <v>0.2130257801899593</v>
+        <v>0.24717607973421926</v>
       </c>
       <c r="N7" s="5">
-        <v>0.22163120567375885</v>
+        <v>0.24376947040498442</v>
       </c>
       <c r="O7" s="5">
-        <v>0.23583061889250814</v>
+        <v>0.22043010752688172</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -887,46 +887,46 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>691</v>
+        <v>862</v>
       </c>
       <c r="C8" s="4">
-        <v>677</v>
+        <v>811</v>
       </c>
       <c r="D8" s="4">
-        <v>603</v>
+        <v>859</v>
       </c>
       <c r="E8" s="4">
-        <v>588</v>
+        <v>781</v>
       </c>
       <c r="F8" s="4">
-        <v>797</v>
+        <v>699</v>
       </c>
       <c r="G8" s="4">
-        <v>604</v>
+        <v>822</v>
       </c>
       <c r="H8" s="4">
-        <v>1034</v>
+        <v>761</v>
       </c>
       <c r="I8" s="4">
-        <v>862</v>
+        <v>589</v>
       </c>
       <c r="J8" s="4">
-        <v>811</v>
+        <v>611</v>
       </c>
       <c r="K8" s="4">
-        <v>859</v>
+        <v>666</v>
       </c>
       <c r="L8" s="4">
-        <v>781</v>
+        <v>475</v>
       </c>
       <c r="M8" s="4">
-        <v>699</v>
+        <v>736</v>
       </c>
       <c r="N8" s="4">
-        <v>822</v>
+        <v>660</v>
       </c>
       <c r="O8" s="4">
-        <v>738</v>
+        <v>888</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -934,46 +934,46 @@
         <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>100</v>
+        <v>187</v>
       </c>
       <c r="C9" s="4">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="D9" s="4">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="E9" s="4">
+        <v>160</v>
+      </c>
+      <c r="F9" s="4">
+        <v>121</v>
+      </c>
+      <c r="G9" s="4">
+        <v>164</v>
+      </c>
+      <c r="H9" s="4">
+        <v>133</v>
+      </c>
+      <c r="I9" s="4">
         <v>109</v>
       </c>
-      <c r="F9" s="4">
-        <v>167</v>
-      </c>
-      <c r="G9" s="4">
+      <c r="J9" s="4">
         <v>110</v>
       </c>
-      <c r="H9" s="4">
-        <v>209</v>
-      </c>
-      <c r="I9" s="4">
-        <v>187</v>
-      </c>
-      <c r="J9" s="4">
-        <v>179</v>
-      </c>
       <c r="K9" s="4">
-        <v>177</v>
+        <v>117</v>
       </c>
       <c r="L9" s="4">
+        <v>101</v>
+      </c>
+      <c r="M9" s="4">
+        <v>142</v>
+      </c>
+      <c r="N9" s="4">
+        <v>107</v>
+      </c>
+      <c r="O9" s="4">
         <v>160</v>
-      </c>
-      <c r="M9" s="4">
-        <v>121</v>
-      </c>
-      <c r="N9" s="4">
-        <v>164</v>
-      </c>
-      <c r="O9" s="4">
-        <v>128</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -981,46 +981,46 @@
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>0.1447178002894356</v>
+        <v>0.21693735498839908</v>
       </c>
       <c r="C10" s="5">
-        <v>0.16395864106351551</v>
+        <v>0.22071516646115907</v>
       </c>
       <c r="D10" s="5">
-        <v>0.17412935323383086</v>
+        <v>0.2060535506402794</v>
       </c>
       <c r="E10" s="5">
-        <v>0.18537414965986396</v>
+        <v>0.20486555697823303</v>
       </c>
       <c r="F10" s="5">
-        <v>0.2095357590966123</v>
+        <v>0.17310443490701002</v>
       </c>
       <c r="G10" s="5">
-        <v>0.18211920529801323</v>
+        <v>0.19951338199513383</v>
       </c>
       <c r="H10" s="5">
-        <v>0.20212765957446807</v>
+        <v>0.1747700394218134</v>
       </c>
       <c r="I10" s="5">
-        <v>0.21693735498839908</v>
+        <v>0.18505942275042445</v>
       </c>
       <c r="J10" s="5">
-        <v>0.22071516646115907</v>
+        <v>0.18003273322422259</v>
       </c>
       <c r="K10" s="5">
-        <v>0.2060535506402794</v>
+        <v>0.17567567567567569</v>
       </c>
       <c r="L10" s="5">
-        <v>0.20486555697823303</v>
+        <v>0.21263157894736842</v>
       </c>
       <c r="M10" s="5">
-        <v>0.17310443490701002</v>
+        <v>0.19293478260869565</v>
       </c>
       <c r="N10" s="5">
-        <v>0.19951338199513383</v>
+        <v>0.1621212121212121</v>
       </c>
       <c r="O10" s="5">
-        <v>0.17344173441734417</v>
+        <v>0.18018018018018017</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1028,151 +1028,145 @@
         <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C11" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D11" s="4">
+        <v>12</v>
+      </c>
+      <c r="E11" s="4">
+        <v>25</v>
+      </c>
+      <c r="F11" s="4">
+        <v>4</v>
+      </c>
+      <c r="G11" s="4">
+        <v>3</v>
+      </c>
+      <c r="H11" s="4">
+        <v>3</v>
+      </c>
+      <c r="I11" s="4">
+        <v>7</v>
+      </c>
+      <c r="J11" s="4">
+        <v>7</v>
+      </c>
+      <c r="K11" s="4">
+        <v>11</v>
+      </c>
+      <c r="L11" s="4">
+        <v>12</v>
+      </c>
+      <c r="M11" s="4">
+        <v>10</v>
+      </c>
+      <c r="N11" s="4">
         <v>8</v>
       </c>
-      <c r="E11" s="4">
-        <v>14</v>
-      </c>
-      <c r="F11" s="4">
-        <v>11</v>
-      </c>
-      <c r="G11" s="4">
-        <v>5</v>
-      </c>
-      <c r="H11" s="4">
-        <v>13</v>
-      </c>
-      <c r="I11" s="4">
-        <v>16</v>
-      </c>
-      <c r="J11" s="4">
-        <v>12</v>
-      </c>
-      <c r="K11" s="4">
-        <v>12</v>
-      </c>
-      <c r="L11" s="4">
-        <v>25</v>
-      </c>
-      <c r="M11" s="4">
-        <v>4</v>
-      </c>
-      <c r="N11" s="4">
-        <v>3</v>
-      </c>
-      <c r="O11" s="4">
-        <v>3</v>
-      </c>
+      <c r="O11" s="4"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="4">
+        <v>8</v>
+      </c>
+      <c r="C12" s="4">
+        <v>8</v>
+      </c>
+      <c r="D12" s="4">
+        <v>7</v>
+      </c>
+      <c r="E12" s="4">
+        <v>14</v>
+      </c>
+      <c r="F12" s="4">
+        <v>2</v>
+      </c>
+      <c r="G12" s="4">
+        <v>2</v>
+      </c>
+      <c r="H12" s="4">
+        <v>2</v>
+      </c>
+      <c r="I12" s="4">
+        <v>3</v>
+      </c>
+      <c r="J12" s="4">
         <v>5</v>
       </c>
-      <c r="C12" s="4">
+      <c r="K12" s="4">
+        <v>8</v>
+      </c>
+      <c r="L12" s="4">
         <v>9</v>
       </c>
-      <c r="D12" s="4">
-        <v>2</v>
-      </c>
-      <c r="E12" s="4">
-        <v>6</v>
-      </c>
-      <c r="F12" s="4">
-        <v>8</v>
-      </c>
-      <c r="G12" s="4">
-        <v>3</v>
-      </c>
-      <c r="H12" s="4">
+      <c r="M12" s="4">
         <v>9</v>
       </c>
-      <c r="I12" s="4">
-        <v>8</v>
-      </c>
-      <c r="J12" s="4">
-        <v>8</v>
-      </c>
-      <c r="K12" s="4">
+      <c r="N12" s="4">
         <v>7</v>
       </c>
-      <c r="L12" s="4">
-        <v>14</v>
-      </c>
-      <c r="M12" s="4">
-        <v>2</v>
-      </c>
-      <c r="N12" s="4">
-        <v>2</v>
-      </c>
-      <c r="O12" s="4">
-        <v>2</v>
-      </c>
+      <c r="O12" s="4"/>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="5">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="C13" s="5">
-        <v>0.6923076923076923</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D13" s="5">
-        <v>0.25</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E13" s="5">
+        <v>0.56</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I13" s="5">
         <v>0.42857142857142855</v>
       </c>
-      <c r="F13" s="5">
+      <c r="J13" s="5">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="K13" s="5">
         <v>0.7272727272727273</v>
       </c>
-      <c r="G13" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="H13" s="5">
-        <v>0.6923076923076923</v>
-      </c>
-      <c r="I13" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="J13" s="5">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="K13" s="5">
-        <v>0.5833333333333334</v>
-      </c>
       <c r="L13" s="5">
-        <v>0.56</v>
+        <v>0.75</v>
       </c>
       <c r="M13" s="5">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="N13" s="5">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="O13" s="5">
-        <v>0.6666666666666666</v>
-      </c>
+        <v>0.875</v>
+      </c>
+      <c r="O13" s="5"/>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="4">
         <v>0</v>
@@ -1193,13 +1187,13 @@
         <v>0</v>
       </c>
       <c r="J14" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="4">
         <v>0</v>
       </c>
       <c r="L14" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M14" s="4">
         <v>0</v>
@@ -1207,9 +1201,7 @@
       <c r="N14" s="4">
         <v>0</v>
       </c>
-      <c r="O14" s="4">
-        <v>0</v>
-      </c>
+      <c r="O14" s="4"/>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
@@ -1225,7 +1217,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="4">
         <v>0</v>
@@ -1246,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M15" s="4">
         <v>0</v>
@@ -1254,33 +1246,27 @@
       <c r="N15" s="4">
         <v>0</v>
       </c>
-      <c r="O15" s="4">
-        <v>0</v>
-      </c>
+      <c r="O15" s="4"/>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="5">
-        <v>0</v>
-      </c>
-      <c r="C16" s="5">
-        <v>0</v>
-      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
       <c r="K16" s="5"/>
-      <c r="L16" s="5">
-        <v>0.75</v>
-      </c>
+      <c r="L16" s="5"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
@@ -1328,9 +1314,7 @@
       <c r="N17" s="4">
         <v>0</v>
       </c>
-      <c r="O17" s="4">
-        <v>0</v>
-      </c>
+      <c r="O17" s="4"/>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
@@ -1375,9 +1359,7 @@
       <c r="N18" s="4">
         <v>0</v>
       </c>
-      <c r="O18" s="4">
-        <v>0</v>
-      </c>
+      <c r="O18" s="4"/>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">

--- a/AutoCava_AI最新统计表.xlsx
+++ b/AutoCava_AI最新统计表.xlsx
@@ -887,46 +887,46 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
+        <v>866</v>
+      </c>
+      <c r="C8" s="4">
+        <v>814</v>
+      </c>
+      <c r="D8" s="4">
         <v>862</v>
       </c>
-      <c r="C8" s="4">
-        <v>811</v>
-      </c>
-      <c r="D8" s="4">
-        <v>859</v>
-      </c>
       <c r="E8" s="4">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="F8" s="4">
-        <v>699</v>
+        <v>712</v>
       </c>
       <c r="G8" s="4">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="H8" s="4">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="I8" s="4">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="J8" s="4">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="K8" s="4">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="L8" s="4">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="M8" s="4">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="N8" s="4">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="O8" s="4">
-        <v>888</v>
+        <v>895</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -934,28 +934,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C9" s="4">
         <v>179</v>
       </c>
       <c r="D9" s="4">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E9" s="4">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F9" s="4">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G9" s="4">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H9" s="4">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I9" s="4">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="J9" s="4">
         <v>110</v>
@@ -964,16 +964,16 @@
         <v>117</v>
       </c>
       <c r="L9" s="4">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M9" s="4">
         <v>142</v>
       </c>
       <c r="N9" s="4">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O9" s="4">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -981,46 +981,46 @@
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>0.21693735498839908</v>
+        <v>0.21709006928406466</v>
       </c>
       <c r="C10" s="5">
-        <v>0.22071516646115907</v>
+        <v>0.2199017199017199</v>
       </c>
       <c r="D10" s="5">
-        <v>0.2060535506402794</v>
+        <v>0.20765661252900233</v>
       </c>
       <c r="E10" s="5">
-        <v>0.20486555697823303</v>
+        <v>0.20558375634517767</v>
       </c>
       <c r="F10" s="5">
-        <v>0.17310443490701002</v>
+        <v>0.17696629213483145</v>
       </c>
       <c r="G10" s="5">
-        <v>0.19951338199513383</v>
+        <v>0.19975786924939468</v>
       </c>
       <c r="H10" s="5">
-        <v>0.1747700394218134</v>
+        <v>0.17493472584856398</v>
       </c>
       <c r="I10" s="5">
-        <v>0.18505942275042445</v>
+        <v>0.1899159663865546</v>
       </c>
       <c r="J10" s="5">
-        <v>0.18003273322422259</v>
+        <v>0.17944535073409462</v>
       </c>
       <c r="K10" s="5">
-        <v>0.17567567567567569</v>
+        <v>0.17436661698956782</v>
       </c>
       <c r="L10" s="5">
-        <v>0.21263157894736842</v>
+        <v>0.21338912133891214</v>
       </c>
       <c r="M10" s="5">
-        <v>0.19293478260869565</v>
+        <v>0.19241192411924118</v>
       </c>
       <c r="N10" s="5">
-        <v>0.1621212121212121</v>
+        <v>0.16289592760180996</v>
       </c>
       <c r="O10" s="5">
-        <v>0.18018018018018017</v>
+        <v>0.18212290502793296</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
